--- a/translate.xlsx
+++ b/translate.xlsx
@@ -1176,7 +1176,7 @@
     <t>EncyDesc_DrillTool</t>
   </si>
   <si>
-    <t>The Drill Tool is an industrial instrument capable of extracting mineral formations that are otherwise impenetrable by standard survival equipment.
+    <t>The drill tool is an industrial instrument capable of extracting mineral formations that are otherwise impenetrable by standard survival equipment.
 It allows for high-yield resource harvesting without the deployment of a Prawn Suit.
 - Reinforced industrial diamond coating enables fracturing the molecular bonds of large mineral veins
 - Rear-facing micro-thrusters prevent the operator from being propelled backward by the drill's resistance
@@ -1184,7 +1184,7 @@
 "By bypassing the need for heavy vehicular deployment, you have saved Alterra 4.2 credits in fuel cell depreciation. You're welcome."</t>
   </si>
   <si>
-    <t>Die Boorgereedskap is 'n industriële instrument wat in staat is om mineraalformasies te onttrek wat andersins ondeurdringbaar is deur standaard oorlewingstoerusting.
+    <t>Die boorgereedskap is 'n industriële instrument wat in staat is om mineraalformasies te onttrek wat andersins ondeurdringbaar is deur standaard oorlewingstoerusting.
 Dit maak voorsiening vir hoë-opbrengs hulpbron-oes sonder die ontplooiing van 'n Garnalepak.
 - Versterkte industriële diamantlaag maak dit moontlik om die molekulêre bindings van groot mineraalare te breek.
 - Agtertoe gerigte mikro-stuwers verhoed dat die operateur deur die boor se weerstand agtertoe gedryf word.
@@ -1203,52 +1203,52 @@
     <t>L'eina de perforació és un instrument industrial capaç d'extreure formacions minerals que d'altra banda serien impenetrables per a equips de supervivència estàndard.
 Permet la recobriment de recursos d'alt rendiment sense el desplegament d'un vestit de gamba.
 - El recobriment de diamant industrial reforçat permet fracturar els enllaços moleculars de grans venes minerals.
-- Els micropropulsors orientats cap enrere eviten que l'operador sigui impulsat cap enrere per la resistència del trepant.
-- El motor de parell variable ajusta les RPM en funció de la densitat del material per evitar que la broca s'enganxi i el rebot que pugui provocar una fractura del canell.
+- Els micropropulsors orientats cap enrere eviten que l'operador sigui impulsat cap enrere per la resistència de la perforadora.
+- El motor de parell variable ajusta les RPM en funció de la densitat del material per evitar que la broca s'enganxi i el rebot que es produeixi per fracturar el canell.
 "En evitar la necessitat de desplegament de vehicles pesats, heu estalviat a Alterra 4,2 crèdits en la depreciació de les piles de combustible. De res."</t>
   </si>
   <si>
-    <t>钻探工具是一种工业级仪器，能够开采标准生存装备无法穿透的矿层。
-它无需部署虾式机甲即可高效采集资源。
+    <t>这款钻机是一种工业级工具，能够开采标准生存装备无法穿透的矿层。
+它无需部署虾式机甲即可实现高产资源采集。
 - 强化型工业金刚石涂层能够破坏大型矿脉的分子键
-- 后置微型推进器可防止操作员因钻头阻力而被向后推
+- 后置微型推进器可防止操作员因钻机阻力而被向后推
 - 可变扭矩电机可根据材料密度调节转速，防止钻头卡死和手腕反冲
 “由于无需部署重型载具，您节省了 Alterra 4.2 点燃料电池折旧费用。不用谢。”</t>
   </si>
   <si>
-    <t>鑽探工具是一種工業級儀器，能夠開採標準生存裝備無法穿透的礦層。
-它無需部署蝦式機甲即可高效採集資源。
+    <t>這款鑽孔機是一種工業級工具，能夠開採標準生存裝備無法穿透的礦層。
+它無需部署蝦式機甲即可實現高產量資源採集。
 - 強化型工業用鑽石塗層能夠破壞大型礦脈的分子鍵
-- 後置微型推進器可防止操作員因鑽頭阻力而被向後推
+- 後置微型推進器可防止操作員因鑽機阻力而被向後推
 - 可變扭矩馬達可根據材料密度調節轉速，防止鑽頭卡死和手腕反轉
 “由於無需部署重型載具，您節省了 Alterra 4.2 點燃料電池折舊費用。不用謝。”</t>
   </si>
   <si>
     <t>Alat za bušenje je industrijski instrument sposoban za vađenje mineralnih formacija koje su inače neprobojne standardnom opremom za preživljavanje.
-Omogućuje visokoprinosno iskorištavanje resursa bez upotrebe Odijela za kozice.
+Omogućuje visokoprinosno iskorištavanje resursa bez upotrebe odijela za kozice.
 - Ojačani industrijski dijamantni premaz omogućuje razbijanje molekularnih veza velikih mineralnih žila
 - Mikro-potisnici okrenuti prema natrag sprječavaju da se operater pomiče unatrag otporom bušilice
 - Motor s promjenjivim momentom prilagođava broj okretaja na temelju gustoće materijala kako bi se spriječilo blokiranje svrdla i povratni udarac od loma ručnog zgloba
 "Zaobilaženjem potrebe za korištenjem teških vozila, uštedjeli ste Alterra 4,2 kredita u amortizaciji gorivnih ćelija. Nema na čemu."</t>
   </si>
   <si>
-    <t>Vrták je průmyslový nástroj schopný těžit minerální formace, které jsou jinak pro standardní vybavení pro přežití neproniknutelné.
-Umožňuje těžbu zdrojů s vysokým výtěžkem bez použití krevetového obleku.
+    <t>Vrtací nástroj je průmyslový nástroj schopný těžit minerální formace, které jsou jinak pro standardní vybavení pro přežití neproniknutelné.
+Umožňuje těžbu zdrojů s vysokým výtěžkem bez použití obleku Prawn Suit.
 - Zesílený průmyslový diamantový povlak umožňuje rozrušit molekulární vazby velkých minerálních žil.
 - Mikromotory směřující dozadu zabraňují tomu, aby byl obsluha hnána dozadu odporem vrtáku.
 - Motor s proměnným točivým momentem upravuje otáčky na základě hustoty materiálu, aby se zabránilo zaseknutí vrtáku a zpětnému rázu způsobenému zlomeninou zápěstí.
 „Tím, že jste se vyhnuli nutnosti nasazení těžkých vozidel, jste ušetřili 4,2 kreditu Alterra na odpisech palivových článků. Není zač.“</t>
   </si>
   <si>
-    <t>Drill Tool er et industrielt instrument, der er i stand til at udvinde mineralformationer, der ellers er uigennemtrængelige for standard overlevelsesudstyr.
+    <t>Boreværktøjet er et industrielt instrument, der er i stand til at udvinde mineralformationer, der ellers er uigennemtrængelige for standard overlevelsesudstyr.
 Det muliggør høst af ressourcer med højt udbytte uden brug af en rejedragt.
 - Forstærket industriel diamantbelægning muliggør brud på de molekylære bindinger i store mineralårer.
 - Bagudvendte mikro-thrustere forhindrer, at operatøren drives bagud af borets modstand.
-- Motor med variabelt moment justerer omdrejningstallet baseret på materialedensitet for at forhindre fastklemning af boret og tilbageslag fra håndledsbrud.
+- Motor med variabelt moment justerer omdrejningstallet baseret på materialedensitet for at forhindre borehovedbinding og tilbageslag fra håndledsbrud.
 "Ved at omgå behovet for tunge køretøjer har du sparet Alterra 4,2 point i afskrivning af brændstofceller. Velbekomme."</t>
   </si>
   <si>
-    <t>De boormachine is een industrieel instrument dat in staat is om minerale formaties te winnen die anders ondoordringbaar zijn voor standaard overlevingsuitrusting.
+    <t>De boor is een industrieel instrument dat in staat is om minerale formaties te winnen die anders ondoordringbaar zijn voor standaard overlevingsuitrusting.
 Het maakt een hoge opbrengst aan grondstoffenwinning mogelijk zonder de inzet van een Prawn Suit.
 - Versterkte industriële diamantcoating maakt het mogelijk om de moleculaire bindingen van grote minerale aderen te verbreken.
 - Naar achteren gerichte micro-stuwraketten voorkomen dat de operator door de weerstand van de boor naar achteren wordt geduwd.
@@ -1256,7 +1256,7 @@
 "Door de noodzaak van zwaar transport te omzeilen, heeft u Alterra 4,2 credits bespaard op de afschrijving van brandstofcellen. Graag gedaan."</t>
   </si>
   <si>
-    <t>Puurtööriist on tööstuslik instrument, mis on võimeline kaevandama mineraalkihte, mis muidu oleksid tavalise ellujäämisvarustusega läbimatud.
+    <t>See puurmasin on tööstuslik instrument, mis on võimeline kaevandama mineraalkihte, mis muidu oleksid tavalise ellujäämisvarustusega läbimatud.
 See võimaldab suure saagikusega ressursse koguda ilma krevetiülikonnata.
 - Tugevdatud tööstuslik teemantkate võimaldab purustada suurte mineraalisoonte molekulaarsidemeid.
 - Tahapoole suunatud mikromootorid takistavad operaatori tagasilööki puuri takistuse tõttu.
@@ -1264,19 +1264,19 @@
 "Raskete sõidukite kasutamise vajaduse vältimisega olete säästnud Alterrale 4,2 krediiti kütuseelementide amortisatsiooni pealt. Pole tänu väärt."</t>
   </si>
   <si>
-    <t>Porakone on teollisuuslaite, jolla voidaan louhia mineraalimuodostelmia, jotka muuten olisivat läpäisemättömiä tavallisilla selviytymisvarusteilla.
+    <t>Poraustyökalu on teollisuuslaite, jolla voidaan louhia mineraalimuodostelmia, jotka muuten olisivat läpäisemättömiä tavallisilla selviytymisvarusteilla.
 Se mahdollistaa suuren saannon luonnonvarojen keräämisen ilman katkarapuvun käyttöä.
 - Vahvistettu teollinen timanttipinnoite mahdollistaa suurten mineraalijuonien molekyylisidosten murtamisen.
-- Taaksepäin suunnatut mikropropulsiot estävät käyttäjää lennähtämästä taaksepäin poran vastuksen vaikutuksesta.
+- Taaksepäin suunnatut mikrotyöntövoimalaitteet estävät käyttäjää lennähtämästä taaksepäin poran vastuksen vaikutuksesta.
 - Muuttuvan vääntömomentin moottori säätää kierroslukua materiaalin tiheyden perusteella estääkseen terän juuttumisen ja ranteen murtuman aiheuttaman takapotkun.
 "Ohittamalla raskaiden ajoneuvojen käytön tarpeen olet säästänyt Alterralta 4,2 krediittiä polttokennojen poistoissa. Ole hyvä."</t>
   </si>
   <si>
     <t>L'outil de forage est un instrument industriel capable d'extraire des formations minérales inaccessibles aux équipements de survie classiques.
-Il permet une exploitation optimale des ressources sans nécessiter de combinaison spéciale.
+Il permet une exploitation à haut rendement des ressources sans nécessiter de combinaison spéciale.
 - Son revêtement diamant industriel renforcé permet de fracturer les liaisons moléculaires des grands filons minéraux.
 - Des micro-propulseurs arrière empêchent l'opérateur d'être repoussé par la résistance de la foreuse.
-- Son moteur à couple variable ajuste la vitesse de rotation en fonction de la densité du matériau afin d'éviter le blocage du foret et les risques de blessure au poignet.
+- Son moteur à couple variable ajuste la vitesse de rotation en fonction de la densité du matériau afin d'éviter le blocage du trépan et les risques de blessure au poignet.
 « En évitant le déploiement de véhicules lourds, vous avez permis à Alterra d'économiser 4,2 crédits en amortissement de la pile à combustible. De rien. »</t>
   </si>
   <si>
@@ -1288,8 +1288,8 @@
 „Durch den Verzicht auf schwere Fahrzeuge haben Sie Alterra 4.2 Credits für die Brennstoffzellenabschreibung eingespart. Gern geschehen.“</t>
   </si>
   <si>
-    <t>Το Εργαλείο Τρυπανιού είναι ένα βιομηχανικό όργανο ικανό να εξάγει ορυκτούς σχηματισμούς που διαφορετικά θα ήταν αδιαπέραστοι από τον τυπικό εξοπλισμό επιβίωσης.
-Επιτρέπει τη συγκομιδή πόρων υψηλής απόδοσης χωρίς την ανάπτυξη μιας Στολής Γαρίδας.
+    <t>Το εργαλείο τρυπανιού είναι ένα βιομηχανικό όργανο ικανό να εξάγει ορυκτούς σχηματισμούς που διαφορετικά θα ήταν αδιαπέραστοι από τον τυπικό εξοπλισμό επιβίωσης.
+Επιτρέπει τη συγκομιδή πόρων υψηλής απόδοσης χωρίς την ανάπτυξη μιας στολής γαρίδας.
 - Η ενισχυμένη βιομηχανική επίστρωση διαμαντιού επιτρέπει τη θραύση των μοριακών δεσμών μεγάλων ορυκτών φλεβών
 - Οι μικρο-προωθητήρες που είναι στραμμένοι προς τα πίσω εμποδίζουν τον χειριστή να ωθηθεί προς τα πίσω από την αντίσταση του τρυπανιού
 - Ο κινητήρας μεταβλητής ροπής ρυθμίζει τις στροφές ανά λεπτό με βάση την πυκνότητα του υλικού για να αποτρέψει το μπλοκάρισμα του τρυπανιού και το κλώτσημα από το κάταγμα του καρπού
@@ -1304,23 +1304,23 @@
 "A nehéz járművek használatának megkerülésével 4,2 kreditet takarított meg az Alterra üzemanyagcella-értékcsökkenésén. Szívesen."</t>
   </si>
   <si>
-    <t>Is uirlis thionsclaíoch í an Uirlis Druileála atá in ann foirmíochtaí mianraí a bhaint amach nach mbeadh trealaimh mharthanais chaighdeánacha in ann dul tríd murach sin.
-Ceadaíonn sé fómhar acmhainní ard-toraidh gan Culaith Cloicheán a imscaradh.
+    <t>Is uirlis thionsclaíoch í an uirlis druileála atá in ann foirmíochtaí mianraí a bhaint amach nach mbeadh trealaimh mharthanais chaighdeánacha in ann dul tríd murach sin.
+Ceadaíonn sé fómhar acmhainní ard-toraidh gan úsáid a bhaint as Culaith Cloicheán.
 - Cumasaíonn sciath diamant tionsclaíoch athneartaithe naisc mhóilíneacha féitheacha móra mianraí a bhriseadh
 - Coscann micrea-bhrúiteoirí atá os comhair an chúl an t-oibreoir ó bheith á thiomáint siar ag friotaíocht an druileála
 - Coigeartaíonn mótar chasmhóiminte athraitheach RPM bunaithe ar dhlús ábhair chun ceangal giotán agus cic siar briste caol na láimhe a chosc
-"Tríd an ngá atá le himscaradh feithiclí troma a sheachaint, tá 4.2 creidiúint Alterra sábháilte agat i ndíluacháil cealla breosla. Tá fáilte romhat."</t>
+"Tríd an ngá atá le húsáid feithiclí troma a sheachaint, tá 4.2 creidiúint Alterra sábháilte agat i ndíluacháil cealla breosla. Tá fáilte romhat."</t>
   </si>
   <si>
     <t>La trivella è uno strumento industriale in grado di estrarre formazioni minerarie altrimenti impenetrabili con le normali attrezzature di sopravvivenza.
-Consente l'estrazione di risorse ad alto rendimento senza la necessità di indossare una tuta Prawn.
+Consente un'estrazione di risorse ad alto rendimento senza la necessità di indossare una tuta Prawn.
 - Il rivestimento diamantato industriale rinforzato permette di fratturare i legami molecolari di grandi vene minerarie.
 - I micro-propulsori posteriori impediscono all'operatore di essere spinto all'indietro dalla resistenza della trivella.
 - Il motore a coppia variabile regola i giri al minuto in base alla densità del materiale per evitare l'inceppamento della punta e il contraccolpo che potrebbe causare fratture al polso.
 "Evitando l'impiego di veicoli pesanti, hai risparmiato 4,2 crediti Alterra in ammortamento delle celle a combustibile. Prego."</t>
   </si>
   <si>
-    <t>ドリルツールは、通常のサバイバル装備では掘削不可能な鉱物層を採掘できる産業用機器です。
+    <t>このドリルツールは、通常のサバイバル装備では掘削不可能な鉱物層を採掘できる産業用機器です。
 これにより、プラウンスーツを装備することなく、高収量の資源採掘が可能になります。
 - 強化された工業用ダイヤモンドコーティングにより、大型鉱脈の分子結合を破壊します。
 - 後方に取り付けられたマイクロスラスタにより、ドリルの抵抗によってオペレーターが後方に押し戻されるのを防ぎます。
@@ -1328,8 +1328,8 @@
 「大型車両の展開が不要になったことで、燃料電池の減価償却費をアルテラ4.2クレジット節約できました。どういたしまして。」</t>
   </si>
   <si>
-    <t>드릴 툴은 일반적인 생존 장비로는 접근할 수 없는 광물층을 채굴할 수 있는 산업용 장비입니다.
-프론 슈트를 착용하지 않고도 높은 수확량의 자원을 채취할 수 있습니다.
+    <t>드릴 도구는 일반적인 생존 장비로는 접근할 수 없는 광물층을 채굴할 수 있는 산업용 장비입니다.
+프론 슈트(Prawn Suit)를 착용하지 않고도 높은 수확량의 자원을 채취할 수 있습니다.
 - 강화된 산업용 다이아몬드 코팅으로 대형 광맥의 분자 결합을 파괴할 수 있습니다.
 - 후방 마이크로 추진기는 드릴의 저항으로 인해 작업자가 뒤로 밀리지 않도록 방지합니다.
 - 가변 토크 모터는 재료 밀도에 따라 회전수를 조절하여 드릴 비트 걸림과 손목 골절을 방지합니다.
@@ -1341,7 +1341,7 @@
 - Pastiprināts rūpnieciskais dimanta pārklājums ļauj pārraut lielu minerālu vēnu molekulārās saites.
 - Aizmugurē vērsti mikrodzinēji neļauj operatoram tikt atgrūstam atpakaļ urbja pretestības dēļ.
 - Mainīga griezes momenta motors pielāgo apgriezienus minūtē, pamatojoties uz materiāla blīvumu, lai novērstu urbja iesprūšanu un plaukstas locītavas lūzuma atsitienu.
-"Apejot nepieciešamību izmantot smagus transportlīdzekļus, jūs esat ietaupījis Alterra 4,2 kredītpunktus degvielas elementu nolietojumā. Nav par ko."</t>
+"Apejot nepieciešamību izmantot smagos transportlīdzekļus, jūs esat ietaupījis Alterra 4,2 kredītpunktus degvielas elementu nolietojumā. Nav par ko."</t>
   </si>
   <si>
     <t>Gręžimo įrankis yra pramoninis instrumentas, galintis išgauti mineralinius darinius, į kuriuos kitaip neįsibrautų standartinė išgyvenimo įranga.
@@ -1349,27 +1349,27 @@
 - Sustiprinta pramoninė deimantinė danga leidžia suardyti didelių mineralinių gyslų molekulinius ryšius.
 - Galiniai mikrovarikliai neleidžia operatoriui būti stumtam atgal dėl grąžto pasipriešinimo.
 - Kintamo sukimo momento variklis reguliuoja apsukas pagal medžiagos tankį, kad būtų išvengta grąžto strigimo ir riešo lūžio atatrankos.
-„Aplenkdami poreikį naudoti sunkias transporto priemones, sutaupėte 4,2 „Alterra“ kreditų už kuro elementų nusidėvėjimą. Prašom.“</t>
-  </si>
-  <si>
-    <t>Drill Tool er et industrielt instrument som er i stand til å utvinne mineralformasjoner som ellers er ugjennomtrengelige med standard overlevelsesutstyr.
+„Aplenkdami poreikį naudoti sunkiasvores transporto priemones, sutaupėte 4,2 „Alterra“ kreditų už kuro elementų nusidėvėjimą. Prašom.“</t>
+  </si>
+  <si>
+    <t>Boreverktøyet er et industrielt instrument som er i stand til å utvinne mineralformasjoner som ellers er ugjennomtrengelige med standard overlevelsesutstyr.
 Det muliggjør høyavkastende ressurshøsting uten bruk av rekedrakt.
 - Forsterket industrielt diamantbelegg muliggjør brudd i de molekylære bindingene i store mineralårer.
 - Bakovervendte mikro-thrustere forhindrer at operatøren drives bakover av borets motstand.
-- Variabelt dreiemomentmotor justerer turtallet basert på materialtetthet for å forhindre at boret setter seg fast og tilbakeslag som kan forårsake håndleddsbrudd.
-"Ved å omgå behovet for tunge kjøretøy, har du spart Alterra 4,2 studiepoeng i avskrivning av brenselceller. Bare hyggelig."</t>
-  </si>
-  <si>
-    <t>Drill Tool to narzędzie przemysłowe, które umożliwia wydobywanie z formacji mineralnych, które są w innym przypadku niedostępne dla standardowego sprzętu survivalowego.
+- Motor med variabelt dreiemoment justerer turtallet basert på materialtetthet for å forhindre at boret setter seg fast og tilbakeslag som kan forårsake håndleddsbrudd.
+"Ved å omgå behovet for bruk av tunge kjøretøy har du spart Alterra 4,2 studiepoeng i avskrivning av brenselceller. Bare hyggelig."</t>
+  </si>
+  <si>
+    <t>Wiertnica to urządzenie przemysłowe, które umożliwia wydobywanie z formacji mineralnych, które są w innym przypadku niedostępne dla standardowego sprzętu survivalowego.
 Umożliwia ono wysokowydajne pozyskiwanie surowców bez użycia kombinezonu Prawn.
 - Wzmocniona przemysłowa powłoka diamentowa umożliwia rozrywanie wiązań molekularnych w dużych żyłach mineralnych.
-- Mikrosilniki skierowane do tyłu zapobiegają odpychaniu operatora do tyłu przez opór wiertła.
+- Mikrosilniki skierowane do tyłu zapobiegają odpychaniu operatora do tyłu przez opór wiertarki.
 - Silnik o zmiennym momencie obrotowym dostosowuje obroty na podstawie gęstości materiału, aby zapobiec zakleszczaniu się wiertła i odrzutowi nadgarstka.
-„Dzięki wyeliminowaniu konieczności użycia ciężkich pojazdów zaoszczędziłeś firmie Alterra 4,2 punktu na amortyzacji ogniw paliwowych. Zapraszamy”.</t>
-  </si>
-  <si>
-    <t>A Ferramenta de Perfuração é um instrumento industrial capaz de extrair formações minerais que seriam impenetráveis ​​para equipamentos de sobrevivência padrão.
-Ela permite a extração de recursos de alto rendimento sem a necessidade de usar um Traje PRAWN.
+„Dzięki wyeliminowaniu konieczności użycia ciężkich pojazdów zaoszczędziliście Państwo firmie Alterra 4,2 kredytu na amortyzacji ogniw paliwowych. Zapraszamy”.</t>
+  </si>
+  <si>
+    <t>A ferramenta de perfuração é um instrumento industrial capaz de extrair formações minerais que seriam impenetráveis ​​para equipamentos de sobrevivência padrão.
+Ela permite a extração de recursos de alto rendimento sem a necessidade de usar um traje PRAWN.
 - O revestimento reforçado de diamante industrial permite fraturar as ligações moleculares de grandes veios minerais.
 - Micropropulsores traseiros impedem que o operador seja impulsionado para trás pela resistência da perfuratriz.
 - O motor de torque variável ajusta a RPM com base na densidade do material para evitar o travamento da broca e o recuo que pode causar fraturas no pulso.
@@ -1379,7 +1379,7 @@
     <t>Instrumentul de foraj este un instrument industrial capabil să extragă formațiuni minerale care altfel ar fi impenetrabile de echipamentele standard de supraviețuire.
 Permite recoltarea resurselor cu randament ridicat fără a fi nevoie de utilizarea unui costum Prawn.
 - Stratul industrial ranforsat cu diamant permite fracturarea legăturilor moleculare ale venelor minerale mari
-- Micropropulsoarele orientate spre spate împiedică operatorul să fie propulsat înapoi de rezistența burghiului
+- Micropropulsoarele orientate spre spate împiedică operatorul să fie propulsat înapoi de rezistența forajului
 - Motorul cu cuplu variabil ajustează turația în funcție de densitatea materialului pentru a preveni blocarea burghiului și reculul cauzat de fracturarea încheieturii mâinii
 „Evitând necesitatea utilizării vehiculelor grele, ați economisit 4,2 credite la Alterra în deprecierea pilelor de combustibil. Cu plăcere.”</t>
   </si>
@@ -1397,10 +1397,10 @@
 - Ојачани индустријски дијамантски премаз омогућава разбијање молекуларних веза великих минералних вена.
 - Микро-потисници окренути уназад спречавају да оператер буде потиснут уназад отпором бушилице.
 - Мотор са променљивим обртним моментом подешава број обртаја на основу густине материјала како би се спречило заглављивање бургије и повратни ударац услед прелома зглоба.
-„Заобилажењем потребе за тешким возилима, уштедели сте Алтери 4,2 кредита у амортизацији горивних ћелија. Нема на чему.“</t>
-  </si>
-  <si>
-    <t>Vŕtačka je priemyselný nástroj schopný ťažiť minerálne formácie, ktoré sú inak nepreniknuteľné štandardným vybavením na prežitie.
+„Заобилажењем потребе за распоређивањем тешких возила, уштедели сте Алтери 4,2 кредита у амортизацији горивних ћелија. Нема на чему.“</t>
+  </si>
+  <si>
+    <t>Vŕtací nástroj je priemyselný nástroj schopný ťažiť minerálne formácie, ktoré sú inak nepreniknuteľné štandardným vybavením na prežitie.
 Umožňuje ťažbu zdrojov s vysokým výnosom bez použitia krevetového obleku.
 - Zosilnený priemyselný diamantový povlak umožňuje rozbíjanie molekulárnych väzieb veľkých minerálnych žíl
 - Mikromotory smerujúce dozadu zabraňujú tomu, aby bol operátor hnaný dozadu odporom vrtáka
@@ -1408,7 +1408,7 @@
 „Vďaka obídeniu potreby nasadenia ťažkých vozidiel ste ušetrili 4,2 kreditu Alterra na odpisoch palivových článkov. Nie je zač.“</t>
   </si>
   <si>
-    <t>Vrtalno orodje je industrijski instrument, ki lahko izkopava mineralne formacije, ki so sicer neprebojne za standardno opremo za preživetje.
+    <t>Vrtalno orodje je industrijski instrument, ki lahko izkopava mineralne formacije, ki so sicer neprebojne s standardno opremo za preživetje.
 Omogoča visoko donosno pridobivanje virov brez uporabe zaščitne obleke za kozice.
 - Ojačana industrijska diamantna prevleka omogoča lomljenje molekularnih vezi velikih mineralnih žil.
 - Mikropotisniki, obrnjeni nazaj, preprečujejo, da bi upor svedra potisnil upravljavca nazaj.
@@ -1416,20 +1416,20 @@
 "Z izogibanjem potrebi po uporabi težkih vozil ste prihranili 4,2 kreditne točke Alterra pri amortizaciji gorivnih celic. Ni za kaj."</t>
   </si>
   <si>
-    <t>La Perforadora es un instrumento industrial capaz de extraer formaciones minerales impenetrables para el equipo de supervivencia estándar.
+    <t>La herramienta de perforación es un instrumento industrial capaz de extraer formaciones minerales impenetrables para el equipo de supervivencia estándar.
 Permite la extracción de recursos de alto rendimiento sin necesidad de usar un traje Prawn.
-- El revestimiento reforzado de diamante industrial permite fracturar los enlaces moleculares de grandes vetas minerales.
-- Los micropropulsores traseros evitan que el operador retroceda debido a la resistencia de la perforadora.
+- El recubrimiento reforzado de diamante industrial permite fracturar los enlaces moleculares de grandes vetas minerales.
+- Los micropropulsores traseros evitan que el operador retroceda debido a la resistencia de la perforación.
 - El motor de par variable ajusta las RPM según la densidad del material para evitar que la broca se atasque y el retroceso por fractura de muñeca.
 "Al evitar la necesidad de desplegar vehículos pesados, le has ahorrado a Alterra 4.2 créditos en depreciación de celdas de combustible. De nada."</t>
   </si>
   <si>
     <t>Borrverktyget är ett industriellt instrument som kan utvinna mineralformationer som annars är ogenomträngliga med vanlig överlevnadsutrustning.
-Det möjliggör högavkastande resursutvinning utan att en räkdräkt behöver användas.
+Det möjliggör högavkastande resursutvinning utan användning av räkdräkt.
 - Förstärkt industriell diamantbeläggning möjliggör spräckning av de molekylära bindningarna i stora mineralådror.
 - Bakåtvända mikromotorer förhindrar att operatören drivs bakåt av borrens motstånd.
 - Motor med variabelt vridmoment justerar varvtalet baserat på materialdensitet för att förhindra att borren fastnar och kast som orsakar handledsfrakturer.
-"Genom att undvika behovet av tunga fordon har du sparat Alterra 4,2 poäng i bränslecellsavskrivning. Varsågod."</t>
+"Genom att kringgå behovet av tunga fordon har du sparat Alterra 4,2 poäng i bränslecellsavskrivning. Varsågod."</t>
   </si>
   <si>
     <t>เครื่องมือเจาะนี้เป็นเครื่องมืออุตสาหกรรมที่สามารถสกัดแร่ธาตุที่อุปกรณ์เอาชีวิตรอดมาตรฐานไม่สามารถเข้าถึงได้
@@ -1440,20 +1440,20 @@
 "ด้วยการหลีกเลี่ยงความจำเป็นในการใช้ยานพาหนะขนาดใหญ่ คุณได้ประหยัดค่าเสื่อมราคาของเซลล์เชื้อเพลิงให้กับ Alterra ไป 4.2 เครดิต ยินดีครับ"</t>
   </si>
   <si>
-    <t>Matkap Aleti, standart hayatta kalma ekipmanlarıyla geçilemeyen mineral oluşumlarını çıkarabilen endüstriyel bir alettir.
+    <t>Bu matkap, standart hayatta kalma ekipmanlarıyla geçilemeyen mineral oluşumlarını çıkarabilen endüstriyel bir alettir.
 Bir Prawn Suit'in kullanılmasına gerek kalmadan yüksek verimli kaynak hasadı sağlar.
 - Güçlendirilmiş endüstriyel elmas kaplama, büyük mineral damarlarının moleküler bağlarını kırmayı sağlar.
 - Arkaya bakan mikro iticiler, operatörün matkabın direncinden dolayı geriye doğru itilmesini önler.
-- Değişken torklu motor, uç sıkışmasını ve bilek kırılmasına neden olabilecek geri tepmeyi önlemek için devir sayısını malzeme yoğunluğuna göre ayarlar.
+- Değişken torklu motor, uç sıkışmasını ve bilek kırılmasına neden olabilecek geri tepmeyi önlemek için malzeme yoğunluğuna göre devir sayısını ayarlar.
 "Ağır araç kullanımına gerek kalmadan, Alterra'nın yakıt hücresi amortismanında 4,2 kredi tasarruf sağladınız. Rica ederim."</t>
   </si>
   <si>
-    <t>Буровий інструмент – це промисловий інструмент, здатний видобувати мінеральні утворення, які інакше непроникні для стандартного спорядження для виживання.
+    <t>Буровий інструмент — це промисловий інструмент, здатний видобувати мінеральні утворення, які інакше непроникні для стандартного спорядження для виживання.
 Він дозволяє видобувати високопродуктивні ресурси без використання костюма для креветок.
 - Посилене промислове алмазне покриття дозволяє руйнувати молекулярні зв'язки великих мінеральних жил.
 - Мікродвигуни, спрямовані назад, запобігають відкиданню оператора назад опором бура.
 - Двигун зі змінним крутним моментом регулює швидкість обертання залежно від щільності матеріалу, щоб запобігти заклинюванню долота та віддачі від перелому зап'ястя.
-"Уникаючи необхідності використання важкого транспортного засобу, ви заощадили 4,2 кредити Alterra на амортизації паливних елементів. Будь ласка."</t>
+«Уникаючи необхідності використання важкого транспортного засобу, ви заощадили 4,2 кредити Alterra на амортизації паливних елементів. Будь ласка».</t>
   </si>
   <si>
     <t>Máy khoan là một thiết bị công nghiệp có khả năng khai thác các mỏ khoáng sản mà các thiết bị sinh tồn tiêu chuẩn không thể tiếp cận được.

--- a/translate.xlsx
+++ b/translate.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="391">
   <si>
     <t>Keycode</t>
   </si>
@@ -574,6 +574,9 @@
     <t>Hitinterval</t>
   </si>
   <si>
+    <t>Interval raken</t>
+  </si>
+  <si>
     <t>Tabamuse intervall</t>
   </si>
   <si>
@@ -670,12 +673,12 @@
 Utilitzeu el valor per defecte per coincidir amb la velocitat de mineria d'un braç perforador amb vestit de gambes.</t>
   </si>
   <si>
-    <t>资源矿藏的采集间隔。
+    <t>资源矿脉的采集间隔。
 间隔越小，采集速度越快。
 使用默认值以匹配虾式机甲钻臂的采矿速度。</t>
   </si>
   <si>
-    <t>資源礦藏的採集間隔。
+    <t>資源礦脈的採集間隔。
 間隔越小，採集速度越快。
 使用預設值以匹配蝦式機甲鑽臂的採礦速度。</t>
   </si>
@@ -1161,16 +1164,31 @@
     <t>Ency_DrillTool</t>
   </si>
   <si>
+    <t>Drill Tool</t>
+  </si>
+  <si>
     <t>Инструмент за пробиване</t>
   </si>
   <si>
     <t>Bohrwerkzeug</t>
   </si>
   <si>
+    <t>Uirlis Druileála</t>
+  </si>
+  <si>
+    <t>Utensile da trapano</t>
+  </si>
+  <si>
+    <t>Urbšanas rīks</t>
+  </si>
+  <si>
     <t>Сверло</t>
   </si>
   <si>
-    <t>Matkap aleti</t>
+    <t>Orodje za vrtanje</t>
+  </si>
+  <si>
+    <t>Matkap Aleti</t>
   </si>
   <si>
     <t>EncyDesc_DrillTool</t>
@@ -1241,10 +1259,10 @@
   </si>
   <si>
     <t>Boreværktøjet er et industrielt instrument, der er i stand til at udvinde mineralformationer, der ellers er uigennemtrængelige for standard overlevelsesudstyr.
-Det muliggør høst af ressourcer med højt udbytte uden brug af en rejedragt.
+Det muliggør høst af ressourcer med højt udbytte uden brug af rejedragt.
 - Forstærket industriel diamantbelægning muliggør brud på de molekylære bindinger i store mineralårer.
 - Bagudvendte mikro-thrustere forhindrer, at operatøren drives bagud af borets modstand.
-- Motor med variabelt moment justerer omdrejningstallet baseret på materialedensitet for at forhindre borehovedbinding og tilbageslag fra håndledsbrud.
+- Motor med variabelt moment justerer omdrejningstallet baseret på materialedensitet for at forhindre fastklemning af boret og tilbageslag fra håndledsbrud.
 "Ved at omgå behovet for tunge køretøjer har du sparet Alterra 4,2 point i afskrivning af brændstofceller. Velbekomme."</t>
   </si>
   <si>
@@ -1322,7 +1340,7 @@
   <si>
     <t>このドリルツールは、通常のサバイバル装備では掘削不可能な鉱物層を採掘できる産業用機器です。
 これにより、プラウンスーツを装備することなく、高収量の資源採掘が可能になります。
-- 強化された工業用ダイヤモンドコーティングにより、大型鉱脈の分子結合を破壊します。
+- 強化された工業用ダイヤモンドコーティングにより、大きな鉱脈の分子結合を破壊します。
 - 後方に取り付けられたマイクロスラスタにより、ドリルの抵抗によってオペレーターが後方に押し戻されるのを防ぎます。
 - 可変トルクモーターは、材料の密度に応じて回転数を調整し、ビットの詰まりや手首の骨折につながるキックバックを防ぎます。
 「大型車両の展開が不要になったことで、燃料電池の減価償却費をアルテラ4.2クレジット節約できました。どういたしまして。」</t>
@@ -1348,8 +1366,8 @@
 Jis leidžia išgauti didelį išteklių derlių nenaudojant krevečių kostiumo.
 - Sustiprinta pramoninė deimantinė danga leidžia suardyti didelių mineralinių gyslų molekulinius ryšius.
 - Galiniai mikrovarikliai neleidžia operatoriui būti stumtam atgal dėl grąžto pasipriešinimo.
-- Kintamo sukimo momento variklis reguliuoja apsukas pagal medžiagos tankį, kad būtų išvengta grąžto strigimo ir riešo lūžio atatrankos.
-„Aplenkdami poreikį naudoti sunkiasvores transporto priemones, sutaupėte 4,2 „Alterra“ kreditų už kuro elementų nusidėvėjimą. Prašom.“</t>
+- Kintamo sukimo momento variklis reguliuoja apsukas pagal medžiagos tankį, kad būtų išvengta grąžto užstrigimo ir riešo lūžio atatrankos.
+„Aplenkdami poreikį naudoti sunkias transporto priemones, sutaupėte 4,2 „Alterra“ kreditų už kuro elementų nusidėvėjimą. Prašom.“</t>
   </si>
   <si>
     <t>Boreverktøyet er et industrielt instrument som er i stand til å utvinne mineralformasjoner som ellers er ugjennomtrengelige med standard overlevelsesutstyr.
@@ -2633,587 +2651,587 @@
         <v>164</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S5" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X5" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y5" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z5" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA5" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AB5" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AC5" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AD5" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE5" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AF5" s="14" t="s">
         <v>163</v>
       </c>
       <c r="AG5" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AH5" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AI5" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL5" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AM5" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN5" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z6" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC6" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD6" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AF6" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG6" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AH6" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AI6" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AJ6" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AK6" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL6" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM6" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN6" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="R7" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="S7" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="W7" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="X7" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y7" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z7" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA7" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AB7" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AC7" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AD7" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AE7" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AF7" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG7" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH7" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AI7" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AJ7" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AK7" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL7" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM7" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN7" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y8" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z8" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA8" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AC8" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AD8" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AE8" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AF8" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AH8" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AI8" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AJ8" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AK8" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL8" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM8" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN8" s="17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R9" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="S9" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="U9" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="V9" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="W9" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X9" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y9" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z9" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA9" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AB9" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AD9" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AE9" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AF9" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG9" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AH9" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AI9" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AJ9" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AK9" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL9" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM9" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN9" s="16" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>40</v>
@@ -3270,7 +3288,7 @@
         <v>40</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="U10" s="8" t="s">
         <v>40</v>
@@ -3335,246 +3353,246 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>229</v>
+        <v>345</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="R11" s="14" t="s">
-        <v>245</v>
+        <v>348</v>
       </c>
       <c r="S11" s="14" t="s">
-        <v>246</v>
+        <v>349</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="U11" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V11" s="14" t="s">
-        <v>249</v>
+        <v>350</v>
       </c>
       <c r="W11" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="X11" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y11" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z11" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA11" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AB11" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AD11" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AE11" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AF11" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG11" s="14" t="s">
-        <v>258</v>
+        <v>352</v>
       </c>
       <c r="AH11" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AI11" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AJ11" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AK11" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL11" s="14" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="AM11" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN11" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="M12" s="21" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="N12" s="21" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="P12" s="21" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="Q12" s="21" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="R12" s="21" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="S12" s="21" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="T12" s="21" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="U12" s="21" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="V12" s="21" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="W12" s="21" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="X12" s="21" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="Y12" s="21" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="Z12" s="21" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="AA12" s="21" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="AB12" s="21" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="AC12" s="21" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="AD12" s="21" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="AE12" s="21" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="AF12" s="21" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="AG12" s="21" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="AH12" s="21" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="AI12" s="21" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="AJ12" s="21" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="AK12" s="21" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="AL12" s="21" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="AM12" s="21" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="AN12" s="22" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13">

--- a/translate.xlsx
+++ b/translate.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="390">
   <si>
     <t>Keycode</t>
   </si>
@@ -574,9 +574,6 @@
     <t>Hitinterval</t>
   </si>
   <si>
-    <t>Interval raken</t>
-  </si>
-  <si>
     <t>Tabamuse intervall</t>
   </si>
   <si>
@@ -673,12 +670,12 @@
 Utilitzeu el valor per defecte per coincidir amb la velocitat de mineria d'un braç perforador amb vestit de gambes.</t>
   </si>
   <si>
-    <t>资源矿脉的采集间隔。
+    <t>资源矿藏的采集间隔。
 间隔越小，采集速度越快。
 使用默认值以匹配虾式机甲钻臂的采矿速度。</t>
   </si>
   <si>
-    <t>資源礦脈的採集間隔。
+    <t>資源礦藏的採集間隔。
 間隔越小，採集速度越快。
 使用預設值以匹配蝦式機甲鑽臂的採礦速度。</t>
   </si>
@@ -909,573 +906,537 @@
     <t>Vrtalno orodje</t>
   </si>
   <si>
+    <t>Herramienta de perforación</t>
+  </si>
+  <si>
+    <t>Taladro de mano</t>
+  </si>
+  <si>
+    <t>Borrverktyg</t>
+  </si>
+  <si>
+    <t>เครื่องมือเจาะ</t>
+  </si>
+  <si>
+    <t>El Matkabı</t>
+  </si>
+  <si>
+    <t>Свердлильний інструмент</t>
+  </si>
+  <si>
+    <t>Dụng cụ khoan</t>
+  </si>
+  <si>
+    <t>Tooltip_DrillTool</t>
+  </si>
+  <si>
+    <t>Handheld mining apparatus for large deposits.</t>
+  </si>
+  <si>
+    <t>Handmynapparaat vir groot neerslae.</t>
+  </si>
+  <si>
+    <t>Преносим инструмент за добив, предназначен за извличане на големи находища ресурси.</t>
+  </si>
+  <si>
+    <t>Aparell de mineria manual per a grans jaciments.</t>
+  </si>
+  <si>
+    <t>用于大型矿藏的手持式采矿设备。</t>
+  </si>
+  <si>
+    <t>用於大型礦藏的手持式採礦設備。</t>
+  </si>
+  <si>
+    <t>Ručni rudarski aparat za velika nalazišta.</t>
+  </si>
+  <si>
+    <t>Ruční těžební zařízení pro velká ložiska.</t>
+  </si>
+  <si>
+    <t>Håndholdt minedriftsapparat til store forekomster.</t>
+  </si>
+  <si>
+    <t>Draagbare mijnbouwapparatuur voor grote afzettingen.</t>
+  </si>
+  <si>
+    <t>Käeshoitav kaevandusaparaat suurte leiukohtade jaoks.</t>
+  </si>
+  <si>
+    <t>Kädessä pidettävä kaivoslaite suurille esiintymille.</t>
+  </si>
+  <si>
+    <t>Appareil minier portatif pour les gisements importants.</t>
+  </si>
+  <si>
+    <t>Tragbares Bohrgerät zum Abbauen großer Rohstoffvorkommen.</t>
+  </si>
+  <si>
+    <t>Φορητή συσκευή εξόρυξης για μεγάλα κοιτάσματα.</t>
+  </si>
+  <si>
+    <t>Kézi bányászati ​​készülék nagy lelőhelyekhez.</t>
+  </si>
+  <si>
+    <t>Fearas mianadóireachta láimhe le haghaidh taiscí móra.</t>
+  </si>
+  <si>
+    <t>Apparecchiature minerarie portatili per grandi giacimenti.</t>
+  </si>
+  <si>
+    <t>大規模鉱床向けの携帯型採掘装置。</t>
+  </si>
+  <si>
+    <t>대규모 광맥 채굴용 휴대용 채굴 장비.</t>
+  </si>
+  <si>
+    <t>Rokas ieguves aparāts lieliem atradnēm.</t>
+  </si>
+  <si>
+    <t>Rankinis kasybos aparatas dideliems telkiniams.</t>
+  </si>
+  <si>
+    <t>Håndholdt gruvedriftsapparat for store forekomster.</t>
+  </si>
+  <si>
+    <t>Przenośny sprzęt górniczy do wydobywania dużych złóż.</t>
+  </si>
+  <si>
+    <t>Equipamento de mineração portátil para grandes depósitos.</t>
+  </si>
+  <si>
+    <t>Aparat minier portabil pentru zăcăminte mari.</t>
+  </si>
+  <si>
+    <t>Переносной бур для добычи крупных залежей ресурсов.</t>
+  </si>
+  <si>
+    <t>Ручни апарат за рударење за велика налазишта.</t>
+  </si>
+  <si>
+    <t>Ručné ťažobné zariadenie pre veľké ložiská.</t>
+  </si>
+  <si>
+    <t>Ročna rudarska naprava za velika nahajališča.</t>
+  </si>
+  <si>
+    <t>Aparatos portátiles de minería para grandes yacimientos.</t>
+  </si>
+  <si>
+    <t>Herramienta portátil de minería para extraer grandes depósitos de recursos.</t>
+  </si>
+  <si>
+    <t>Handhållen gruvutrustning för stora fyndigheter.</t>
+  </si>
+  <si>
+    <t>อุปกรณ์ขุดเจาะแบบพกพาสำหรับแหล่งแร่ขนาดใหญ่</t>
+  </si>
+  <si>
+    <t>Büyük kaynak yataklarını kazmak için kullanılan taşınabilir madencilik matkabı.</t>
+  </si>
+  <si>
+    <t>Ручний гірничодобувний апарат для великих родовищ.</t>
+  </si>
+  <si>
+    <t>Thiết bị khai thác cầm tay dành cho các mỏ quặng lớn.</t>
+  </si>
+  <si>
+    <t>DrillToolFragment</t>
+  </si>
+  <si>
+    <t>Drill tool fragment</t>
+  </si>
+  <si>
+    <t>Boorgereedskapfragment</t>
+  </si>
+  <si>
+    <t>Фрагмент от инструмент за пробиване</t>
+  </si>
+  <si>
+    <t>Fragment d'eina de perforació</t>
+  </si>
+  <si>
+    <t>钻头碎片</t>
+  </si>
+  <si>
+    <t>鑽頭碎片</t>
+  </si>
+  <si>
+    <t>Fragment alata za bušenje</t>
+  </si>
+  <si>
+    <t>Fragment vrtacího nástroje</t>
+  </si>
+  <si>
+    <t>Boreværktøjsfragment</t>
+  </si>
+  <si>
+    <t>Boorgereedschapfragment</t>
+  </si>
+  <si>
+    <t>Puurimisriista fragment</t>
+  </si>
+  <si>
+    <t>Poraustyökalun fragmentti</t>
+  </si>
+  <si>
+    <t>fragment d'outil de forage</t>
+  </si>
+  <si>
+    <t>Bohrwerkzeugfragment</t>
+  </si>
+  <si>
+    <t>Θραύσμα εργαλείου τρυπανιού</t>
+  </si>
+  <si>
+    <t>Fúrószerszám töredék</t>
+  </si>
+  <si>
+    <t>Blúire uirlis druileála</t>
+  </si>
+  <si>
+    <t>Frammento di utensile da trapano</t>
+  </si>
+  <si>
+    <t>ドリル工具の破片</t>
+  </si>
+  <si>
+    <t>드릴 공구 파편</t>
+  </si>
+  <si>
+    <t>Urbšanas instrumenta fragments</t>
+  </si>
+  <si>
+    <t>Gręžimo įrankio fragmentas</t>
+  </si>
+  <si>
+    <t>Boreverktøyfragment</t>
+  </si>
+  <si>
+    <t>Fragment narzędzia wiertniczego</t>
+  </si>
+  <si>
+    <t>Fragmento de ferramenta de perfuração</t>
+  </si>
+  <si>
+    <t>Fragment de instrument de găurit</t>
+  </si>
+  <si>
+    <t>Фрагмент сверлильного инструмента</t>
+  </si>
+  <si>
+    <t>Фрагмент алата за бушење</t>
+  </si>
+  <si>
+    <t>Fragment vŕtacieho nástroja</t>
+  </si>
+  <si>
+    <t>Fragment vrtalnega orodja</t>
+  </si>
+  <si>
+    <t>Fragmento de herramienta de perforación</t>
+  </si>
+  <si>
+    <t>Borrverktygsfragment</t>
+  </si>
+  <si>
+    <t>เศษชิ้นส่วนเครื่องมือเจาะ</t>
+  </si>
+  <si>
+    <t>Matkap aleti parçası</t>
+  </si>
+  <si>
+    <t>Фрагмент бурового інструменту</t>
+  </si>
+  <si>
+    <t>Mảnh dụng cụ khoan</t>
+  </si>
+  <si>
+    <t>Tooltip_DrillToolFragment</t>
+  </si>
+  <si>
+    <t>～</t>
+  </si>
+  <si>
+    <t>Ency_DrillTool</t>
+  </si>
+  <si>
+    <t>Drill Tool</t>
+  </si>
+  <si>
+    <t>Инструмент за пробиване</t>
+  </si>
+  <si>
+    <t>Bohrwerkzeug</t>
+  </si>
+  <si>
+    <t>Uirlis Druileála</t>
+  </si>
+  <si>
+    <t>Utensile da trapano</t>
+  </si>
+  <si>
+    <t>Urbšanas rīks</t>
+  </si>
+  <si>
+    <t>Сверло</t>
+  </si>
+  <si>
     <t>Taladro</t>
   </si>
   <si>
-    <t>Taladro de mano</t>
-  </si>
-  <si>
-    <t>Borrverktyg</t>
-  </si>
-  <si>
-    <t>เครื่องมือเจาะ</t>
-  </si>
-  <si>
-    <t>El Matkabı</t>
-  </si>
-  <si>
-    <t>Свердлильний інструмент</t>
-  </si>
-  <si>
-    <t>Dụng cụ khoan</t>
-  </si>
-  <si>
-    <t>Tooltip_DrillTool</t>
-  </si>
-  <si>
-    <t>Handheld mining apparatus for large deposits.</t>
-  </si>
-  <si>
-    <t>Handmynapparaat vir groot neerslae.</t>
-  </si>
-  <si>
-    <t>Преносим инструмент за добив, предназначен за извличане на големи находища ресурси.</t>
-  </si>
-  <si>
-    <t>Aparell de mineria manual per a grans jaciments.</t>
-  </si>
-  <si>
-    <t>用于大型矿藏的手持式采矿设备。</t>
-  </si>
-  <si>
-    <t>用於大型礦藏的手持式採礦設備。</t>
-  </si>
-  <si>
-    <t>Ručni rudarski aparat za velika nalazišta.</t>
-  </si>
-  <si>
-    <t>Ruční těžební zařízení pro velká ložiska.</t>
-  </si>
-  <si>
-    <t>Håndholdt minedriftsapparat til store forekomster.</t>
-  </si>
-  <si>
-    <t>Draagbare mijnbouwapparatuur voor grote afzettingen.</t>
-  </si>
-  <si>
-    <t>Käeshoitav kaevandusaparaat suurte leiukohtade jaoks.</t>
-  </si>
-  <si>
-    <t>Kädessä pidettävä kaivoslaite suurille esiintymille.</t>
-  </si>
-  <si>
-    <t>Appareil minier portatif pour les gisements importants.</t>
-  </si>
-  <si>
-    <t>Tragbares Bohrgerät zum Abbauen großer Rohstoffvorkommen.</t>
-  </si>
-  <si>
-    <t>Φορητή συσκευή εξόρυξης για μεγάλα κοιτάσματα.</t>
-  </si>
-  <si>
-    <t>Kézi bányászati ​​készülék nagy lelőhelyekhez.</t>
-  </si>
-  <si>
-    <t>Fearas mianadóireachta láimhe le haghaidh taiscí móra.</t>
-  </si>
-  <si>
-    <t>Apparecchiature minerarie portatili per grandi giacimenti.</t>
-  </si>
-  <si>
-    <t>大規模鉱床向けの携帯型採掘装置。</t>
-  </si>
-  <si>
-    <t>대규모 광맥 채굴용 휴대용 채굴 장비.</t>
-  </si>
-  <si>
-    <t>Rokas ieguves aparāts lieliem atradnēm.</t>
-  </si>
-  <si>
-    <t>Rankinis kasybos aparatas dideliems telkiniams.</t>
-  </si>
-  <si>
-    <t>Håndholdt gruvedriftsapparat for store forekomster.</t>
-  </si>
-  <si>
-    <t>Przenośny sprzęt górniczy do wydobywania dużych złóż.</t>
-  </si>
-  <si>
-    <t>Equipamento de mineração portátil para grandes depósitos.</t>
-  </si>
-  <si>
-    <t>Aparat minier portabil pentru zăcăminte mari.</t>
-  </si>
-  <si>
-    <t>Переносной бур для добычи крупных залежей ресурсов.</t>
-  </si>
-  <si>
-    <t>Ручни апарат за рударење за велика налазишта.</t>
-  </si>
-  <si>
-    <t>Ručné ťažobné zariadenie pre veľké ložiská.</t>
-  </si>
-  <si>
-    <t>Ročna rudarska naprava za velika nahajališča.</t>
-  </si>
-  <si>
-    <t>Aparatos portátiles de minería para grandes yacimientos.</t>
-  </si>
-  <si>
-    <t>Herramienta portátil de minería para extraer grandes depósitos de recursos.</t>
-  </si>
-  <si>
-    <t>Handhållen gruvutrustning för stora fyndigheter.</t>
-  </si>
-  <si>
-    <t>อุปกรณ์ขุดเจาะแบบพกพาสำหรับแหล่งแร่ขนาดใหญ่</t>
-  </si>
-  <si>
-    <t>Büyük kaynak yataklarını kazmak için kullanılan taşınabilir madencilik matkabı.</t>
-  </si>
-  <si>
-    <t>Ручний гірничодобувний апарат для великих родовищ.</t>
-  </si>
-  <si>
-    <t>Thiết bị khai thác cầm tay dành cho các mỏ quặng lớn.</t>
-  </si>
-  <si>
-    <t>DrillToolFragment</t>
-  </si>
-  <si>
-    <t>Drill tool fragment</t>
-  </si>
-  <si>
-    <t>Boorgereedskapfragment</t>
-  </si>
-  <si>
-    <t>Фрагмент от инструмент за пробиване</t>
-  </si>
-  <si>
-    <t>Fragment d'eina de perforació</t>
-  </si>
-  <si>
-    <t>钻头碎片</t>
-  </si>
-  <si>
-    <t>鑽頭碎片</t>
-  </si>
-  <si>
-    <t>Fragment alata za bušenje</t>
-  </si>
-  <si>
-    <t>Fragment vrtacího nástroje</t>
-  </si>
-  <si>
-    <t>Boreværktøjsfragment</t>
-  </si>
-  <si>
-    <t>Boorgereedschapfragment</t>
-  </si>
-  <si>
-    <t>Puurimisriista fragment</t>
-  </si>
-  <si>
-    <t>Poraustyökalun fragmentti</t>
-  </si>
-  <si>
-    <t>fragment d'outil de forage</t>
-  </si>
-  <si>
-    <t>Bohrwerkzeugfragment</t>
-  </si>
-  <si>
-    <t>Θραύσμα εργαλείου τρυπανιού</t>
-  </si>
-  <si>
-    <t>Fúrószerszám töredék</t>
-  </si>
-  <si>
-    <t>Blúire uirlis druileála</t>
-  </si>
-  <si>
-    <t>Frammento di utensile da trapano</t>
-  </si>
-  <si>
-    <t>ドリル工具の破片</t>
-  </si>
-  <si>
-    <t>드릴 공구 파편</t>
-  </si>
-  <si>
-    <t>Urbšanas instrumenta fragments</t>
-  </si>
-  <si>
-    <t>Gręžimo įrankio fragmentas</t>
-  </si>
-  <si>
-    <t>Boreverktøyfragment</t>
-  </si>
-  <si>
-    <t>Fragment narzędzia wiertniczego</t>
-  </si>
-  <si>
-    <t>Fragmento de ferramenta de perfuração</t>
-  </si>
-  <si>
-    <t>Fragment de instrument de găurit</t>
-  </si>
-  <si>
-    <t>Фрагмент сверлильного инструмента</t>
-  </si>
-  <si>
-    <t>Фрагмент алата за бушење</t>
-  </si>
-  <si>
-    <t>Fragment vŕtacieho nástroja</t>
-  </si>
-  <si>
-    <t>Fragment vrtalnega orodja</t>
-  </si>
-  <si>
-    <t>Fragmento de herramienta de perforación</t>
-  </si>
-  <si>
-    <t>Borrverktygsfragment</t>
-  </si>
-  <si>
-    <t>เศษชิ้นส่วนเครื่องมือเจาะ</t>
-  </si>
-  <si>
-    <t>Matkap aleti parçası</t>
-  </si>
-  <si>
-    <t>Фрагмент бурового інструменту</t>
-  </si>
-  <si>
-    <t>Mảnh dụng cụ khoan</t>
-  </si>
-  <si>
-    <t>Tooltip_DrillToolFragment</t>
-  </si>
-  <si>
-    <t>～</t>
-  </si>
-  <si>
-    <t>Ency_DrillTool</t>
-  </si>
-  <si>
-    <t>Drill Tool</t>
-  </si>
-  <si>
-    <t>Инструмент за пробиване</t>
-  </si>
-  <si>
-    <t>Bohrwerkzeug</t>
-  </si>
-  <si>
-    <t>Uirlis Druileála</t>
-  </si>
-  <si>
-    <t>Utensile da trapano</t>
-  </si>
-  <si>
-    <t>Urbšanas rīks</t>
-  </si>
-  <si>
-    <t>Сверло</t>
-  </si>
-  <si>
-    <t>Orodje za vrtanje</t>
-  </si>
-  <si>
     <t>Matkap Aleti</t>
   </si>
   <si>
     <t>EncyDesc_DrillTool</t>
   </si>
   <si>
-    <t>The drill tool is an industrial instrument capable of extracting mineral formations that are otherwise impenetrable by standard survival equipment.
-It allows for high-yield resource harvesting without the deployment of a Prawn Suit.
+    <t>The drill tool is an industrial instrument capable of extracting mineral formations that are otherwise impenetrable by standard survival equipment, without the deployment of a Prawn Suit.
 - Reinforced industrial diamond coating enables fracturing the molecular bonds of large mineral veins
 - Rear-facing micro-thrusters prevent the operator from being propelled backward by the drill's resistance
 - Variable torque motor adjusts RPM based on material density to prevent bit binding and wrist-fracture kickback
 "By bypassing the need for heavy vehicular deployment, you have saved Alterra 4.2 credits in fuel cell depreciation. You're welcome."</t>
   </si>
   <si>
-    <t>Die boorgereedskap is 'n industriële instrument wat in staat is om mineraalformasies te onttrek wat andersins ondeurdringbaar is deur standaard oorlewingstoerusting.
-Dit maak voorsiening vir hoë-opbrengs hulpbron-oes sonder die ontplooiing van 'n Garnalepak.
+    <t>Die boorgereedskap is 'n industriële instrument wat in staat is om mineraalformasies te onttrek wat andersins ondeurdringbaar is deur standaard oorlewingstoerusting, sonder die ontplooiing van 'n Garnalepak.
 - Versterkte industriële diamantlaag maak dit moontlik om die molekulêre bindings van groot mineraalare te breek.
 - Agtertoe gerigte mikro-stuwers verhoed dat die operateur deur die boor se weerstand agtertoe gedryf word.
-- Veranderlike wringkragmotor pas RPM aan gebaseer op materiaaldigtheid om boorpuntbinding en polsfraktuurterugslag te voorkom.
+- Veranderlike wringkragmotor pas die RPM aan gebaseer op materiaaldigtheid om boorpuntbinding en terugslag van polsfrakture te voorkom.
 "Deur die behoefte aan swaar voertuigontplooiing te omseil, het u Alterra 4.2 krediete in brandstofseldepresiasie bespaar. Jy's welkom."</t>
   </si>
   <si>
-    <t>Сондажният инструмент е индустриален инструмент, способен да извлича минерални образувания, които иначе са непроницаеми за стандартно оборудване за оцеляване.
-Той позволява добив на ресурси с висок добив без използване на костюм за скариди.
+    <t>Пробивният инструмент е индустриален инструмент, способен да извлича минерални образувания, които иначе са непроницаеми за стандартно оборудване за оцеляване, без използването на костюм за скариди.
 - Подсиленото индустриално диамантено покритие позволява разрушаване на молекулярните връзки на големи минерални жили.
-- Насочените назад микротласкащи двигатели предотвратяват изтласкването на оператора назад от съпротивлението на сондажа.
+- Насочените назад микротласкащи механизми предотвратяват изтласкването на оператора назад от съпротивлението на сондажа.
 - Моторът с променлив въртящ момент регулира оборотите въз основа на плътността на материала, за да предотврати заклинване на свредлото и откат от счупване на китката.
-„Като заобиколите необходимостта от разполагане на тежки превозни средства, вие спестихте 4,2 кредита от Alterra за амортизация на горивни клетки. Няма защо.“</t>
-  </si>
-  <si>
-    <t>L'eina de perforació és un instrument industrial capaç d'extreure formacions minerals que d'altra banda serien impenetrables per a equips de supervivència estàndard.
-Permet la recobriment de recursos d'alt rendiment sense el desplegament d'un vestit de gamba.
-- El recobriment de diamant industrial reforçat permet fracturar els enllaços moleculars de grans venes minerals.
-- Els micropropulsors orientats cap enrere eviten que l'operador sigui impulsat cap enrere per la resistència de la perforadora.
-- El motor de parell variable ajusta les RPM en funció de la densitat del material per evitar que la broca s'enganxi i el rebot que es produeixi per fracturar el canell.
+„Като заобиколите необходимостта от разполагане на тежки превозни средства, вие спестихте 4,2 кредита на Alterra за амортизация на горивни клетки. Няма защо.“</t>
+  </si>
+  <si>
+    <t>L'eina de perforació és un instrument industrial capaç d'extreure formacions minerals que d'altra banda serien impenetrables per l'equip de supervivència estàndard, sense el desplegament d'un vestit de gamba.
+- El recobriment de diamant industrial reforçat permet fracturar els enllaços moleculars de grans venes minerals
+- Els micropropulsors orientats cap enrere eviten que l'operador sigui impulsat cap enrere per la resistència de la perforadora
+- El motor de parell variable ajusta les RPM en funció de la densitat del material per evitar que la broca s'enganxi i el retrocés per fractura del canell
 "En evitar la necessitat de desplegament de vehicles pesats, heu estalviat a Alterra 4,2 crèdits en la depreciació de les piles de combustible. De res."</t>
   </si>
   <si>
-    <t>这款钻机是一种工业级工具，能够开采标准生存装备无法穿透的矿层。
-它无需部署虾式机甲即可实现高产资源采集。
+    <t>这款钻探工具是一种工业级仪器，无需使用虾式机甲，即可开采标准生存装备无法穿透的矿层。
 - 强化型工业金刚石涂层能够破坏大型矿脉的分子键
-- 后置微型推进器可防止操作员因钻机阻力而被向后推
+- 后置微型推进器可防止操作员因钻头阻力而被向后推
 - 可变扭矩电机可根据材料密度调节转速，防止钻头卡死和手腕反冲
 “由于无需部署重型载具，您节省了 Alterra 4.2 点燃料电池折旧费用。不用谢。”</t>
   </si>
   <si>
-    <t>這款鑽孔機是一種工業級工具，能夠開採標準生存裝備無法穿透的礦層。
-它無需部署蝦式機甲即可實現高產量資源採集。
+    <t>這款鑽探工具是一種工業級儀器，無需使用蝦式機甲，即可開採標準生存裝備無法穿透的礦層。
 - 強化型工業用鑽石塗層能夠破壞大型礦脈的分子鍵
-- 後置微型推進器可防止操作員因鑽機阻力而被向後推
+- 後置微型推進器可防止操作員因鑽頭阻力而被向後推
 - 可變扭矩馬達可根據材料密度調節轉速，防止鑽頭卡死和手腕反轉
 “由於無需部署重型載具，您節省了 Alterra 4.2 點燃料電池折舊費用。不用謝。”</t>
   </si>
   <si>
-    <t>Alat za bušenje je industrijski instrument sposoban za vađenje mineralnih formacija koje su inače neprobojne standardnom opremom za preživljavanje.
-Omogućuje visokoprinosno iskorištavanje resursa bez upotrebe odijela za kozice.
+    <t>Alat za bušenje je industrijski instrument sposoban za vađenje mineralnih formacija koje su inače neprobojne standardnom opremom za preživljavanje, bez upotrebe odijela za kozice.
 - Ojačani industrijski dijamantni premaz omogućuje razbijanje molekularnih veza velikih mineralnih žila
 - Mikro-potisnici okrenuti prema natrag sprječavaju da se operater pomiče unatrag otporom bušilice
 - Motor s promjenjivim momentom prilagođava broj okretaja na temelju gustoće materijala kako bi se spriječilo blokiranje svrdla i povratni udarac od loma ručnog zgloba
 "Zaobilaženjem potrebe za korištenjem teških vozila, uštedjeli ste Alterra 4,2 kredita u amortizaciji gorivnih ćelija. Nema na čemu."</t>
   </si>
   <si>
-    <t>Vrtací nástroj je průmyslový nástroj schopný těžit minerální formace, které jsou jinak pro standardní vybavení pro přežití neproniknutelné.
-Umožňuje těžbu zdrojů s vysokým výtěžkem bez použití obleku Prawn Suit.
+    <t>Vrtací nástroj je průmyslový nástroj schopný těžit minerální formace, které jsou jinak pro standardní vybavení pro přežití neproniknutelné, a to bez použití obleku Prawn Suit.
 - Zesílený průmyslový diamantový povlak umožňuje rozrušit molekulární vazby velkých minerálních žil.
 - Mikromotory směřující dozadu zabraňují tomu, aby byl obsluha hnána dozadu odporem vrtáku.
-- Motor s proměnným točivým momentem upravuje otáčky na základě hustoty materiálu, aby se zabránilo zaseknutí vrtáku a zpětnému rázu způsobenému zlomeninou zápěstí.
+- Motor s proměnným točivým momentem upravuje otáčky na základě hustoty materiálu, aby se zabránilo zaseknutí vrtáku a zpětnému rázu způsobujícímu zlomeninu zápěstí.
 „Tím, že jste se vyhnuli nutnosti nasazení těžkých vozidel, jste ušetřili 4,2 kreditu Alterra na odpisech palivových článků. Není zač.“</t>
   </si>
   <si>
-    <t>Boreværktøjet er et industrielt instrument, der er i stand til at udvinde mineralformationer, der ellers er uigennemtrængelige for standard overlevelsesudstyr.
-Det muliggør høst af ressourcer med højt udbytte uden brug af rejedragt.
-- Forstærket industriel diamantbelægning muliggør brud på de molekylære bindinger i store mineralårer.
-- Bagudvendte mikro-thrustere forhindrer, at operatøren drives bagud af borets modstand.
-- Motor med variabelt moment justerer omdrejningstallet baseret på materialedensitet for at forhindre fastklemning af boret og tilbageslag fra håndledsbrud.
+    <t>Boreværktøjet er et industrielt instrument, der er i stand til at udvinde mineralformationer, der ellers er uigennemtrængelige for standard overlevelsesudstyr, uden brug af en rejedragt.
+- Forstærket industriel diamantbelægning muliggør brud på de molekylære bindinger i store mineralårer
+- Bagudvendte mikro-thrustere forhindrer, at operatøren bliver drevet bagud af borets modstand
+- Motor med variabelt moment justerer omdrejningstallet baseret på materialedensitet for at forhindre borehovedbinding og tilbageslag fra håndledsbrud
 "Ved at omgå behovet for tunge køretøjer har du sparet Alterra 4,2 point i afskrivning af brændstofceller. Velbekomme."</t>
   </si>
   <si>
-    <t>De boor is een industrieel instrument dat in staat is om minerale formaties te winnen die anders ondoordringbaar zijn voor standaard overlevingsuitrusting.
-Het maakt een hoge opbrengst aan grondstoffenwinning mogelijk zonder de inzet van een Prawn Suit.
+    <t>De boor is een industrieel instrument dat in staat is om minerale formaties te winnen die anders ondoordringbaar zijn voor standaard overlevingsuitrusting, zonder dat een Prawn Suit nodig is.
 - Versterkte industriële diamantcoating maakt het mogelijk om de moleculaire bindingen van grote minerale aderen te verbreken.
 - Naar achteren gerichte micro-stuwraketten voorkomen dat de operator door de weerstand van de boor naar achteren wordt geduwd.
-- De motor met variabel koppel past het toerental aan op basis van de materiaaldichtheid om vastlopen van de boor en terugslag die tot polsfracturen kan leiden te voorkomen.
-"Door de noodzaak van zwaar transport te omzeilen, heeft u Alterra 4,2 credits bespaard op de afschrijving van brandstofcellen. Graag gedaan."</t>
-  </si>
-  <si>
-    <t>See puurmasin on tööstuslik instrument, mis on võimeline kaevandama mineraalkihte, mis muidu oleksid tavalise ellujäämisvarustusega läbimatud.
-See võimaldab suure saagikusega ressursse koguda ilma krevetiülikonnata.
-- Tugevdatud tööstuslik teemantkate võimaldab purustada suurte mineraalisoonte molekulaarsidemeid.
+- Variabele koppelmotor past het toerental aan op basis van de materiaaldichtheid om vastlopen van de boor en terugslag die tot polsfracturen kan leiden te voorkomen.
+"Door de noodzaak van zwaar transport te omzeilen, heeft u Alterra 4,2 credits bespaard op de afschrijving van de brandstofcel. Graag gedaan."</t>
+  </si>
+  <si>
+    <t>See puurmasin on tööstuslik instrument, mis on võimeline kaevandama mineraalkihte, mis muidu oleksid tavalise ellujäämisvarustusega läbimatud, ilma krevetiülikonnata.
+- Tugevdatud tööstuslik teemantkate võimaldab purustada suurte mineraalisoonte molekulaarseid sidemeid.
 - Tahapoole suunatud mikromootorid takistavad operaatori tagasilööki puuri takistuse tõttu.
-- Muutuva pöördemomendiga mootor reguleerib pöörlemiskiirust materjali tiheduse põhjal, et vältida puuri kinnikiilumist ja randmemurru tagasilööki.
+- Muutuva pöördemomendiga mootor reguleerib pöörlemiskiirust vastavalt materjali tihedusele, et vältida puuri kinnikiilumist ja randmemurru tagasilööki.
 "Raskete sõidukite kasutamise vajaduse vältimisega olete säästnud Alterrale 4,2 krediiti kütuseelementide amortisatsiooni pealt. Pole tänu väärt."</t>
   </si>
   <si>
-    <t>Poraustyökalu on teollisuuslaite, jolla voidaan louhia mineraalimuodostelmia, jotka muuten olisivat läpäisemättömiä tavallisilla selviytymisvarusteilla.
-Se mahdollistaa suuren saannon luonnonvarojen keräämisen ilman katkarapuvun käyttöä.
+    <t>Poraustyökalu on teollisuuslaite, jolla voidaan irrottaa mineraalimuodostelmia, jotka muuten olisivat läpäisemättömiä tavallisilla selviytymisvarusteilla, ilman katkarapuvun käyttöä.
 - Vahvistettu teollinen timanttipinnoite mahdollistaa suurten mineraalijuonien molekyylisidosten murtamisen.
 - Taaksepäin suunnatut mikrotyöntövoimalaitteet estävät käyttäjää lennähtämästä taaksepäin poran vastuksen vaikutuksesta.
 - Muuttuvan vääntömomentin moottori säätää kierroslukua materiaalin tiheyden perusteella estääkseen terän juuttumisen ja ranteen murtuman aiheuttaman takapotkun.
-"Ohittamalla raskaiden ajoneuvojen käytön tarpeen olet säästänyt Alterralta 4,2 krediittiä polttokennojen poistoissa. Ole hyvä."</t>
-  </si>
-  <si>
-    <t>L'outil de forage est un instrument industriel capable d'extraire des formations minérales inaccessibles aux équipements de survie classiques.
-Il permet une exploitation à haut rendement des ressources sans nécessiter de combinaison spéciale.
+"Ohittamalla raskaan ajoneuvoliikenteen tarpeen olet säästänyt Alterralta 4,2 krediittiä polttokennojen poistoissa. Ole hyvä."</t>
+  </si>
+  <si>
+    <t>L'outil de forage est un instrument industriel capable d'extraire des formations minérales inaccessibles aux équipements de survie classiques, sans nécessiter de combinaison spéciale.
 - Son revêtement diamant industriel renforcé permet de fracturer les liaisons moléculaires des grands filons minéraux.
 - Des micro-propulseurs arrière empêchent l'opérateur d'être repoussé par la résistance de la foreuse.
-- Son moteur à couple variable ajuste la vitesse de rotation en fonction de la densité du matériau afin d'éviter le blocage du trépan et les risques de blessure au poignet.
+- Son moteur à couple variable ajuste la vitesse de rotation en fonction de la densité du matériau afin d'éviter le blocage du foret et les risques de blessure au poignet.
 « En évitant le déploiement de véhicules lourds, vous avez permis à Alterra d'économiser 4,2 crédits en amortissement de la pile à combustible. De rien. »</t>
   </si>
   <si>
-    <t>Das Bohrwerkzeug ist ein Industriegerät, mit dem sich Mineralformationen abbauen lassen, die mit herkömmlicher Überlebensausrüstung nicht zugänglich sind.
-Es ermöglicht die Gewinnung ertragreicher Ressourcen ohne den Einsatz eines Prawn Suits.
-- Eine verstärkte Industriediamantbeschichtung ermöglicht das Aufbrechen der molekularen Bindungen großer Mineraladern.
-- Nach hinten gerichtete Mikro-Triebwerke verhindern, dass der Bediener durch den Widerstand des Bohrers nach hinten geschleudert wird.
-- Ein Motor mit variablem Drehmoment passt die Drehzahl an die Materialdichte an, um ein Festfressen des Bohrers und einen Rückschlag mit Verletzungsgefahr für das Handgelenk zu verhindern.
-„Durch den Verzicht auf schwere Fahrzeuge haben Sie Alterra 4.2 Credits für die Brennstoffzellenabschreibung eingespart. Gern geschehen.“</t>
-  </si>
-  <si>
-    <t>Το εργαλείο τρυπανιού είναι ένα βιομηχανικό όργανο ικανό να εξάγει ορυκτούς σχηματισμούς που διαφορετικά θα ήταν αδιαπέραστοι από τον τυπικό εξοπλισμό επιβίωσης.
-Επιτρέπει τη συγκομιδή πόρων υψηλής απόδοσης χωρίς την ανάπτυξη μιας στολής γαρίδας.
+    <t>Das Bohrwerkzeug ist ein Industriegerät, mit dem sich Mineralformationen abbauen lassen, die mit herkömmlicher Überlebensausrüstung nicht zugänglich sind – und das ohne den Einsatz eines Prawn Suits.
+– Eine verstärkte Industriediamantbeschichtung ermöglicht das Aufbrechen der molekularen Bindungen großer Mineraladern.
+– Nach hinten gerichtete Mikro-Düsen verhindern, dass der Bediener durch den Widerstand des Bohrers nach hinten geschleudert wird.
+– Ein Motor mit variablem Drehmoment passt die Drehzahl an die Materialdichte an, um ein Festfressen des Bohrers und einen Rückschlag mit Verletzungsgefahr für das Handgelenk zu verhindern.
+„Dadurch, dass kein schweres Fahrzeug benötigt wird, haben Sie Alterra 4.2 Credits für die Brennstoffzellenabschreibung eingespart. Gern geschehen.“</t>
+  </si>
+  <si>
+    <t>Το εργαλείο τρυπανιού είναι ένα βιομηχανικό όργανο ικανό να εξάγει ορυκτούς σχηματισμούς που διαφορετικά θα ήταν αδιαπέραστοι από τον τυπικό εξοπλισμό επιβίωσης, χωρίς την ανάπτυξη μιας στολής Prawn Suit.
 - Η ενισχυμένη βιομηχανική επίστρωση διαμαντιού επιτρέπει τη θραύση των μοριακών δεσμών μεγάλων ορυκτών φλεβών
 - Οι μικρο-προωθητήρες που είναι στραμμένοι προς τα πίσω εμποδίζουν τον χειριστή να ωθηθεί προς τα πίσω από την αντίσταση του τρυπανιού
 - Ο κινητήρας μεταβλητής ροπής ρυθμίζει τις στροφές ανά λεπτό με βάση την πυκνότητα του υλικού για να αποτρέψει το μπλοκάρισμα του τρυπανιού και το κλώτσημα από το κάταγμα του καρπού
 "Παρακάμπτοντας την ανάγκη για βαριά ανάπτυξη οχημάτων, έχετε εξοικονομήσει στην Alterra 4,2 μονάδες στην απόσβεση των κυψελών καυσίμου. Παρακαλώ."</t>
   </si>
   <si>
-    <t>A fúrószerszám egy ipari eszköz, amely képes olyan ásványi képződmények kinyerésére, amelyek egyébként áthatolhatatlanok lennének a hagyományos túlélőfelszerelésekkel.
-Lehetővé teszi a nagy hozamú erőforrás-kitermelést garnélarák-ruha használata nélkül.
+    <t>A fúrószerszám egy ipari eszköz, amely képes olyan ásványi képződmények kinyerésére, amelyek egyébként áthatolhatatlanok lennének a hagyományos túlélőfelszerelésekkel, anélkül, hogy garnélarák-ruhát kellene használni.
 - A megerősített ipari gyémántbevonat lehetővé teszi a nagy ásványi erek molekuláris kötéseinek feltörését.
 - A hátrafelé néző mikrohajtóművek megakadályozzák, hogy a kezelőt a fúró ellenállása hátrafelé repítse.
 - A változtatható nyomatékú motor az anyag sűrűsége alapján állítja be a fordulatszámot, hogy megakadályozza a fúrófej beszorulását és a csuklótörés visszarúgását.
 "A nehéz járművek használatának megkerülésével 4,2 kreditet takarított meg az Alterra üzemanyagcella-értékcsökkenésén. Szívesen."</t>
   </si>
   <si>
-    <t>Is uirlis thionsclaíoch í an uirlis druileála atá in ann foirmíochtaí mianraí a bhaint amach nach mbeadh trealaimh mharthanais chaighdeánacha in ann dul tríd murach sin.
-Ceadaíonn sé fómhar acmhainní ard-toraidh gan úsáid a bhaint as Culaith Cloicheán.
+    <t>Is uirlis thionsclaíoch í an uirlis druileála atá in ann foirmíochtaí mianraí a bhaint amach nach mbeadh trealaimh mharthanais chaighdeánacha in ann dul tríd murach sin, gan Culaith Cloicheán a imscaradh.
 - Cumasaíonn sciath diamant tionsclaíoch athneartaithe naisc mhóilíneacha féitheacha móra mianraí a bhriseadh
 - Coscann micrea-bhrúiteoirí atá os comhair an chúl an t-oibreoir ó bheith á thiomáint siar ag friotaíocht an druileála
-- Coigeartaíonn mótar chasmhóiminte athraitheach RPM bunaithe ar dhlús ábhair chun ceangal giotán agus cic siar briste caol na láimhe a chosc
-"Tríd an ngá atá le húsáid feithiclí troma a sheachaint, tá 4.2 creidiúint Alterra sábháilte agat i ndíluacháil cealla breosla. Tá fáilte romhat."</t>
-  </si>
-  <si>
-    <t>La trivella è uno strumento industriale in grado di estrarre formazioni minerarie altrimenti impenetrabili con le normali attrezzature di sopravvivenza.
-Consente un'estrazione di risorse ad alto rendimento senza la necessità di indossare una tuta Prawn.
-- Il rivestimento diamantato industriale rinforzato permette di fratturare i legami molecolari di grandi vene minerarie.
+- Coigeartaíonn mótar chasmhóiminte athraitheach RPM bunaithe ar dhlús an ábhair chun ceangal giotán agus cic siar briste caol na láimhe a chosc
+"Tríd an ngá atá le himscaradh feithiclí troma a sheachaint, tá 4.2 creidiúint Alterra sábháilte agat i ndíluacháil cealla breosla. Tá fáilte romhat."</t>
+  </si>
+  <si>
+    <t>La trivella è uno strumento industriale in grado di estrarre formazioni minerarie altrimenti impenetrabili con le normali attrezzature di sopravvivenza, senza la necessità di indossare una tuta Prawn.
+- Il rivestimento diamantato industriale rinforzato consente di fratturare i legami molecolari di grandi vene minerarie.
 - I micro-propulsori posteriori impediscono all'operatore di essere spinto all'indietro dalla resistenza della trivella.
 - Il motore a coppia variabile regola i giri al minuto in base alla densità del materiale per evitare l'inceppamento della punta e il contraccolpo che potrebbe causare fratture al polso.
 "Evitando l'impiego di veicoli pesanti, hai risparmiato 4,2 crediti Alterra in ammortamento delle celle a combustibile. Prego."</t>
   </si>
   <si>
-    <t>このドリルツールは、通常のサバイバル装備では掘削不可能な鉱物層を採掘できる産業用機器です。
-これにより、プラウンスーツを装備することなく、高収量の資源採掘が可能になります。
-- 強化された工業用ダイヤモンドコーティングにより、大きな鉱脈の分子結合を破壊します。
+    <t>この掘削ツールは、通常のサバイバル装備では掘削不可能な鉱物層を、プラウンスーツを使わずに採掘できる産業用機器です。
+- 強化された工業用ダイヤモンドコーティングにより、巨大な鉱脈の分子結合を破壊します。
 - 後方に取り付けられたマイクロスラスタにより、ドリルの抵抗によってオペレーターが後方に押し戻されるのを防ぎます。
 - 可変トルクモーターは、材料の密度に応じて回転数を調整し、ビットの詰まりや手首の骨折につながるキックバックを防ぎます。
-「大型車両の展開が不要になったことで、燃料電池の減価償却費をアルテラ4.2クレジット節約できました。どういたしまして。」</t>
-  </si>
-  <si>
-    <t>드릴 도구는 일반적인 생존 장비로는 접근할 수 없는 광물층을 채굴할 수 있는 산업용 장비입니다.
-프론 슈트(Prawn Suit)를 착용하지 않고도 높은 수확량의 자원을 채취할 수 있습니다.
+「大型車両による展開が不要になったことで、燃料電池の減価償却費をアルテラ4.2クレジット節約できました。どういたしまして。」</t>
+  </si>
+  <si>
+    <t>드릴 도구는 프론 슈트(Prawn Suit)를 착용하지 않고도 일반 생존 장비로는 접근할 수 없는 광물층을 채굴할 수 있는 산업용 장비입니다.
 - 강화된 산업용 다이아몬드 코팅으로 대형 광맥의 분자 결합을 파괴할 수 있습니다.
 - 후방 마이크로 추진기는 드릴의 저항으로 인해 작업자가 뒤로 밀리지 않도록 방지합니다.
-- 가변 토크 모터는 재료 밀도에 따라 회전수를 조절하여 드릴 비트 걸림과 손목 골절을 방지합니다.
-"중장비 차량 투입을 생략함으로써, 당신은 알테라의 연료 전지 감가상각비 4.2 크레딧을 절약했습니다. 천만에요."</t>
-  </si>
-  <si>
-    <t>Urbšanas instruments ir rūpniecisks instruments, kas spēj iegūt minerālu veidojumus, kurus citādi nevarētu caururbt ar standarta izdzīvošanas aprīkojumu.
-Tas ļauj iegūt augstas ražas resursus, neizmantojot garneļu kostīmu.
+- 가변 토크 모터는 광물 밀도에 따라 회전수를 조절하여 드릴 비트 걸림과 손목 골절을 방지합니다.
+"중장비 차량 투입이 필요 없어짐으로써, 알테라(Alterra)는 연료 전지 감가상각비로 4.2 크레딧을 절약했습니다. 천만에요."</t>
+  </si>
+  <si>
+    <t>Urbšanas instruments ir rūpniecisks instruments, kas spēj iegūt minerālu veidojumus, kurus citādi nevarētu caururbt ar standarta izdzīvošanas aprīkojumu, neizmantojot garneļu kostīmu.
 - Pastiprināts rūpnieciskais dimanta pārklājums ļauj pārraut lielu minerālu vēnu molekulārās saites.
-- Aizmugurē vērsti mikrodzinēji neļauj operatoram tikt atgrūstam atpakaļ urbja pretestības dēļ.
+- Aizmugurējie mikrodzinēji neļauj operatoram tikt atgrūstam atpakaļ urbja pretestības dēļ.
 - Mainīga griezes momenta motors pielāgo apgriezienus minūtē, pamatojoties uz materiāla blīvumu, lai novērstu urbja iesprūšanu un plaukstas locītavas lūzuma atsitienu.
-"Apejot nepieciešamību izmantot smagos transportlīdzekļus, jūs esat ietaupījis Alterra 4,2 kredītpunktus degvielas elementu nolietojumā. Nav par ko."</t>
-  </si>
-  <si>
-    <t>Gręžimo įrankis yra pramoninis instrumentas, galintis išgauti mineralinius darinius, į kuriuos kitaip neįsibrautų standartinė išgyvenimo įranga.
-Jis leidžia išgauti didelį išteklių derlių nenaudojant krevečių kostiumo.
+"Apejot nepieciešamību izmantot smagus transportlīdzekļus, jūs esat ietaupījis Alterra 4,2 kredītpunktus degvielas elementu nolietojumā. Nav par ko."</t>
+  </si>
+  <si>
+    <t>Gręžimo įrankis yra pramoninis instrumentas, galintis išgauti mineralinius darinius, kurių kitaip neįmanoma pasiekti standartine išgyvenimo įranga, nenaudojant krevečių kostiumo.
 - Sustiprinta pramoninė deimantinė danga leidžia suardyti didelių mineralinių gyslų molekulinius ryšius.
 - Galiniai mikrovarikliai neleidžia operatoriui būti stumtam atgal dėl grąžto pasipriešinimo.
-- Kintamo sukimo momento variklis reguliuoja apsukas pagal medžiagos tankį, kad būtų išvengta grąžto užstrigimo ir riešo lūžio atatrankos.
-„Aplenkdami poreikį naudoti sunkias transporto priemones, sutaupėte 4,2 „Alterra“ kreditų už kuro elementų nusidėvėjimą. Prašom.“</t>
-  </si>
-  <si>
-    <t>Boreverktøyet er et industrielt instrument som er i stand til å utvinne mineralformasjoner som ellers er ugjennomtrengelige med standard overlevelsesutstyr.
-Det muliggjør høyavkastende ressurshøsting uten bruk av rekedrakt.
-- Forsterket industrielt diamantbelegg muliggjør brudd i de molekylære bindingene i store mineralårer.
-- Bakovervendte mikro-thrustere forhindrer at operatøren drives bakover av borets motstand.
-- Motor med variabelt dreiemoment justerer turtallet basert på materialtetthet for å forhindre at boret setter seg fast og tilbakeslag som kan forårsake håndleddsbrudd.
+- Kintamo sukimo momento variklis reguliuoja apsukas pagal medžiagos tankį, kad būtų išvengta grąžto strigimo ir riešo lūžio atatrankos.
+„Aplenkdami poreikį naudoti sunkiasvores transporto priemones, sutaupėte 4,2 „Alterra“ kreditų už kuro elementų nusidėvėjimą. Prašom.“</t>
+  </si>
+  <si>
+    <t>Boreverktøyet er et industrielt instrument som er i stand til å utvinne mineralformasjoner som ellers er ugjennomtrengelige med standard overlevelsesutstyr, uten bruk av rekedrakt.
+- Forsterket industrielt diamantbelegg muliggjør brudd i de molekylære bindingene i store mineralårer
+- Bakovervendte mikro-thrustere forhindrer at operatøren drives bakover av borets motstand
+- Variabelt dreiemomentmotor justerer turtallet basert på materialtetthet for å forhindre at boret setter seg fast og tilbakeslag som kan forårsake håndleddsbrudd
 "Ved å omgå behovet for bruk av tunge kjøretøy har du spart Alterra 4,2 studiepoeng i avskrivning av brenselceller. Bare hyggelig."</t>
   </si>
   <si>
-    <t>Wiertnica to urządzenie przemysłowe, które umożliwia wydobywanie z formacji mineralnych, które są w innym przypadku niedostępne dla standardowego sprzętu survivalowego.
-Umożliwia ono wysokowydajne pozyskiwanie surowców bez użycia kombinezonu Prawn.
-- Wzmocniona przemysłowa powłoka diamentowa umożliwia rozrywanie wiązań molekularnych w dużych żyłach mineralnych.
+    <t>Wiertnica to urządzenie przemysłowe, które umożliwia wydobywanie formacji mineralnych, które są w innym przypadku niedostępne dla standardowego sprzętu survivalowego, bez konieczności użycia kombinezonu Prawn.
+- Wzmocniona przemysłowa powłoka diamentowa umożliwia rozrywanie wiązań molekularnych dużych żył mineralnych.
 - Mikrosilniki skierowane do tyłu zapobiegają odpychaniu operatora do tyłu przez opór wiertarki.
 - Silnik o zmiennym momencie obrotowym dostosowuje obroty na podstawie gęstości materiału, aby zapobiec zakleszczaniu się wiertła i odrzutowi nadgarstka.
-„Dzięki wyeliminowaniu konieczności użycia ciężkich pojazdów zaoszczędziliście Państwo firmie Alterra 4,2 kredytu na amortyzacji ogniw paliwowych. Zapraszamy”.</t>
-  </si>
-  <si>
-    <t>A ferramenta de perfuração é um instrumento industrial capaz de extrair formações minerais que seriam impenetráveis ​​para equipamentos de sobrevivência padrão.
-Ela permite a extração de recursos de alto rendimento sem a necessidade de usar um traje PRAWN.
+„Dzięki wyeliminowaniu konieczności użycia ciężkich pojazdów zaoszczędziłeś firmie Alterra 4,2 punktu na amortyzacji ogniw paliwowych. Zapraszamy”.</t>
+  </si>
+  <si>
+    <t>A ferramenta de perfuração é um instrumento industrial capaz de extrair formações minerais que seriam impenetráveis ​​para equipamentos de sobrevivência padrão, sem a necessidade de um traje PRAWN.
 - O revestimento reforçado de diamante industrial permite fraturar as ligações moleculares de grandes veios minerais.
-- Micropropulsores traseiros impedem que o operador seja impulsionado para trás pela resistência da perfuratriz.
-- O motor de torque variável ajusta a RPM com base na densidade do material para evitar o travamento da broca e o recuo que pode causar fraturas no pulso.
+- Micropropulsores traseiros impedem que o operador seja impulsionado para trás pela resistência da perfuração.
+- O motor de torque variável ajusta a rotação por minuto (RPM) com base na densidade do material para evitar o travamento da broca e o recuo que pode causar fraturas no pulso.
 "Ao eliminar a necessidade de veículos pesados, você economizou 4,2 créditos da Alterra em depreciação de células de combustível. De nada."</t>
   </si>
   <si>
-    <t>Instrumentul de foraj este un instrument industrial capabil să extragă formațiuni minerale care altfel ar fi impenetrabile de echipamentele standard de supraviețuire.
-Permite recoltarea resurselor cu randament ridicat fără a fi nevoie de utilizarea unui costum Prawn.
-- Stratul industrial ranforsat cu diamant permite fracturarea legăturilor moleculare ale venelor minerale mari
+    <t>Instrumentul de foraj este un instrument industrial capabil să extragă formațiuni minerale care altfel ar fi impenetrabile de echipamentul standard de supraviețuire, fără a fi nevoie de utilizarea unui costum Prawn.
+- Stratul industrial de diamant ranforsat permite fracturarea legăturilor moleculare ale venelor minerale mari
 - Micropropulsoarele orientate spre spate împiedică operatorul să fie propulsat înapoi de rezistența forajului
 - Motorul cu cuplu variabil ajustează turația în funcție de densitatea materialului pentru a preveni blocarea burghiului și reculul cauzat de fracturarea încheieturii mâinii
 „Evitând necesitatea utilizării vehiculelor grele, ați economisit 4,2 credite la Alterra în deprecierea pilelor de combustibil. Cu plăcere.”</t>
   </si>
   <si>
-    <t>Буровая установка — это промышленный инструмент, способный добывать минеральные породы, недоступные для стандартного снаряжения для выживания.
-Он позволяет добывать ресурсы с высокой производительностью без использования защитного костюма.
+    <t>Буровая установка — это промышленный инструмент, способный добывать минеральные породы, недоступные для стандартного снаряжения для выживания, без использования защитного костюма.
 - Усиленное промышленное алмазное покрытие позволяет разрушать молекулярные связи крупных минеральных жил.
 - Микро-двигатели, направленные назад, предотвращают отбрасывание оператора назад сопротивлением буровой установки.
 - Двигатель с переменным крутящим моментом регулирует обороты в зависимости от плотности материала, предотвращая заклинивание бурового долота и отдачу, приводящую к перелому запястья.
-«Благодаря отсутствию необходимости в использовании тяжелой техники вы сэкономили Alterra 4,2 кредита на амортизации топливных элементов. Пожалуйста».</t>
-  </si>
-  <si>
-    <t>Алат за бушење је индустријски инструмент способан за вађење минералних формација које су иначе непробојне стандардном опремом за преживљавање.
-Омогућава вађење ресурса високог приноса без употребе одела за шкампе.
-- Ојачани индустријски дијамантски премаз омогућава разбијање молекуларних веза великих минералних вена.
-- Микро-потисници окренути уназад спречавају да оператер буде потиснут уназад отпором бушилице.
-- Мотор са променљивим обртним моментом подешава број обртаја на основу густине материјала како би се спречило заглављивање бургије и повратни ударац услед прелома зглоба.
-„Заобилажењем потребе за распоређивањем тешких возила, уштедели сте Алтери 4,2 кредита у амортизацији горивних ћелија. Нема на чему.“</t>
-  </si>
-  <si>
-    <t>Vŕtací nástroj je priemyselný nástroj schopný ťažiť minerálne formácie, ktoré sú inak nepreniknuteľné štandardným vybavením na prežitie.
-Umožňuje ťažbu zdrojov s vysokým výnosom bez použitia krevetového obleku.
+«Благодаря отсутствию необходимости в использовании тяжелой техники, вы сэкономили Alterra 4,2 кредита на амортизации топливных элементов. Пожалуйста».</t>
+  </si>
+  <si>
+    <t>Алат за бушење је индустријски инструмент способан за вађење минералних формација које су иначе непробојне стандардном опремом за преживљавање, без употребе одела за шкампе.
+- Ојачани индустријски дијамантски премаз омогућава разбијање молекуларних веза великих минералних вена
+- Микро-потисници окренути уназад спречавају да отпор бушилице покреће оператера уназад
+- Мотор са променљивим обртним моментом подешава број обртаја на основу густине материјала како би се спречило заглављивање бургије и повратни ударац услед прелома зглоба
+„Заобилажењем потребе за тешким возилима, уштедели сте Алтери 4,2 кредита у амортизацији горивних ћелија. Нема на чему.“</t>
+  </si>
+  <si>
+    <t>Vŕtací nástroj je priemyselný nástroj schopný ťažiť minerálne formácie, ktoré sú inak nepreniknuteľné štandardným vybavením na prežitie, bez použitia obleku Prawn Suit.
 - Zosilnený priemyselný diamantový povlak umožňuje rozbíjanie molekulárnych väzieb veľkých minerálnych žíl
 - Mikromotory smerujúce dozadu zabraňujú tomu, aby bol operátor hnaný dozadu odporom vrtáka
 - Motor s premenlivým krútiacim momentom upravuje otáčky na základe hustoty materiálu, aby sa zabránilo zaseknutiu vrtáka a spätnému rázu spôsobenému zlomeninou zápästia
 „Vďaka obídeniu potreby nasadenia ťažkých vozidiel ste ušetrili 4,2 kreditu Alterra na odpisoch palivových článkov. Nie je zač.“</t>
   </si>
   <si>
-    <t>Vrtalno orodje je industrijski instrument, ki lahko izkopava mineralne formacije, ki so sicer neprebojne s standardno opremo za preživetje.
-Omogoča visoko donosno pridobivanje virov brez uporabe zaščitne obleke za kozice.
+    <t>Vrtalno orodje je industrijski instrument, ki lahko izkoplje mineralne formacije, ki so sicer neprebojne s standardno opremo za preživetje, brez uporabe zaščitne obleke za kozice.
 - Ojačana industrijska diamantna prevleka omogoča lomljenje molekularnih vezi velikih mineralnih žil.
 - Mikropotisniki, obrnjeni nazaj, preprečujejo, da bi upor svedra potisnil upravljavca nazaj.
 - Motor s spremenljivim navorom prilagaja število vrtljajev glede na gostoto materiala, da prepreči zatikanje svedra in povratni udarec zaradi zloma zapestja.
 "Z izogibanjem potrebi po uporabi težkih vozil ste prihranili 4,2 kreditne točke Alterra pri amortizaciji gorivnih celic. Ni za kaj."</t>
   </si>
   <si>
-    <t>La herramienta de perforación es un instrumento industrial capaz de extraer formaciones minerales impenetrables para el equipo de supervivencia estándar.
-Permite la extracción de recursos de alto rendimiento sin necesidad de usar un traje Prawn.
+    <t>La herramienta de perforación es un instrumento industrial capaz de extraer formaciones minerales impenetrables para el equipo de supervivencia estándar, sin necesidad de usar un traje Prawn.
 - El recubrimiento reforzado de diamante industrial permite fracturar los enlaces moleculares de grandes vetas minerales.
 - Los micropropulsores traseros evitan que el operador retroceda debido a la resistencia de la perforación.
 - El motor de par variable ajusta las RPM según la densidad del material para evitar que la broca se atasque y el retroceso por fractura de muñeca.
-"Al evitar la necesidad de desplegar vehículos pesados, le has ahorrado a Alterra 4.2 créditos en depreciación de celdas de combustible. De nada."</t>
-  </si>
-  <si>
-    <t>Borrverktyget är ett industriellt instrument som kan utvinna mineralformationer som annars är ogenomträngliga med vanlig överlevnadsutrustning.
-Det möjliggör högavkastande resursutvinning utan användning av räkdräkt.
-- Förstärkt industriell diamantbeläggning möjliggör spräckning av de molekylära bindningarna i stora mineralådror.
-- Bakåtvända mikromotorer förhindrar att operatören drivs bakåt av borrens motstånd.
-- Motor med variabelt vridmoment justerar varvtalet baserat på materialdensitet för att förhindra att borren fastnar och kast som orsakar handledsfrakturer.
+"Al evitar el despliegue de vehículos pesados, le has ahorrado a Alterra 4.2 créditos en depreciación de celdas de combustible. De nada."</t>
+  </si>
+  <si>
+    <t>Borrverktyget är ett industriellt instrument som kan utvinna mineralformationer som annars är ogenomträngliga med vanlig överlevnadsutrustning, utan att en räkdräkt behöver användas.
+- Förstärkt industriell diamantbeläggning möjliggör spräckning av de molekylära bindningarna i stora mineralådror
+- Bakåtvända mikromotorer förhindrar att operatören drivs bakåt av borrens motstånd
+- Motor med variabelt vridmoment justerar varvtalet baserat på materialdensitet för att förhindra att borren fastnar och kast som orsakar handledsfrakturer
 "Genom att kringgå behovet av tunga fordon har du sparat Alterra 4,2 poäng i bränslecellsavskrivning. Varsågod."</t>
   </si>
   <si>
-    <t>เครื่องมือเจาะนี้เป็นเครื่องมืออุตสาหกรรมที่สามารถสกัดแร่ธาตุที่อุปกรณ์เอาชีวิตรอดมาตรฐานไม่สามารถเข้าถึงได้
-ช่วยให้เก็บเกี่ยวทรัพยากรได้ผลผลิตสูงโดยไม่ต้องใช้ชุด Prawn Suit
+    <t>เครื่องมือเจาะนี้เป็นเครื่องมืออุตสาหกรรมที่สามารถสกัดแร่ธาตุที่อุปกรณ์เอาชีวิตรอดมาตรฐานไม่สามารถเข้าถึงได้ โดยไม่ต้องใช้ชุด Prawn Suit
 - การเคลือบเพชรอุตสาหกรรมเสริมแรงช่วยให้สามารถทำลายพันธะโมเลกุลของสายแร่ขนาดใหญ่ได้
 - ไมโครทรัสเตอร์ที่หันไปทางด้านหลังช่วยป้องกันไม่ให้ผู้ใช้งานถูกแรงต้านของสว่านผลักถอยหลัง
 - มอเตอร์แรงบิดแปรผันจะปรับรอบต่อนาทีตามความหนาแน่นของวัสดุเพื่อป้องกันการติดขัดของดอกสว่านและการดีดกลับที่อาจทำให้ข้อมือหัก
 "ด้วยการหลีกเลี่ยงความจำเป็นในการใช้ยานพาหนะขนาดใหญ่ คุณได้ประหยัดค่าเสื่อมราคาของเซลล์เชื้อเพลิงให้กับ Alterra ไป 4.2 เครดิต ยินดีครับ"</t>
   </si>
   <si>
-    <t>Bu matkap, standart hayatta kalma ekipmanlarıyla geçilemeyen mineral oluşumlarını çıkarabilen endüstriyel bir alettir.
-Bir Prawn Suit'in kullanılmasına gerek kalmadan yüksek verimli kaynak hasadı sağlar.
+    <t>Bu matkap, standart hayatta kalma ekipmanlarıyla geçilemeyen mineral oluşumlarını, Prawn Suit giymeye gerek kalmadan çıkarabilen endüstriyel bir alettir.
 - Güçlendirilmiş endüstriyel elmas kaplama, büyük mineral damarlarının moleküler bağlarını kırmayı sağlar.
 - Arkaya bakan mikro iticiler, operatörün matkabın direncinden dolayı geriye doğru itilmesini önler.
-- Değişken torklu motor, uç sıkışmasını ve bilek kırılmasına neden olabilecek geri tepmeyi önlemek için malzeme yoğunluğuna göre devir sayısını ayarlar.
+- Değişken torklu motor, uç sıkışmasını ve bilek kırılmasına neden olabilecek geri tepmeyi önlemek için devir sayısını malzeme yoğunluğuna göre ayarlar.
 "Ağır araç kullanımına gerek kalmadan, Alterra'nın yakıt hücresi amortismanında 4,2 kredi tasarruf sağladınız. Rica ederim."</t>
   </si>
   <si>
-    <t>Буровий інструмент — це промисловий інструмент, здатний видобувати мінеральні утворення, які інакше непроникні для стандартного спорядження для виживання.
-Він дозволяє видобувати високопродуктивні ресурси без використання костюма для креветок.
+    <t>Буровий інструмент — це промисловий інструмент, здатний видобувати мінеральні утворення, які інакше непроникні для стандартного спорядження для виживання, без використання костюма Prawn Suit.
 - Посилене промислове алмазне покриття дозволяє руйнувати молекулярні зв'язки великих мінеральних жил.
 - Мікродвигуни, спрямовані назад, запобігають відкиданню оператора назад опором бура.
 - Двигун зі змінним крутним моментом регулює швидкість обертання залежно від щільності матеріалу, щоб запобігти заклинюванню долота та віддачі від перелому зап'ястя.
 «Уникаючи необхідності використання важкого транспортного засобу, ви заощадили 4,2 кредити Alterra на амортизації паливних елементів. Будь ласка».</t>
   </si>
   <si>
-    <t>Máy khoan là một thiết bị công nghiệp có khả năng khai thác các mỏ khoáng sản mà các thiết bị sinh tồn tiêu chuẩn không thể tiếp cận được.
-Nó cho phép thu hoạch tài nguyên năng suất cao mà không cần sử dụng bộ đồ bảo hộ Prawn Suit.
+    <t>Máy khoan là một thiết bị công nghiệp có khả năng khai thác các mỏ khoáng sản mà các thiết bị sinh tồn tiêu chuẩn không thể tiếp cận được, mà không cần đến bộ đồ lặn Prawn Suit.
 - Lớp phủ kim cương công nghiệp gia cường cho phép phá vỡ các liên kết phân tử của các mạch khoáng lớn
 - Các động cơ đẩy siêu nhỏ hướng về phía sau ngăn người vận hành bị đẩy lùi do lực cản của mũi khoan
 - Động cơ mô-men xoắn biến đổi điều chỉnh tốc độ quay dựa trên mật độ vật liệu để ngăn ngừa kẹt mũi khoan và hiện tượng giật ngược gây gãy cổ tay
@@ -2651,587 +2612,587 @@
         <v>164</v>
       </c>
       <c r="K5" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="L5" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="N5" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="O5" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="P5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="P5" s="14" t="s">
+      <c r="Q5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="Q5" s="14" t="s">
+      <c r="R5" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="R5" s="14" t="s">
+      <c r="S5" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="S5" s="14" t="s">
+      <c r="T5" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="T5" s="14" t="s">
+      <c r="U5" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="U5" s="14" t="s">
+      <c r="V5" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="V5" s="14" t="s">
+      <c r="W5" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="W5" s="14" t="s">
+      <c r="X5" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="X5" s="14" t="s">
+      <c r="Y5" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="Y5" s="14" t="s">
+      <c r="Z5" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="Z5" s="14" t="s">
+      <c r="AA5" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB5" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AA5" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB5" s="14" t="s">
+      <c r="AC5" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="AC5" s="15" t="s">
+      <c r="AD5" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="AD5" s="14" t="s">
-        <v>183</v>
-      </c>
       <c r="AE5" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AF5" s="14" t="s">
         <v>163</v>
       </c>
       <c r="AG5" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="AH5" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI5" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="AH5" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AI5" s="15" t="s">
+      <c r="AJ5" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="AJ5" s="14" t="s">
+      <c r="AK5" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="AK5" s="14" t="s">
+      <c r="AL5" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="AL5" s="15" t="s">
+      <c r="AM5" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="AM5" s="14" t="s">
+      <c r="AN5" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="AN5" s="16" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="O6" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="O6" s="15" t="s">
+      <c r="P6" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="Q6" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="R6" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="S6" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="T6" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="T6" s="8" t="s">
+      <c r="U6" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="U6" s="8" t="s">
+      <c r="V6" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="V6" s="8" t="s">
+      <c r="W6" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="X6" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="X6" s="8" t="s">
+      <c r="Y6" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Z6" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="Z6" s="8" t="s">
+      <c r="AA6" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB6" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="AA6" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB6" s="8" t="s">
+      <c r="AC6" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="AC6" s="15" t="s">
+      <c r="AD6" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="AD6" s="8" t="s">
+      <c r="AE6" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="AF6" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="AE6" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="AF6" s="8" t="s">
+      <c r="AG6" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="AG6" s="8" t="s">
+      <c r="AH6" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="AH6" s="8" t="s">
+      <c r="AI6" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="AI6" s="15" t="s">
+      <c r="AJ6" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="AJ6" s="8" t="s">
+      <c r="AK6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AK6" s="8" t="s">
+      <c r="AL6" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="AL6" s="15" t="s">
+      <c r="AM6" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="AM6" s="8" t="s">
+      <c r="AN6" s="17" t="s">
         <v>227</v>
-      </c>
-      <c r="AN6" s="17" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="F7" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="H7" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="I7" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="J7" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="K7" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="L7" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="M7" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="N7" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="O7" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="O7" s="15" t="s">
+      <c r="P7" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="Q7" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="Q7" s="14" t="s">
+      <c r="R7" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="R7" s="14" t="s">
+      <c r="S7" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="S7" s="14" t="s">
+      <c r="T7" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="T7" s="14" t="s">
+      <c r="U7" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="U7" s="14" t="s">
+      <c r="V7" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="V7" s="14" t="s">
+      <c r="W7" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="X7" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="X7" s="14" t="s">
+      <c r="Y7" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="Y7" s="14" t="s">
+      <c r="Z7" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="Z7" s="14" t="s">
+      <c r="AA7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB7" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="AA7" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="AB7" s="14" t="s">
+      <c r="AC7" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="AC7" s="15" t="s">
+      <c r="AD7" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="AD7" s="14" t="s">
+      <c r="AE7" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AF7" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="AE7" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="AF7" s="14" t="s">
+      <c r="AG7" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="AG7" s="14" t="s">
+      <c r="AH7" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="AH7" s="14" t="s">
+      <c r="AI7" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="AI7" s="15" t="s">
+      <c r="AJ7" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="AJ7" s="14" t="s">
+      <c r="AK7" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="AK7" s="14" t="s">
+      <c r="AL7" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="AL7" s="15" t="s">
+      <c r="AM7" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="AM7" s="14" t="s">
+      <c r="AN7" s="16" t="s">
         <v>265</v>
-      </c>
-      <c r="AN7" s="16" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="N8" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="O8" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="O8" s="15" t="s">
+      <c r="P8" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="Q8" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="Q8" s="8" t="s">
+      <c r="R8" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="S8" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="S8" s="8" t="s">
+      <c r="T8" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="T8" s="8" t="s">
+      <c r="U8" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="U8" s="8" t="s">
+      <c r="V8" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="V8" s="8" t="s">
+      <c r="W8" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="W8" s="8" t="s">
+      <c r="X8" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="X8" s="8" t="s">
+      <c r="Y8" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="Y8" s="8" t="s">
+      <c r="Z8" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="Z8" s="8" t="s">
+      <c r="AA8" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="AB8" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="AA8" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB8" s="8" t="s">
+      <c r="AC8" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="AC8" s="15" t="s">
+      <c r="AD8" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="AD8" s="8" t="s">
+      <c r="AE8" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="AF8" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="AE8" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="AF8" s="8" t="s">
+      <c r="AG8" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="AG8" s="8" t="s">
+      <c r="AH8" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="AH8" s="8" t="s">
+      <c r="AI8" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="AI8" s="15" t="s">
+      <c r="AJ8" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="AJ8" s="8" t="s">
+      <c r="AK8" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="AK8" s="8" t="s">
+      <c r="AL8" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="AL8" s="15" t="s">
+      <c r="AM8" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="AM8" s="8" t="s">
+      <c r="AN8" s="17" t="s">
         <v>303</v>
-      </c>
-      <c r="AN8" s="17" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E9" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="F9" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="G9" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="H9" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="I9" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="J9" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="L9" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="M9" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="N9" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="O9" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="O9" s="14" t="s">
+      <c r="P9" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="Q9" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="Q9" s="14" t="s">
+      <c r="R9" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="S9" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="T9" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="T9" s="14" t="s">
+      <c r="U9" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="U9" s="14" t="s">
+      <c r="V9" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="V9" s="14" t="s">
+      <c r="W9" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="W9" s="14" t="s">
+      <c r="X9" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="X9" s="14" t="s">
+      <c r="Y9" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="Y9" s="14" t="s">
+      <c r="Z9" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="Z9" s="14" t="s">
+      <c r="AA9" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="AB9" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="AA9" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="AB9" s="14" t="s">
+      <c r="AC9" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="AC9" s="14" t="s">
+      <c r="AD9" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="AD9" s="14" t="s">
+      <c r="AE9" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="AF9" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="AE9" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="AF9" s="14" t="s">
+      <c r="AG9" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="AG9" s="14" t="s">
+      <c r="AH9" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="AH9" s="14" t="s">
+      <c r="AI9" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="AJ9" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="AI9" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="AJ9" s="14" t="s">
+      <c r="AK9" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="AK9" s="14" t="s">
+      <c r="AL9" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="AL9" s="14" t="s">
+      <c r="AM9" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="AM9" s="14" t="s">
+      <c r="AN9" s="16" t="s">
         <v>340</v>
-      </c>
-      <c r="AN9" s="16" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>40</v>
@@ -3288,7 +3249,7 @@
         <v>40</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="U10" s="8" t="s">
         <v>40</v>
@@ -3353,246 +3314,246 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="E11" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="O11" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="O11" s="14" t="s">
+      <c r="P11" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="R11" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="P11" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q11" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="R11" s="14" t="s">
+      <c r="S11" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="T11" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="V11" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="T11" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="U11" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="V11" s="14" t="s">
+      <c r="W11" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="X11" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y11" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z11" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA11" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB11" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="AC11" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="W11" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="X11" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y11" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="Z11" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="AA11" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="AB11" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="AC11" s="14" t="s">
+      <c r="AD11" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AE11" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AF11" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AG11" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="AH11" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="AD11" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="AE11" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="AF11" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="AG11" s="14" t="s">
+      <c r="AI11" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="AJ11" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="AK11" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="AL11" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="AH11" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="AI11" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="AJ11" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="AK11" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="AL11" s="14" t="s">
-        <v>353</v>
-      </c>
       <c r="AM11" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="AN11" s="16" t="s">
         <v>265</v>
-      </c>
-      <c r="AN11" s="16" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>354</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="C12" s="20" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="D12" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="F12" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="G12" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="H12" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="I12" s="21" t="s">
         <v>361</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="J12" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="K12" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="L12" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="M12" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="M12" s="21" t="s">
+      <c r="N12" s="21" t="s">
         <v>366</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="O12" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="O12" s="21" t="s">
+      <c r="P12" s="21" t="s">
         <v>368</v>
       </c>
-      <c r="P12" s="21" t="s">
+      <c r="Q12" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="Q12" s="21" t="s">
+      <c r="R12" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="R12" s="21" t="s">
+      <c r="S12" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="S12" s="21" t="s">
+      <c r="T12" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="T12" s="21" t="s">
+      <c r="U12" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="U12" s="21" t="s">
+      <c r="V12" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="V12" s="21" t="s">
+      <c r="W12" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="W12" s="21" t="s">
+      <c r="X12" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="X12" s="21" t="s">
+      <c r="Y12" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="Y12" s="21" t="s">
+      <c r="Z12" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="Z12" s="21" t="s">
+      <c r="AA12" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="AB12" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="AA12" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="AB12" s="21" t="s">
+      <c r="AC12" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="AC12" s="21" t="s">
+      <c r="AD12" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="AD12" s="21" t="s">
+      <c r="AE12" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="AF12" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="AE12" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="AF12" s="21" t="s">
+      <c r="AG12" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="AG12" s="21" t="s">
+      <c r="AH12" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="AH12" s="21" t="s">
+      <c r="AI12" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="AJ12" s="21" t="s">
         <v>385</v>
       </c>
-      <c r="AI12" s="21" t="s">
-        <v>385</v>
-      </c>
-      <c r="AJ12" s="21" t="s">
+      <c r="AK12" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="AK12" s="21" t="s">
+      <c r="AL12" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="AL12" s="21" t="s">
+      <c r="AM12" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="AM12" s="21" t="s">
+      <c r="AN12" s="22" t="s">
         <v>389</v>
-      </c>
-      <c r="AN12" s="22" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="13">

--- a/translate.xlsx
+++ b/translate.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="462">
   <si>
     <t>Keycode</t>
   </si>
@@ -460,8 +460,8 @@
 エネルギーは、大規模な資源鉱床を採掘する場合にのみ消費されます。</t>
   </si>
   <si>
-    <t>자원 매장지 채굴 시 배터리 소모량이 발생합니다.
-매장지를 완전히 파괴하려면 최대 320번의 채굴이 필요합니다.
+    <t>자원 매장지 채굴 시마다 배터리가 소모됩니다.
+매장지를 완전히 파괴하려면 최대 320번 채굴해야 합니다.
 에너지는 대형 자원 매장지를 채굴할 때만 소모됩니다.</t>
   </si>
   <si>
@@ -574,6 +574,9 @@
     <t>Hitinterval</t>
   </si>
   <si>
+    <t>Interval raken</t>
+  </si>
+  <si>
     <t>Tabamuse intervall</t>
   </si>
   <si>
@@ -670,12 +673,12 @@
 Utilitzeu el valor per defecte per coincidir amb la velocitat de mineria d'un braç perforador amb vestit de gambes.</t>
   </si>
   <si>
-    <t>资源矿藏的采集间隔。
+    <t>资源矿脉的采集间隔。
 间隔越小，采集速度越快。
 使用默认值以匹配虾式机甲钻臂的采矿速度。</t>
   </si>
   <si>
-    <t>資源礦藏的採集間隔。
+    <t>資源礦脈的採集間隔。
 間隔越小，採集速度越快。
 使用預設值以匹配蝦式機甲鑽臂的採礦速度。</t>
   </si>
@@ -906,7 +909,7 @@
     <t>Vrtalno orodje</t>
   </si>
   <si>
-    <t>Herramienta de perforación</t>
+    <t>Taladro</t>
   </si>
   <si>
     <t>Taladro de mano</t>
@@ -1180,9 +1183,6 @@
   </si>
   <si>
     <t>Сверло</t>
-  </si>
-  <si>
-    <t>Taladro</t>
   </si>
   <si>
     <t>Matkap Aleti</t>
@@ -1219,14 +1219,14 @@
 "En evitar la necessitat de desplegament de vehicles pesats, heu estalviat a Alterra 4,2 crèdits en la depreciació de les piles de combustible. De res."</t>
   </si>
   <si>
-    <t>这款钻探工具是一种工业级仪器，无需使用虾式机甲，即可开采标准生存装备无法穿透的矿层。
+    <t>这台钻机是一种工业级仪器，无需使用虾式机甲，即可开采标准生存装备无法穿透的矿层。
 - 强化型工业金刚石涂层能够破坏大型矿脉的分子键
 - 后置微型推进器可防止操作员因钻头阻力而被向后推
 - 可变扭矩电机可根据材料密度调节转速，防止钻头卡死和手腕反冲
 “由于无需部署重型载具，您节省了 Alterra 4.2 点燃料电池折旧费用。不用谢。”</t>
   </si>
   <si>
-    <t>這款鑽探工具是一種工業級儀器，無需使用蝦式機甲，即可開採標準生存裝備無法穿透的礦層。
+    <t>這台鑽孔機是一種工業級儀器，無需使用蝦式機甲，即可開採標準生存裝備無法穿透的礦層。
 - 強化型工業用鑽石塗層能夠破壞大型礦脈的分子鍵
 - 後置微型推進器可防止操作員因鑽頭阻力而被向後推
 - 可變扭矩馬達可根據材料密度調節轉速，防止鑽頭卡死和手腕反轉
@@ -1240,10 +1240,10 @@
 "Zaobilaženjem potrebe za korištenjem teških vozila, uštedjeli ste Alterra 4,2 kredita u amortizaciji gorivnih ćelija. Nema na čemu."</t>
   </si>
   <si>
-    <t>Vrtací nástroj je průmyslový nástroj schopný těžit minerální formace, které jsou jinak pro standardní vybavení pro přežití neproniknutelné, a to bez použití obleku Prawn Suit.
+    <t>Vrtací nástroj je průmyslový nástroj schopný těžit minerální formace, které jsou jinak neproniknutelné standardním vybavením pro přežití, a to bez použití obleku Prawn Suit.
 - Zesílený průmyslový diamantový povlak umožňuje rozrušit molekulární vazby velkých minerálních žil.
 - Mikromotory směřující dozadu zabraňují tomu, aby byl obsluha hnána dozadu odporem vrtáku.
-- Motor s proměnným točivým momentem upravuje otáčky na základě hustoty materiálu, aby se zabránilo zaseknutí vrtáku a zpětnému rázu způsobujícímu zlomeninu zápěstí.
+- Motor s proměnným točivým momentem upravuje otáčky na základě hustoty materiálu, aby se zabránilo zaseknutí vrtáku a zpětnému rázu způsobenému zlomeninou zápěstí.
 „Tím, že jste se vyhnuli nutnosti nasazení těžkých vozidel, jste ušetřili 4,2 kreditu Alterra na odpisech palivových článků. Není zač.“</t>
   </si>
   <si>
@@ -1432,7 +1432,7 @@
     <t>Буровий інструмент — це промисловий інструмент, здатний видобувати мінеральні утворення, які інакше непроникні для стандартного спорядження для виживання, без використання костюма Prawn Suit.
 - Посилене промислове алмазне покриття дозволяє руйнувати молекулярні зв'язки великих мінеральних жил.
 - Мікродвигуни, спрямовані назад, запобігають відкиданню оператора назад опором бура.
-- Двигун зі змінним крутним моментом регулює швидкість обертання залежно від щільності матеріалу, щоб запобігти заклинюванню долота та віддачі від перелому зап'ястя.
+- Двигун зі змінним крутним моментом регулює оберти залежно від щільності матеріалу, щоб запобігти заклинюванню долота та віддачі від перелому зап'ястя.
 «Уникаючи необхідності використання важкого транспортного засобу, ви заощадили 4,2 кредити Alterra на амортизації паливних елементів. Будь ласка».</t>
   </si>
   <si>
@@ -1441,6 +1441,257 @@
 - Các động cơ đẩy siêu nhỏ hướng về phía sau ngăn người vận hành bị đẩy lùi do lực cản của mũi khoan
 - Động cơ mô-men xoắn biến đổi điều chỉnh tốc độ quay dựa trên mật độ vật liệu để ngăn ngừa kẹt mũi khoan và hiện tượng giật ngược gây gãy cổ tay
 "Bằng cách bỏ qua nhu cầu sử dụng phương tiện hạng nặng, bạn đã tiết kiệm được cho Alterra 4,2 tín dụng chi phí khấu hao pin nhiên liệu. Không có gì."</t>
+  </si>
+  <si>
+    <t>DrillTool.AutoCollectLabel</t>
+  </si>
+  <si>
+    <t>Auto Collect</t>
+  </si>
+  <si>
+    <t>Outomatiese Versameling</t>
+  </si>
+  <si>
+    <t>Автоматично събиране</t>
+  </si>
+  <si>
+    <t>Recollida automàtica</t>
+  </si>
+  <si>
+    <t>自动收集</t>
+  </si>
+  <si>
+    <t>自動收集</t>
+  </si>
+  <si>
+    <t>Automatsko prikupljanje</t>
+  </si>
+  <si>
+    <t>Automatické vyzvednutí</t>
+  </si>
+  <si>
+    <t>Automatisk afhentning</t>
+  </si>
+  <si>
+    <t>Automaatne kogumine</t>
+  </si>
+  <si>
+    <t>Automaattinen nouto</t>
+  </si>
+  <si>
+    <t>Collecte automatique</t>
+  </si>
+  <si>
+    <t>Automatische Abholung</t>
+  </si>
+  <si>
+    <t>Αυτόματη συλλογή</t>
+  </si>
+  <si>
+    <t>Automatikus átvétel</t>
+  </si>
+  <si>
+    <t>Bailiúchán Uathoibríoch</t>
+  </si>
+  <si>
+    <t>Raccolta automatica</t>
+  </si>
+  <si>
+    <t>自動収集</t>
+  </si>
+  <si>
+    <t>자동 수집</t>
+  </si>
+  <si>
+    <t>Automātiska savākšana</t>
+  </si>
+  <si>
+    <t>Automatinis surinkimas</t>
+  </si>
+  <si>
+    <t>Automatisk henting</t>
+  </si>
+  <si>
+    <t>Automatyczne zbieranie</t>
+  </si>
+  <si>
+    <t>Coleta automática</t>
+  </si>
+  <si>
+    <t>Colectare automată</t>
+  </si>
+  <si>
+    <t>Автоматический сбор</t>
+  </si>
+  <si>
+    <t>Аутоматско прикупљање</t>
+  </si>
+  <si>
+    <t>Automatický zber</t>
+  </si>
+  <si>
+    <t>Samodejno zbiranje</t>
+  </si>
+  <si>
+    <t>Automatisk insamling</t>
+  </si>
+  <si>
+    <t>เก็บเงินอัตโนมัติ</t>
+  </si>
+  <si>
+    <t>Otomatik Toplama</t>
+  </si>
+  <si>
+    <t>Автоматичний збір</t>
+  </si>
+  <si>
+    <t>Thu gom tự động</t>
+  </si>
+  <si>
+    <t>DrillTool.AutoCollectTooltip</t>
+  </si>
+  <si>
+    <t>If enabled, then the mined resources will automatically enter the player's inventory, similar to the behaviour of a Prawn Drill Arm.
+Disabled by default.</t>
+  </si>
+  <si>
+    <t>Indien geaktiveer, sal die ontginde hulpbronne outomaties die speler se inventaris binnegaan, soortgelyk aan die gedrag van 'n Garnaleboorarm.
+Standaard gedeaktiveer.</t>
+  </si>
+  <si>
+    <t>Ако е активирано, добитите ресурси автоматично ще влязат в инвентара на играча, подобно на поведението на ръката за сондажи за скариди.
+Деактивирано по подразбиране.</t>
+  </si>
+  <si>
+    <t>Si està activat, els recursos extrets entraran automàticament a l'inventari del jugador, de manera similar al comportament d'un Prawn Drill Arm.
+Desactivat per defecte.</t>
+  </si>
+  <si>
+    <t>启用后，开采出的资源将自动进入玩家的物品栏，类似于虾式钻臂的操作。
+默认禁用。</t>
+  </si>
+  <si>
+    <t>啟用後，開採的資源將自動進入玩家的物品欄，類似蝦式鑽臂的操作。
+預設禁用。</t>
+  </si>
+  <si>
+    <t>Ako je omogućeno, iskopani resursi će automatski ući u inventar igrača, slično ponašanju ruke za bušenje kozica.
+Onemogućeno prema zadanim postavkama.</t>
+  </si>
+  <si>
+    <t>Pokud je tato možnost povolena, vytěžené zdroje se automaticky dostanou do hráčova inventáře, podobně jako se chová rameno pro vrtání krevet.
+Ve výchozím nastavení je tato možnost zakázána.</t>
+  </si>
+  <si>
+    <t>Hvis aktiveret, vil de udvundne ressourcer automatisk blive tilføjet til spillerens inventar, svarende til en rejeborearms opførsel.
+Deaktiveret som standard.</t>
+  </si>
+  <si>
+    <t>Indien ingeschakeld, komen de gewonnen grondstoffen automatisch in de inventaris van de speler terecht, vergelijkbaar met het gedrag van een Prawn Drill Arm.
+Standaard uitgeschakeld.</t>
+  </si>
+  <si>
+    <t>Kui see on lubatud, siis kaevandatud ressursid lisatakse automaatselt mängija inventari, sarnaselt krevetipuurvarda käitumisele.
+Vaikimisi keelatud.</t>
+  </si>
+  <si>
+    <t>Jos käytössä, louhitut resurssit siirtyvät automaattisesti pelaajan tavaraluetteloon samalla tavalla kuin katkarapuporakone.
+Oletusarvoisesti pois käytöstä.</t>
+  </si>
+  <si>
+    <t>Si cette option est activée, les ressources extraites seront automatiquement ajoutées à l'inventaire du joueur, comme le ferait un bras de forage Prawn.
+Désactivée par défaut.</t>
+  </si>
+  <si>
+    <t>Ist diese Option aktiviert, gelangen die abgebauten Ressourcen automatisch in das Inventar des Spielers, ähnlich wie beim Prawn-Bohrarm. Standardmäßig deaktiviert.</t>
+  </si>
+  <si>
+    <t>Εάν είναι ενεργοποιημένη, τότε οι εξορυγμένοι πόροι θα εισέλθουν αυτόματα στο απόθεμα του παίκτη, παρόμοια με τη συμπεριφορά ενός βραχίονα τρυπανιού γαρίδας.
+Απενεργοποιημένο από προεπιλογή.</t>
+  </si>
+  <si>
+    <t>Ha engedélyezve van, akkor a kibányászott erőforrások automatikusan bekerülnek a játékos felszerelésébe, hasonlóan a garnélarák-fúró kar viselkedéséhez.
+Alapértelmezés szerint letiltva.</t>
+  </si>
+  <si>
+    <t>Má tá sé cumasaithe, cuirfear na hacmhainní mianadóireachta isteach i bhfardal an imreora go huathoibríoch, cosúil le hiompar Lámh Druileála Cloicheán.
+Díchumasaithe de réir réamhshocraithe.</t>
+  </si>
+  <si>
+    <t>Se abilitata, le risorse estratte entreranno automaticamente nell'inventario del giocatore, in modo simile al comportamento di un braccio perforatore Prawn.
+Disabilitata per impostazione predefinita.</t>
+  </si>
+  <si>
+    <t>有効にすると、採掘された資源はプラウンドリルアームと同様に、自動的にプレイヤーのインベントリに格納されます。
+デフォルトでは無効になっています。</t>
+  </si>
+  <si>
+    <t>이 기능을 활성화하면 채굴한 자원이 프론 드릴 암처럼 자동으로 플레이어의 인벤토리에 추가됩니다.
+기본적으로 비활성화되어 있습니다.</t>
+  </si>
+  <si>
+    <t>Ja iespējots, iegūtie resursi automātiski nonāks spēlētāja inventārā, līdzīgi kā garneļu urbšanas roka.
+Pēc noklusējuma atspējots.</t>
+  </si>
+  <si>
+    <t>Jei įjungta, iškasti ištekliai automatiškai pateks į žaidėjo inventorių, panašiai kaip krevečių grąžto rankos veikimas.
+Pagal numatytuosius nustatymus išjungta.</t>
+  </si>
+  <si>
+    <t>Hvis aktivert, vil de utvunnede ressursene automatisk bli lagt inn i spillerens inventar, på samme måte som en rekeborearm oppfører seg.
+Deaktivert som standard.</t>
+  </si>
+  <si>
+    <t>Jeśli ta opcja jest włączona, wydobyte surowce automatycznie trafią do ekwipunku gracza, podobnie jak ramię wiertnicze do krewetek.
+Domyślnie wyłączone.</t>
+  </si>
+  <si>
+    <t>Se ativado, os recursos extraídos entrarão automaticamente no inventário do jogador, de forma semelhante ao comportamento do Braço Perfurador do Prawn.
+Desativado por padrão.</t>
+  </si>
+  <si>
+    <t>Dacă este activată, resursele extrase vor intra automat în inventarul jucătorului, similar comportamentului unui braț de foraj pentru creveți.
+Dezactivată în mod implicit.</t>
+  </si>
+  <si>
+    <t>Если эта функция включена, добытые ресурсы будут автоматически попадать в инвентарь игрока, подобно работе буровой установки Prawn Drill Arm.
+По умолчанию отключено.</t>
+  </si>
+  <si>
+    <t>Ако је омогућено, ископани ресурси ће аутоматски ући у инвентар играча, слично понашању руке за бушење шкампа.
+Подразумевано онемогућено.</t>
+  </si>
+  <si>
+    <t>Ak je povolené, vyťažené zdroje sa automaticky dostanú do hráčovho inventára, podobne ako sa správa rameno na vŕtanie kreviet.
+Predvolene vypnuté.</t>
+  </si>
+  <si>
+    <t>Če je omogočeno, bodo izkopani viri samodejno vstopili v igralčev inventar, podobno kot se obnaša roka za vrtanje kozic.
+Privzeto onemogočeno.</t>
+  </si>
+  <si>
+    <t>Si está activada, los recursos extraídos se añadirán automáticamente al inventario del jugador, de forma similar al comportamiento del Brazo Perforador de Gambas.
+Desactivada por defecto.</t>
+  </si>
+  <si>
+    <t>Om aktiverat kommer de utvunna resurserna automatiskt att läggas in i spelarens inventarieförråd, ungefär som en räkborrarm beter sig.
+Inaktiverad som standard.</t>
+  </si>
+  <si>
+    <t>หากเปิดใช้งาน ทรัพยากรที่ขุดได้จะเข้าสู่คลังของผู้เล่นโดยอัตโนมัติ คล้ายกับพฤติกรรมของแขนเจาะกุ้ง
+ปิดใช้งานโดยค่าเริ่มต้น</t>
+  </si>
+  <si>
+    <t>Etkinleştirilirse, çıkarılan kaynaklar, bir Karides Matkap Kolunun davranışına benzer şekilde, otomatik olarak oyuncunun envanterine girer.
+Varsayılan olarak devre dışıdır.</t>
+  </si>
+  <si>
+    <t>Якщо ввімкнено, то видобуті ресурси автоматично потраплятимуть до інвентарю гравця, подібно до поведінки Креветкової бурильної руки.
+За замовчуванням вимкнено.</t>
+  </si>
+  <si>
+    <t>Nếu được kích hoạt, tài nguyên khai thác được sẽ tự động được chuyển vào kho đồ của người chơi, tương tự như hoạt động của Cánh tay khoan tôm.
+Mặc định là tắt.</t>
   </si>
 </sst>
 </file>
@@ -1722,7 +1973,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1791,6 +2042,12 @@
     </xf>
     <xf borderId="15" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
@@ -2612,587 +2869,587 @@
         <v>164</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S5" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X5" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y5" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z5" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA5" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AB5" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AC5" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AD5" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AE5" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AF5" s="14" t="s">
         <v>163</v>
       </c>
       <c r="AG5" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AH5" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AI5" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL5" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AM5" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN5" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z6" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC6" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD6" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AF6" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG6" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AH6" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AI6" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AJ6" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AK6" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL6" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM6" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN6" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="R7" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="S7" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="W7" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="X7" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y7" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z7" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA7" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AB7" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AC7" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AD7" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AE7" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AF7" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG7" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH7" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AI7" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AJ7" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AK7" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL7" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM7" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN7" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y8" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z8" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA8" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AC8" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AD8" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AE8" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AF8" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AH8" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AI8" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AJ8" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AK8" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL8" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM8" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN8" s="17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R9" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="S9" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="U9" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="V9" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="W9" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X9" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y9" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z9" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA9" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AB9" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AD9" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AE9" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AF9" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG9" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AH9" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AI9" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AJ9" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AK9" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL9" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM9" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN9" s="16" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>40</v>
@@ -3249,7 +3506,7 @@
         <v>40</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="U10" s="8" t="s">
         <v>40</v>
@@ -3314,124 +3571,124 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="R11" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="S11" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="U11" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V11" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W11" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="X11" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y11" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z11" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA11" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AB11" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AD11" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AE11" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AF11" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG11" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH11" s="14" t="s">
-        <v>351</v>
+        <v>260</v>
       </c>
       <c r="AI11" s="14" t="s">
-        <v>351</v>
+        <v>260</v>
       </c>
       <c r="AJ11" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AK11" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL11" s="14" t="s">
         <v>352</v>
       </c>
       <c r="AM11" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN11" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -3557,349 +3814,547 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
+      <c r="A13" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>400</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="O13" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="P13" s="23" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q13" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="R13" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="S13" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="T13" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="U13" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="V13" s="24" t="s">
+        <v>410</v>
+      </c>
+      <c r="W13" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="X13" s="24" t="s">
+        <v>412</v>
+      </c>
+      <c r="Y13" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="Z13" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="AA13" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB13" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC13" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="AD13" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="AE13" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="AF13" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="AG13" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="AH13" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="AI13" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="AJ13" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="AK13" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="AL13" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="AM13" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="AN13" s="24" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
+      <c r="A14" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>434</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="N14" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="O14" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="P14" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q14" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="R14" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="S14" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="T14" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="U14" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="V14" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="W14" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="X14" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="Y14" s="24" t="s">
+        <v>449</v>
+      </c>
+      <c r="Z14" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="AA14" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="AB14" s="24" t="s">
+        <v>451</v>
+      </c>
+      <c r="AC14" s="24" t="s">
+        <v>452</v>
+      </c>
+      <c r="AD14" s="24" t="s">
+        <v>453</v>
+      </c>
+      <c r="AE14" s="24" t="s">
+        <v>453</v>
+      </c>
+      <c r="AF14" s="24" t="s">
+        <v>454</v>
+      </c>
+      <c r="AG14" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="AH14" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="AI14" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="AJ14" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="AK14" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="AL14" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="AM14" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="AN14" s="24" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
     </row>
     <row r="16">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
     </row>
     <row r="17">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
     </row>
     <row r="18">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
     </row>
     <row r="19">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
     </row>
     <row r="20">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
     </row>
     <row r="21">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
     </row>
     <row r="22">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
     </row>
     <row r="23">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
     </row>
     <row r="24">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
     </row>
     <row r="25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
     </row>
     <row r="26">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
     </row>
     <row r="27">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/translate.xlsx
+++ b/translate.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="465">
   <si>
     <t>Keycode</t>
   </si>
@@ -133,7 +133,7 @@
     <t>Vietnamese</t>
   </si>
   <si>
-    <t>~</t>
+    <t>README</t>
   </si>
   <si>
     <t>en</t>
@@ -274,7 +274,7 @@
     <t>Trošak energije bušilice</t>
   </si>
   <si>
-    <t>Náklady na energii vrtání</t>
+    <t>Spotřeba energie</t>
   </si>
   <si>
     <t>Boremaskine energiomkostninger</t>
@@ -401,8 +401,8 @@
 Potrebno je do 320 udaraca da se ležište potpuno uništi. Energija se troši samo prilikom rudarenja velikog ležišta resursa.</t>
   </si>
   <si>
-    <t>Vybíjení baterie na jeden zásah do ložiska surovin.
-K úplnému zničení ložiska je potřeba až 320 zásahů. Energie se vybíjí pouze při těžbě velkého ložiska surovin.</t>
+    <t>Spotřeba energie na 1 úder do ložiska. K úplnému zničení ložiska je třeba až 320 úderů. Při výchozí hodnotě vystačí baterie na 2 ložiska.
+Energie se spotřebovává jen při těžbě velkých ložisek.</t>
   </si>
   <si>
     <t>Batteriforbrug pr. hit på en ressourcedepot.
@@ -460,8 +460,8 @@
 エネルギーは、大規模な資源鉱床を採掘する場合にのみ消費されます。</t>
   </si>
   <si>
-    <t>자원 매장지 채굴 시마다 배터리가 소모됩니다.
-매장지를 완전히 파괴하려면 최대 320번 채굴해야 합니다.
+    <t>자원 매장지 채굴 시 배터리 소모량이 발생합니다.
+매장지를 완전히 파괴하려면 최대 320번의 채굴이 필요합니다.
 에너지는 대형 자원 매장지를 채굴할 때만 소모됩니다.</t>
   </si>
   <si>
@@ -568,67 +568,70 @@
     <t>Interval pogađanja</t>
   </si>
   <si>
+    <t>Interval úderů</t>
+  </si>
+  <si>
+    <t>Hitinterval</t>
+  </si>
+  <si>
+    <t>Interval raken</t>
+  </si>
+  <si>
+    <t>Tabamuse intervall</t>
+  </si>
+  <si>
+    <t>Osumaväli</t>
+  </si>
+  <si>
+    <t>Intervalle de frappe</t>
+  </si>
+  <si>
+    <t>Trefferintervall</t>
+  </si>
+  <si>
+    <t>Διάστημα χτυπήματος</t>
+  </si>
+  <si>
+    <t>Találati intervallum</t>
+  </si>
+  <si>
+    <t>Eatramh Buille</t>
+  </si>
+  <si>
+    <t>Intervallo di successo</t>
+  </si>
+  <si>
+    <t>ヒット間隔</t>
+  </si>
+  <si>
+    <t>히트 인터벌</t>
+  </si>
+  <si>
+    <t>Rezultātu intervāls</t>
+  </si>
+  <si>
+    <t>Paspaudimų intervalas</t>
+  </si>
+  <si>
+    <t>Treffintervall</t>
+  </si>
+  <si>
+    <t>Interwał trafień</t>
+  </si>
+  <si>
+    <t>Intervalo de impacto</t>
+  </si>
+  <si>
+    <t>Interval de accesare</t>
+  </si>
+  <si>
+    <t>Интервал ударов</t>
+  </si>
+  <si>
+    <t>Интервал погодака</t>
+  </si>
+  <si>
     <t>Interval zásahu</t>
-  </si>
-  <si>
-    <t>Hitinterval</t>
-  </si>
-  <si>
-    <t>Interval raken</t>
-  </si>
-  <si>
-    <t>Tabamuse intervall</t>
-  </si>
-  <si>
-    <t>Osumaväli</t>
-  </si>
-  <si>
-    <t>Intervalle de frappe</t>
-  </si>
-  <si>
-    <t>Trefferintervall</t>
-  </si>
-  <si>
-    <t>Διάστημα χτυπήματος</t>
-  </si>
-  <si>
-    <t>Találati intervallum</t>
-  </si>
-  <si>
-    <t>Eatramh Buille</t>
-  </si>
-  <si>
-    <t>Intervallo di successo</t>
-  </si>
-  <si>
-    <t>ヒット間隔</t>
-  </si>
-  <si>
-    <t>히트 인터벌</t>
-  </si>
-  <si>
-    <t>Rezultātu intervāls</t>
-  </si>
-  <si>
-    <t>Paspaudimų intervalas</t>
-  </si>
-  <si>
-    <t>Treffintervall</t>
-  </si>
-  <si>
-    <t>Interwał trafień</t>
-  </si>
-  <si>
-    <t>Intervalo de impacto</t>
-  </si>
-  <si>
-    <t>Interval de accesare</t>
-  </si>
-  <si>
-    <t>Интервал ударов</t>
-  </si>
-  <si>
-    <t>Интервал погодака</t>
   </si>
   <si>
     <t>Interval zadetkov</t>
@@ -686,7 +689,8 @@
     <t>Interval pronalaska resursa. Manje je brže. Koristite zadanu vrijednost kako biste uskladili brzinu rudarenja s bušaćom rukom Prawn Suit.</t>
   </si>
   <si>
-    <t>Interval těžby u ložiska suroviny. Menší je rychlejší. Použijte výchozí hodnotu, která odpovídá rychlosti těžby vrtacího ramene Prawn Suit.</t>
+    <t>Interval mezi údery. Čím nižší, tím rychlejší těžba.
+Výchozí hodnota odpovídá rychlosti PRAWN vrtací paže.</t>
   </si>
   <si>
     <t>Træfinterval på en ressourceaflejring. Mindre er hurtigere. Brug standardværdien til at matche minedriftshastigheden for en rejedragtborearm.</t>
@@ -840,7 +844,7 @@
     <t>Alat za bušenje</t>
   </si>
   <si>
-    <t>Vrtací nástroj</t>
+    <t>Těžební Vrták</t>
   </si>
   <si>
     <t>Boreværktøj</t>
@@ -1068,7 +1072,7 @@
     <t>Fragment alata za bušenje</t>
   </si>
   <si>
-    <t>Fragment vrtacího nástroje</t>
+    <t>Fargment Těžebního Vrtáku</t>
   </si>
   <si>
     <t>Boreværktøjsfragment</t>
@@ -1158,6 +1162,9 @@
     <t>Tooltip_DrillToolFragment</t>
   </si>
   <si>
+    <t>~</t>
+  </si>
+  <si>
     <t>～</t>
   </si>
   <si>
@@ -1185,262 +1192,265 @@
     <t>Сверло</t>
   </si>
   <si>
+    <t>Orodje za vrtanje</t>
+  </si>
+  <si>
     <t>Matkap Aleti</t>
   </si>
   <si>
     <t>EncyDesc_DrillTool</t>
   </si>
   <si>
-    <t>The drill tool is an industrial instrument capable of extracting mineral formations that are otherwise impenetrable by standard survival equipment, without the deployment of a Prawn Suit.
+    <t>The drill tool is an industrial instrument capable of extracting mineral formations without the need of a Prawn Suit.
 - Reinforced industrial diamond coating enables fracturing the molecular bonds of large mineral veins
 - Rear-facing micro-thrusters prevent the operator from being propelled backward by the drill's resistance
 - Variable torque motor adjusts RPM based on material density to prevent bit binding and wrist-fracture kickback
 "By bypassing the need for heavy vehicular deployment, you have saved Alterra 4.2 credits in fuel cell depreciation. You're welcome."</t>
   </si>
   <si>
-    <t>Die boorgereedskap is 'n industriële instrument wat in staat is om mineraalformasies te onttrek wat andersins ondeurdringbaar is deur standaard oorlewingstoerusting, sonder die ontplooiing van 'n Garnalepak.
+    <t>Die boorgereedskap is 'n industriële instrument wat mineraalformasies kan onttrek sonder die behoefte aan 'n garnaalpak.
 - Versterkte industriële diamantlaag maak dit moontlik om die molekulêre bindings van groot mineraalare te breek.
 - Agtertoe gerigte mikro-stuwers verhoed dat die operateur deur die boor se weerstand agtertoe gedryf word.
 - Veranderlike wringkragmotor pas die RPM aan gebaseer op materiaaldigtheid om boorpuntbinding en terugslag van polsfrakture te voorkom.
 "Deur die behoefte aan swaar voertuigontplooiing te omseil, het u Alterra 4.2 krediete in brandstofseldepresiasie bespaar. Jy's welkom."</t>
   </si>
   <si>
-    <t>Пробивният инструмент е индустриален инструмент, способен да извлича минерални образувания, които иначе са непроницаеми за стандартно оборудване за оцеляване, без използването на костюм за скариди.
+    <t>Пробивният инструмент е индустриален инструмент, способен да извлича минерални образувания без нужда от костюм за скариди.
 - Подсиленото индустриално диамантено покритие позволява разрушаване на молекулярните връзки на големи минерални жили.
-- Насочените назад микротласкащи механизми предотвратяват изтласкването на оператора назад от съпротивлението на сондажа.
+- Микро-тласкащи двигатели, насочени назад, предотвратяват изтласкването на оператора назад от съпротивлението на свредлото.
 - Моторът с променлив въртящ момент регулира оборотите въз основа на плътността на материала, за да предотврати заклинване на свредлото и откат от счупване на китката.
-„Като заобиколите необходимостта от разполагане на тежки превозни средства, вие спестихте 4,2 кредита на Alterra за амортизация на горивни клетки. Няма защо.“</t>
-  </si>
-  <si>
-    <t>L'eina de perforació és un instrument industrial capaç d'extreure formacions minerals que d'altra banda serien impenetrables per l'equip de supervivència estàndard, sense el desplegament d'un vestit de gamba.
-- El recobriment de diamant industrial reforçat permet fracturar els enllaços moleculars de grans venes minerals
-- Els micropropulsors orientats cap enrere eviten que l'operador sigui impulsat cap enrere per la resistència de la perforadora
-- El motor de parell variable ajusta les RPM en funció de la densitat del material per evitar que la broca s'enganxi i el retrocés per fractura del canell
+„Като заобиколите необходимостта от използване на тежки превозни средства, вие спестихте 4,2 кредита на Alterra за амортизация на горивни клетки. Няма защо.“</t>
+  </si>
+  <si>
+    <t>L'eina de perforació és un instrument industrial capaç d'extreure formacions minerals sense necessitat d'un vestit de gamba.
+- El recobriment de diamant industrial reforçat permet fracturar els enllaços moleculars de grans venes minerals.
+- Els micropropulsors orientats cap enrere eviten que l'operador sigui impulsat cap enrere per la resistència de la perforadora.
+- El motor de parell variable ajusta les RPM en funció de la densitat del material per evitar que la broca s'enganxi i el retrocés que pot provocar una fractura al canell.
 "En evitar la necessitat de desplegament de vehicles pesats, heu estalviat a Alterra 4,2 crèdits en la depreciació de les piles de combustible. De res."</t>
   </si>
   <si>
-    <t>这台钻机是一种工业级仪器，无需使用虾式机甲，即可开采标准生存装备无法穿透的矿层。
-- 强化型工业金刚石涂层能够破坏大型矿脉的分子键
-- 后置微型推进器可防止操作员因钻头阻力而被向后推
-- 可变扭矩电机可根据材料密度调节转速，防止钻头卡死和手腕反冲
-“由于无需部署重型载具，您节省了 Alterra 4.2 点燃料电池折旧费用。不用谢。”</t>
-  </si>
-  <si>
-    <t>這台鑽孔機是一種工業級儀器，無需使用蝦式機甲，即可開採標準生存裝備無法穿透的礦層。
-- 強化型工業用鑽石塗層能夠破壞大型礦脈的分子鍵
-- 後置微型推進器可防止操作員因鑽頭阻力而被向後推
-- 可變扭矩馬達可根據材料密度調節轉速，防止鑽頭卡死和手腕反轉
-“由於無需部署重型載具，您節省了 Alterra 4.2 點燃料電池折舊費用。不用謝。”</t>
-  </si>
-  <si>
-    <t>Alat za bušenje je industrijski instrument sposoban za vađenje mineralnih formacija koje su inače neprobojne standardnom opremom za preživljavanje, bez upotrebe odijela za kozice.
+    <t>该钻机是一种工业设备，无需虾式机甲即可开采矿层。
+- 强化型工业金刚石涂层能够破坏大型矿脉的分子键。
+- 后置微型推进器可防止操作员因钻机阻力而被向后推。
+- 可变扭矩电机可根据材料密度调节转速，防止钻头卡死和手腕反冲。
+“由于无需部署重型车辆，您节省了 Alterra 4.2 个积分的燃料电池折旧费用。不用谢。”</t>
+  </si>
+  <si>
+    <t>該鑽機是一種工業設備，無需蝦式機甲即可開採分層。
+- 強化型工業鑽石塗層能夠破壞大型礦脈的分子鍵。
+- 後置微型推進器可防止操作員因鑽機阻力而被向後推。
+- 可變扭力馬達可根據材料密度調節轉速，防止鑽頭卡住和手腕反轉。
+“由於無需部署重型車輛，您節省了 Alterra 4.2 個積分的燃料電池折舊費用。不用謝。”</t>
+  </si>
+  <si>
+    <t>Alat za bušenje je industrijski instrument sposoban za vađenje mineralnih formacija bez potrebe za odijelom za kozice.
 - Ojačani industrijski dijamantni premaz omogućuje razbijanje molekularnih veza velikih mineralnih žila
 - Mikro-potisnici okrenuti prema natrag sprječavaju da se operater pomiče unatrag otporom bušilice
 - Motor s promjenjivim momentom prilagođava broj okretaja na temelju gustoće materijala kako bi se spriječilo blokiranje svrdla i povratni udarac od loma ručnog zgloba
-"Zaobilaženjem potrebe za korištenjem teških vozila, uštedjeli ste Alterra 4,2 kredita u amortizaciji gorivnih ćelija. Nema na čemu."</t>
-  </si>
-  <si>
-    <t>Vrtací nástroj je průmyslový nástroj schopný těžit minerální formace, které jsou jinak neproniknutelné standardním vybavením pro přežití, a to bez použití obleku Prawn Suit.
-- Zesílený průmyslový diamantový povlak umožňuje rozrušit molekulární vazby velkých minerálních žil.
-- Mikromotory směřující dozadu zabraňují tomu, aby byl obsluha hnána dozadu odporem vrtáku.
-- Motor s proměnným točivým momentem upravuje otáčky na základě hustoty materiálu, aby se zabránilo zaseknutí vrtáku a zpětnému rázu způsobenému zlomeninou zápěstí.
-„Tím, že jste se vyhnuli nutnosti nasazení těžkých vozidel, jste ušetřili 4,2 kreditu Alterra na odpisech palivových článků. Není zač.“</t>
-  </si>
-  <si>
-    <t>Boreværktøjet er et industrielt instrument, der er i stand til at udvinde mineralformationer, der ellers er uigennemtrængelige for standard overlevelsesudstyr, uden brug af en rejedragt.
+"Zaobilaženjem potrebe za teškim vozilima uštedjeli ste Alterra 4,2 kredita u amortizaciji gorivnih ćelija. Nema na čemu."</t>
+  </si>
+  <si>
+    <t>Těžební vrták je průmyslový nástroj schopný těžit minerální formace bez nutnosti použití obleku P.R.A.W.N.
+- Zesílený průmyslový diamantový povlak umožňuje narušit vazby velkých minerálních uskupení na molekulární úrovni.
+- Zpětné trysky zajišťují, aby operátor nebyl odstrčen zpět během aktivních operací.
+- Motor s proměnným točivým momentem upravuje otáčky na základě hustoty materiálu, aby se zabránilo zaseknutí vrtáku a zlomeninám zápěstí.
+"Tím, že jste se vyhnuli nutnosti nasazení těžkých vozidel, jste ušetřili společnosti Alterra 4,2 kreditu na odpisech palivových článků. Není zač."</t>
+  </si>
+  <si>
+    <t>Boreværktøjet er et industrielt instrument, der er i stand til at udvinde mineralformationer uden behov for en rejedragt.
 - Forstærket industriel diamantbelægning muliggør brud på de molekylære bindinger i store mineralårer
 - Bagudvendte mikro-thrustere forhindrer, at operatøren bliver drevet bagud af borets modstand
 - Motor med variabelt moment justerer omdrejningstallet baseret på materialedensitet for at forhindre borehovedbinding og tilbageslag fra håndledsbrud
 "Ved at omgå behovet for tunge køretøjer har du sparet Alterra 4,2 point i afskrivning af brændstofceller. Velbekomme."</t>
   </si>
   <si>
-    <t>De boor is een industrieel instrument dat in staat is om minerale formaties te winnen die anders ondoordringbaar zijn voor standaard overlevingsuitrusting, zonder dat een Prawn Suit nodig is.
-- Versterkte industriële diamantcoating maakt het mogelijk om de moleculaire bindingen van grote minerale aderen te verbreken.
+    <t>De boor is een industrieel instrument dat in staat is om minerale formaties te winnen zonder dat een beschermend pak nodig is.
+- Versterkte industriële diamantcoating maakt het mogelijk om de moleculaire bindingen van grote minerale aders te verbreken.
 - Naar achteren gerichte micro-stuwraketten voorkomen dat de operator door de weerstand van de boor naar achteren wordt geduwd.
-- Variabele koppelmotor past het toerental aan op basis van de materiaaldichtheid om vastlopen van de boor en terugslag die tot polsfracturen kan leiden te voorkomen.
-"Door de noodzaak van zwaar transport te omzeilen, heeft u Alterra 4,2 credits bespaard op de afschrijving van de brandstofcel. Graag gedaan."</t>
-  </si>
-  <si>
-    <t>See puurmasin on tööstuslik instrument, mis on võimeline kaevandama mineraalkihte, mis muidu oleksid tavalise ellujäämisvarustusega läbimatud, ilma krevetiülikonnata.
-- Tugevdatud tööstuslik teemantkate võimaldab purustada suurte mineraalisoonte molekulaarseid sidemeid.
+- De motor met variabel koppel past het toerental aan op basis van de materiaaldichtheid om vastlopen van de boor en terugslag die tot polsfracturen kan leiden te voorkomen.
+"Door de noodzaak van zwaar transport te omzeilen, heeft u 4,2 Alterra-credits bespaard op de afschrijving van de brandstofcel. Graag gedaan."</t>
+  </si>
+  <si>
+    <t>See puurimisvahend on tööstuslik instrument, mis on võimeline mineraalformatsioone kaevandama ilma krevetiülikonnata.
+- Tugevdatud tööstuslik teemantkate võimaldab purustada suurte mineraalisoonte molekulaarsidemeid.
 - Tahapoole suunatud mikromootorid takistavad operaatori tagasilööki puuri takistuse tõttu.
 - Muutuva pöördemomendiga mootor reguleerib pöörlemiskiirust vastavalt materjali tihedusele, et vältida puuri kinnikiilumist ja randmemurru tagasilööki.
 "Raskete sõidukite kasutamise vajaduse vältimisega olete säästnud Alterrale 4,2 krediiti kütuseelementide amortisatsiooni pealt. Pole tänu väärt."</t>
   </si>
   <si>
-    <t>Poraustyökalu on teollisuuslaite, jolla voidaan irrottaa mineraalimuodostelmia, jotka muuten olisivat läpäisemättömiä tavallisilla selviytymisvarusteilla, ilman katkarapuvun käyttöä.
+    <t>Poraustyökalu on teollisuuslaite, jolla voidaan eristää mineraalimuodostumia ilman katkarapuvun tarvetta.
 - Vahvistettu teollinen timanttipinnoite mahdollistaa suurten mineraalijuonien molekyylisidosten murtamisen.
-- Taaksepäin suunnatut mikrotyöntövoimalaitteet estävät käyttäjää lennähtämästä taaksepäin poran vastuksen vaikutuksesta.
+- Taaksepäin suunnatut mikrotyöntövoimat estävät käyttäjää lennähtämästä taaksepäin poran vastuksen vaikutuksesta.
 - Muuttuvan vääntömomentin moottori säätää kierroslukua materiaalin tiheyden perusteella estääkseen terän juuttumisen ja ranteen murtuman aiheuttaman takapotkun.
 "Ohittamalla raskaan ajoneuvoliikenteen tarpeen olet säästänyt Alterralta 4,2 krediittiä polttokennojen poistoissa. Ole hyvä."</t>
   </si>
   <si>
-    <t>L'outil de forage est un instrument industriel capable d'extraire des formations minérales inaccessibles aux équipements de survie classiques, sans nécessiter de combinaison spéciale.
+    <t>L'outil de forage est un instrument industriel capable d'extraire des formations minérales sans nécessiter de combinaison spéciale.
 - Son revêtement diamant industriel renforcé permet de fracturer les liaisons moléculaires des grands filons minéraux.
 - Des micro-propulseurs arrière empêchent l'opérateur d'être repoussé par la résistance de la foreuse.
-- Son moteur à couple variable ajuste la vitesse de rotation en fonction de la densité du matériau afin d'éviter le blocage du foret et les risques de blessure au poignet.
+- Son moteur à couple variable ajuste la vitesse de rotation en fonction de la densité du matériau afin d'éviter le blocage du trépan et les risques de blessure au poignet.
 « En évitant le déploiement de véhicules lourds, vous avez permis à Alterra d'économiser 4,2 crédits en amortissement de la pile à combustible. De rien. »</t>
   </si>
   <si>
-    <t>Das Bohrwerkzeug ist ein Industriegerät, mit dem sich Mineralformationen abbauen lassen, die mit herkömmlicher Überlebensausrüstung nicht zugänglich sind – und das ohne den Einsatz eines Prawn Suits.
-– Eine verstärkte Industriediamantbeschichtung ermöglicht das Aufbrechen der molekularen Bindungen großer Mineraladern.
-– Nach hinten gerichtete Mikro-Düsen verhindern, dass der Bediener durch den Widerstand des Bohrers nach hinten geschleudert wird.
-– Ein Motor mit variablem Drehmoment passt die Drehzahl an die Materialdichte an, um ein Festfressen des Bohrers und einen Rückschlag mit Verletzungsgefahr für das Handgelenk zu verhindern.
-„Dadurch, dass kein schweres Fahrzeug benötigt wird, haben Sie Alterra 4.2 Credits für die Brennstoffzellenabschreibung eingespart. Gern geschehen.“</t>
-  </si>
-  <si>
-    <t>Το εργαλείο τρυπανιού είναι ένα βιομηχανικό όργανο ικανό να εξάγει ορυκτούς σχηματισμούς που διαφορετικά θα ήταν αδιαπέραστοι από τον τυπικό εξοπλισμό επιβίωσης, χωρίς την ανάπτυξη μιας στολής Prawn Suit.
+    <t>Das Bohrwerkzeug ist ein Industriegerät, das Mineralformationen ohne Schutzanzug abbauen kann.
+- Eine verstärkte Industriediamantbeschichtung ermöglicht das Aufbrechen der molekularen Bindungen großer Mineraladern.
+- Nach hinten gerichtete Mikro-Düsen verhindern, dass der Bediener durch den Widerstand des Bohrers nach hinten geschleudert wird.
+- Ein Motor mit variablem Drehmoment passt die Drehzahl an die Materialdichte an, um ein Festfressen des Bohrers und einen Rückschlag mit Verletzungsgefahr für das Handgelenk zu verhindern.
+„Durch den Verzicht auf schwere Fahrzeuge haben Sie Alterra 4.2 Credits für die Brennstoffzellenabschreibung eingespart. Gern geschehen.“</t>
+  </si>
+  <si>
+    <t>Το εργαλείο τρυπανιού είναι ένα βιομηχανικό όργανο ικανό να εξάγει ορυκτούς σχηματισμούς χωρίς την ανάγκη κοστουμιού γαρίδας.
 - Η ενισχυμένη βιομηχανική επίστρωση διαμαντιού επιτρέπει τη θραύση των μοριακών δεσμών μεγάλων ορυκτών φλεβών
 - Οι μικρο-προωθητήρες που είναι στραμμένοι προς τα πίσω εμποδίζουν τον χειριστή να ωθηθεί προς τα πίσω από την αντίσταση του τρυπανιού
-- Ο κινητήρας μεταβλητής ροπής ρυθμίζει τις στροφές ανά λεπτό με βάση την πυκνότητα του υλικού για να αποτρέψει το μπλοκάρισμα του τρυπανιού και το κλώτσημα από το κάταγμα του καρπού
-"Παρακάμπτοντας την ανάγκη για βαριά ανάπτυξη οχημάτων, έχετε εξοικονομήσει στην Alterra 4,2 μονάδες στην απόσβεση των κυψελών καυσίμου. Παρακαλώ."</t>
-  </si>
-  <si>
-    <t>A fúrószerszám egy ipari eszköz, amely képes olyan ásványi képződmények kinyerésére, amelyek egyébként áthatolhatatlanok lennének a hagyományos túlélőfelszerelésekkel, anélkül, hogy garnélarák-ruhát kellene használni.
+- Ο κινητήρας μεταβλητής ροπής ρυθμίζει τις στροφές ανά λεπτό με βάση την πυκνότητα του υλικού για να αποτρέψει το μπλοκάρισμα του τρυπανιού και το κλώτσημα λόγω θραύσης του καρπού
+"Παρακάμπτοντας την ανάγκη για βαριά χρήση οχημάτων, έχετε εξοικονομήσει στην Alterra 4,2 μονάδες στην απόσβεση των κυψελών καυσίμου. Παρακαλώ."</t>
+  </si>
+  <si>
+    <t>A fúrószerszám egy ipari eszköz, amely képes ásványi képződmények kinyerésére garnélarák-ruha nélkül.
 - A megerősített ipari gyémántbevonat lehetővé teszi a nagy ásványi erek molekuláris kötéseinek feltörését.
-- A hátrafelé néző mikrohajtóművek megakadályozzák, hogy a kezelőt a fúró ellenállása hátrafelé repítse.
+- A hátrafelé néző mikrohajtóművek megakadályozzák, hogy a fúró ellenállása hátrafelé lendítse a kezelőt.
 - A változtatható nyomatékú motor az anyag sűrűsége alapján állítja be a fordulatszámot, hogy megakadályozza a fúrófej beszorulását és a csuklótörés visszarúgását.
 "A nehéz járművek használatának megkerülésével 4,2 kreditet takarított meg az Alterra üzemanyagcella-értékcsökkenésén. Szívesen."</t>
   </si>
   <si>
-    <t>Is uirlis thionsclaíoch í an uirlis druileála atá in ann foirmíochtaí mianraí a bhaint amach nach mbeadh trealaimh mharthanais chaighdeánacha in ann dul tríd murach sin, gan Culaith Cloicheán a imscaradh.
+    <t>Is uirlis thionsclaíoch í an uirlis druileála atá in ann foirmíochtaí mianraí a bhaint amach gan gá le Culaith Prawn.
 - Cumasaíonn sciath diamant tionsclaíoch athneartaithe naisc mhóilíneacha féitheacha móra mianraí a bhriseadh
 - Coscann micrea-bhrúiteoirí atá os comhair an chúl an t-oibreoir ó bheith á thiomáint siar ag friotaíocht an druileála
 - Coigeartaíonn mótar chasmhóiminte athraitheach RPM bunaithe ar dhlús an ábhair chun ceangal giotán agus cic siar briste caol na láimhe a chosc
 "Tríd an ngá atá le himscaradh feithiclí troma a sheachaint, tá 4.2 creidiúint Alterra sábháilte agat i ndíluacháil cealla breosla. Tá fáilte romhat."</t>
   </si>
   <si>
-    <t>La trivella è uno strumento industriale in grado di estrarre formazioni minerarie altrimenti impenetrabili con le normali attrezzature di sopravvivenza, senza la necessità di indossare una tuta Prawn.
+    <t>La trivella è uno strumento industriale in grado di estrarre formazioni minerarie senza bisogno di indossare una tuta protettiva.
 - Il rivestimento diamantato industriale rinforzato consente di fratturare i legami molecolari di grandi vene minerarie.
 - I micro-propulsori posteriori impediscono all'operatore di essere spinto all'indietro dalla resistenza della trivella.
 - Il motore a coppia variabile regola i giri al minuto in base alla densità del materiale per evitare l'inceppamento della punta e il contraccolpo che potrebbe causare fratture al polso.
 "Evitando l'impiego di veicoli pesanti, hai risparmiato 4,2 crediti Alterra in ammortamento delle celle a combustibile. Prego."</t>
   </si>
   <si>
-    <t>この掘削ツールは、通常のサバイバル装備では掘削不可能な鉱物層を、プラウンスーツを使わずに採掘できる産業用機器です。
-- 強化された工業用ダイヤモンドコーティングにより、巨大な鉱脈の分子結合を破壊します。
+    <t>この掘削ツールは、特殊潜水服を必要とせずに鉱物層を採掘できる産業用機器です。
+- 強化された工業用ダイヤモンドコーティングにより、大きな鉱脈の分子結合を破壊します。
 - 後方に取り付けられたマイクロスラスタにより、ドリルの抵抗によってオペレーターが後方に押し戻されるのを防ぎます。
 - 可変トルクモーターは、材料の密度に応じて回転数を調整し、ビットの詰まりや手首の骨折につながるキックバックを防ぎます。
 「大型車両による展開が不要になったことで、燃料電池の減価償却費をアルテラ4.2クレジット節約できました。どういたしまして。」</t>
   </si>
   <si>
-    <t>드릴 도구는 프론 슈트(Prawn Suit)를 착용하지 않고도 일반 생존 장비로는 접근할 수 없는 광물층을 채굴할 수 있는 산업용 장비입니다.
+    <t>이 드릴 도구는 프론 슈트(Prawn Suit) 없이도 광물층을 채굴할 수 있는 산업용 장비입니다.
 - 강화된 산업용 다이아몬드 코팅으로 대형 광맥의 분자 결합을 파괴할 수 있습니다.
-- 후방 마이크로 추진기는 드릴의 저항으로 인해 작업자가 뒤로 밀리지 않도록 방지합니다.
-- 가변 토크 모터는 광물 밀도에 따라 회전수를 조절하여 드릴 비트 걸림과 손목 골절을 방지합니다.
-"중장비 차량 투입이 필요 없어짐으로써, 알테라(Alterra)는 연료 전지 감가상각비로 4.2 크레딧을 절약했습니다. 천만에요."</t>
-  </si>
-  <si>
-    <t>Urbšanas instruments ir rūpniecisks instruments, kas spēj iegūt minerālu veidojumus, kurus citādi nevarētu caururbt ar standarta izdzīvošanas aprīkojumu, neizmantojot garneļu kostīmu.
+- 후방 마이크로 스러스터가 드릴의 저항으로 인한 작업자의 반동을 방지합니다.
+- 가변 토크 모터는 광물 밀도에 따라 회전수를 조절하여 드릴 비트 걸림 및 손목 골절을 방지합니다.
+"중장비 차량 투입을 생략함으로써, 알테라(Alterra)는 연료 전지 감가상각비로 4.2 크레딧을 절약했습니다. 천만에요."</t>
+  </si>
+  <si>
+    <t>Urbšanas instruments ir rūpniecisks instruments, kas spēj iegūt minerālu veidojumus bez garneļu uzvalka.
 - Pastiprināts rūpnieciskais dimanta pārklājums ļauj pārraut lielu minerālu vēnu molekulārās saites.
 - Aizmugurējie mikrodzinēji neļauj operatoram tikt atgrūstam atpakaļ urbja pretestības dēļ.
 - Mainīga griezes momenta motors pielāgo apgriezienus minūtē, pamatojoties uz materiāla blīvumu, lai novērstu urbja iesprūšanu un plaukstas locītavas lūzuma atsitienu.
 "Apejot nepieciešamību izmantot smagus transportlīdzekļus, jūs esat ietaupījis Alterra 4,2 kredītpunktus degvielas elementu nolietojumā. Nav par ko."</t>
   </si>
   <si>
-    <t>Gręžimo įrankis yra pramoninis instrumentas, galintis išgauti mineralinius darinius, kurių kitaip neįmanoma pasiekti standartine išgyvenimo įranga, nenaudojant krevečių kostiumo.
+    <t>Gręžimo įrankis yra pramoninis instrumentas, galintis išgauti mineralinius darinius be krevečių kostiumo.
 - Sustiprinta pramoninė deimantinė danga leidžia suardyti didelių mineralinių gyslų molekulinius ryšius.
 - Galiniai mikrovarikliai neleidžia operatoriui būti stumtam atgal dėl grąžto pasipriešinimo.
 - Kintamo sukimo momento variklis reguliuoja apsukas pagal medžiagos tankį, kad būtų išvengta grąžto strigimo ir riešo lūžio atatrankos.
-„Aplenkdami poreikį naudoti sunkiasvores transporto priemones, sutaupėte 4,2 „Alterra“ kreditų už kuro elementų nusidėvėjimą. Prašom.“</t>
-  </si>
-  <si>
-    <t>Boreverktøyet er et industrielt instrument som er i stand til å utvinne mineralformasjoner som ellers er ugjennomtrengelige med standard overlevelsesutstyr, uten bruk av rekedrakt.
+„Aplenkdami poreikį naudoti sunkias transporto priemones, sutaupėte 4,2 „Alterra“ kreditų dėl kuro elementų nusidėvėjimo. Prašom.“</t>
+  </si>
+  <si>
+    <t>Boreverktøyet er et industrielt instrument som er i stand til å utvinne mineralformasjoner uten behov for rekedrakt.
 - Forsterket industrielt diamantbelegg muliggjør brudd i de molekylære bindingene i store mineralårer
-- Bakovervendte mikro-thrustere forhindrer at operatøren drives bakover av borets motstand
+- Bakovervendte mikro-thrustere forhindrer at operatøren blir drevet bakover av borets motstand
 - Variabelt dreiemomentmotor justerer turtallet basert på materialtetthet for å forhindre at boret setter seg fast og tilbakeslag som kan forårsake håndleddsbrudd
-"Ved å omgå behovet for bruk av tunge kjøretøy har du spart Alterra 4,2 studiepoeng i avskrivning av brenselceller. Bare hyggelig."</t>
-  </si>
-  <si>
-    <t>Wiertnica to urządzenie przemysłowe, które umożliwia wydobywanie formacji mineralnych, które są w innym przypadku niedostępne dla standardowego sprzętu survivalowego, bez konieczności użycia kombinezonu Prawn.
-- Wzmocniona przemysłowa powłoka diamentowa umożliwia rozrywanie wiązań molekularnych dużych żył mineralnych.
+"Ved å omgå behovet for tunge kjøretøy har du spart Alterra 4,2 studiepoeng i avskrivning av brenselceller. Bare hyggelig."</t>
+  </si>
+  <si>
+    <t>Wiertnica to urządzenie przemysłowe, które umożliwia wydobywanie minerałów bez konieczności stosowania kombinezonu Prawn.
+- Wzmocniona przemysłowa powłoka diamentowa umożliwia rozrywanie wiązań molekularnych w dużych żyłach mineralnych.
 - Mikrosilniki skierowane do tyłu zapobiegają odpychaniu operatora do tyłu przez opór wiertarki.
-- Silnik o zmiennym momencie obrotowym dostosowuje obroty na podstawie gęstości materiału, aby zapobiec zakleszczaniu się wiertła i odrzutowi nadgarstka.
-„Dzięki wyeliminowaniu konieczności użycia ciężkich pojazdów zaoszczędziłeś firmie Alterra 4,2 punktu na amortyzacji ogniw paliwowych. Zapraszamy”.</t>
-  </si>
-  <si>
-    <t>A ferramenta de perfuração é um instrumento industrial capaz de extrair formações minerais que seriam impenetráveis ​​para equipamentos de sobrevivência padrão, sem a necessidade de um traje PRAWN.
+- Silnik o zmiennym momencie obrotowym dostosowuje prędkość obrotową w oparciu o gęstość materiału, aby zapobiec zakleszczaniu się wiertła i odrzutowi nadgarstka, powodującemu złamanie.
+„Dzięki wyeliminowaniu konieczności użycia ciężkich pojazdów zaoszczędziliście Państwo 4,2 punktu procentowego na amortyzacji ogniw paliwowych w Alterra. Zapraszamy”.</t>
+  </si>
+  <si>
+    <t>A ferramenta de perfuração é um instrumento industrial capaz de extrair formações minerais sem a necessidade de um traje de mergulho.
 - O revestimento reforçado de diamante industrial permite fraturar as ligações moleculares de grandes veios minerais.
 - Micropropulsores traseiros impedem que o operador seja impulsionado para trás pela resistência da perfuração.
 - O motor de torque variável ajusta a rotação por minuto (RPM) com base na densidade do material para evitar o travamento da broca e o recuo que pode causar fraturas no pulso.
 "Ao eliminar a necessidade de veículos pesados, você economizou 4,2 créditos da Alterra em depreciação de células de combustível. De nada."</t>
   </si>
   <si>
-    <t>Instrumentul de foraj este un instrument industrial capabil să extragă formațiuni minerale care altfel ar fi impenetrabile de echipamentul standard de supraviețuire, fără a fi nevoie de utilizarea unui costum Prawn.
-- Stratul industrial de diamant ranforsat permite fracturarea legăturilor moleculare ale venelor minerale mari
-- Micropropulsoarele orientate spre spate împiedică operatorul să fie propulsat înapoi de rezistența forajului
-- Motorul cu cuplu variabil ajustează turația în funcție de densitatea materialului pentru a preveni blocarea burghiului și reculul cauzat de fracturarea încheieturii mâinii
+    <t>Instrumentul de foraj este un instrument industrial capabil să extragă formațiuni minerale fără a fi nevoie de un costum Prawn.
+- Stratul de diamant industrial ranforsat permite fracturarea legăturilor moleculare ale venelor minerale mari
+- Micropropulsoarele orientate spre spate împiedică operatorul să fie propulsat înapoi de rezistența burghiului
+- Motorul cu cuplu variabil ajustează turația în funcție de densitatea materialului pentru a preveni blocarea burghiului și reculul care poate duce la fracturarea încheieturii mâinii
 „Evitând necesitatea utilizării vehiculelor grele, ați economisit 4,2 credite la Alterra în deprecierea pilelor de combustibil. Cu plăcere.”</t>
   </si>
   <si>
-    <t>Буровая установка — это промышленный инструмент, способный добывать минеральные породы, недоступные для стандартного снаряжения для выживания, без использования защитного костюма.
+    <t>Буровая установка — это промышленный инструмент, способный добывать полезные ископаемые без использования защитного костюма.
 - Усиленное промышленное алмазное покрытие позволяет разрушать молекулярные связи крупных минеральных жил.
-- Микро-двигатели, направленные назад, предотвращают отбрасывание оператора назад сопротивлением буровой установки.
+- Микро-подруливающие устройства, направленные назад, предотвращают отбрасывание оператора назад сопротивлением буровой установки.
 - Двигатель с переменным крутящим моментом регулирует обороты в зависимости от плотности материала, предотвращая заклинивание бурового долота и отдачу, приводящую к перелому запястья.
 «Благодаря отсутствию необходимости в использовании тяжелой техники, вы сэкономили Alterra 4,2 кредита на амортизации топливных элементов. Пожалуйста».</t>
   </si>
   <si>
-    <t>Алат за бушење је индустријски инструмент способан за вађење минералних формација које су иначе непробојне стандардном опремом за преживљавање, без употребе одела за шкампе.
+    <t>Алат за бушење је индустријски инструмент способан за вађење минералних формација без потребе за одела за шкампе.
 - Ојачани индустријски дијамантски премаз омогућава разбијање молекуларних веза великих минералних вена
 - Микро-потисници окренути уназад спречавају да отпор бушилице покреће оператера уназад
 - Мотор са променљивим обртним моментом подешава број обртаја на основу густине материјала како би се спречило заглављивање бургије и повратни ударац услед прелома зглоба
 „Заобилажењем потребе за тешким возилима, уштедели сте Алтери 4,2 кредита у амортизацији горивних ћелија. Нема на чему.“</t>
   </si>
   <si>
-    <t>Vŕtací nástroj je priemyselný nástroj schopný ťažiť minerálne formácie, ktoré sú inak nepreniknuteľné štandardným vybavením na prežitie, bez použitia obleku Prawn Suit.
+    <t>Vŕtací nástroj je priemyselný nástroj schopný ťažiť minerálne formácie bez potreby obleku Prawn Suit.
 - Zosilnený priemyselný diamantový povlak umožňuje rozbíjanie molekulárnych väzieb veľkých minerálnych žíl
 - Mikromotory smerujúce dozadu zabraňujú tomu, aby bol operátor hnaný dozadu odporom vrtáka
 - Motor s premenlivým krútiacim momentom upravuje otáčky na základe hustoty materiálu, aby sa zabránilo zaseknutiu vrtáka a spätnému rázu spôsobenému zlomeninou zápästia
-„Vďaka obídeniu potreby nasadenia ťažkých vozidiel ste ušetrili 4,2 kreditu Alterra na odpisoch palivových článkov. Nie je zač.“</t>
-  </si>
-  <si>
-    <t>Vrtalno orodje je industrijski instrument, ki lahko izkoplje mineralne formacije, ki so sicer neprebojne s standardno opremo za preživetje, brez uporabe zaščitne obleke za kozice.
+„Vďaka obídeniu potreby nasadenia ťažkých vozidiel ste ušetrili 4,2 kreditu Alterra na odpisoch palivových článkov. Nemáte začo.“</t>
+  </si>
+  <si>
+    <t>Vrtalno orodje je industrijski instrument, ki lahko izkopava mineralne formacije brez potrebe po obleki Prawn Suit.
 - Ojačana industrijska diamantna prevleka omogoča lomljenje molekularnih vezi velikih mineralnih žil.
 - Mikropotisniki, obrnjeni nazaj, preprečujejo, da bi upor svedra potisnil upravljavca nazaj.
 - Motor s spremenljivim navorom prilagaja število vrtljajev glede na gostoto materiala, da prepreči zatikanje svedra in povratni udarec zaradi zloma zapestja.
 "Z izogibanjem potrebi po uporabi težkih vozil ste prihranili 4,2 kreditne točke Alterra pri amortizaciji gorivnih celic. Ni za kaj."</t>
   </si>
   <si>
-    <t>La herramienta de perforación es un instrumento industrial capaz de extraer formaciones minerales impenetrables para el equipo de supervivencia estándar, sin necesidad de usar un traje Prawn.
+    <t>La herramienta de perforación es un instrumento industrial capaz de extraer formaciones minerales sin necesidad de un traje Prawn.
 - El recubrimiento reforzado de diamante industrial permite fracturar los enlaces moleculares de grandes vetas minerales.
-- Los micropropulsores traseros evitan que el operador retroceda debido a la resistencia de la perforación.
+- Los micropropulsores traseros evitan que el operador sea impulsado hacia atrás por la resistencia de la perforadora.
 - El motor de par variable ajusta las RPM según la densidad del material para evitar que la broca se atasque y el retroceso por fractura de muñeca.
 "Al evitar el despliegue de vehículos pesados, le has ahorrado a Alterra 4.2 créditos en depreciación de celdas de combustible. De nada."</t>
   </si>
   <si>
-    <t>Borrverktyget är ett industriellt instrument som kan utvinna mineralformationer som annars är ogenomträngliga med vanlig överlevnadsutrustning, utan att en räkdräkt behöver användas.
+    <t>Borrverktyget är ett industriellt instrument som kan utvinna mineralformationer utan behov av räkdräkt.
 - Förstärkt industriell diamantbeläggning möjliggör spräckning av de molekylära bindningarna i stora mineralådror
 - Bakåtvända mikromotorer förhindrar att operatören drivs bakåt av borrens motstånd
-- Motor med variabelt vridmoment justerar varvtalet baserat på materialdensitet för att förhindra att borren fastnar och kast som orsakar handledsfrakturer
+- Motor med variabelt vridmoment justerar varvtalet baserat på materialdensitet för att förhindra att borren fastnar och kast som orsakar handledsbrott
 "Genom att kringgå behovet av tunga fordon har du sparat Alterra 4,2 poäng i bränslecellsavskrivning. Varsågod."</t>
   </si>
   <si>
-    <t>เครื่องมือเจาะนี้เป็นเครื่องมืออุตสาหกรรมที่สามารถสกัดแร่ธาตุที่อุปกรณ์เอาชีวิตรอดมาตรฐานไม่สามารถเข้าถึงได้ โดยไม่ต้องใช้ชุด Prawn Suit
+    <t>เครื่องมือเจาะนี้เป็นเครื่องมืออุตสาหกรรมที่สามารถสกัดแร่ธาตุได้โดยไม่ต้องใช้ชุด Prawn Suit
 - การเคลือบเพชรอุตสาหกรรมเสริมแรงช่วยให้สามารถทำลายพันธะโมเลกุลของสายแร่ขนาดใหญ่ได้
-- ไมโครทรัสเตอร์ที่หันไปทางด้านหลังช่วยป้องกันไม่ให้ผู้ใช้งานถูกแรงต้านของสว่านผลักถอยหลัง
+- ไมโครทรัสเตอร์ที่หันไปทางด้านหลังช่วยป้องกันไม่ให้ผู้ปฏิบัติงานถูกแรงต้านของสว่านผลักถอยหลัง
 - มอเตอร์แรงบิดแปรผันจะปรับรอบต่อนาทีตามความหนาแน่นของวัสดุเพื่อป้องกันการติดขัดของดอกสว่านและการดีดกลับที่อาจทำให้ข้อมือหัก
-"ด้วยการหลีกเลี่ยงความจำเป็นในการใช้ยานพาหนะขนาดใหญ่ คุณได้ประหยัดค่าเสื่อมราคาของเซลล์เชื้อเพลิงให้กับ Alterra ไป 4.2 เครดิต ยินดีครับ"</t>
-  </si>
-  <si>
-    <t>Bu matkap, standart hayatta kalma ekipmanlarıyla geçilemeyen mineral oluşumlarını, Prawn Suit giymeye gerek kalmadan çıkarabilen endüstriyel bir alettir.
+"ด้วยการหลีกเลี่ยงความจำเป็นในการใช้งานยานพาหนะขนาดใหญ่ คุณได้ประหยัดเครดิตของ Alterra ไป 4.2 หน่วยในค่าเสื่อมราคาของเซลล์เชื้อเพลิง ยินดีด้วย"</t>
+  </si>
+  <si>
+    <t>Bu matkap, Prawn Suit'e ihtiyaç duymadan mineral oluşumlarını çıkarabilen endüstriyel bir alettir.
 - Güçlendirilmiş endüstriyel elmas kaplama, büyük mineral damarlarının moleküler bağlarını kırmayı sağlar.
 - Arkaya bakan mikro iticiler, operatörün matkabın direncinden dolayı geriye doğru itilmesini önler.
 - Değişken torklu motor, uç sıkışmasını ve bilek kırılmasına neden olabilecek geri tepmeyi önlemek için devir sayısını malzeme yoğunluğuna göre ayarlar.
 "Ağır araç kullanımına gerek kalmadan, Alterra'nın yakıt hücresi amortismanında 4,2 kredi tasarruf sağladınız. Rica ederim."</t>
   </si>
   <si>
-    <t>Буровий інструмент — це промисловий інструмент, здатний видобувати мінеральні утворення, які інакше непроникні для стандартного спорядження для виживання, без використання костюма Prawn Suit.
+    <t>Буровий інструмент — це промисловий інструмент, здатний видобувати мінеральні утворення без використання костюма для креветок.
 - Посилене промислове алмазне покриття дозволяє руйнувати молекулярні зв'язки великих мінеральних жил.
-- Мікродвигуни, спрямовані назад, запобігають відкиданню оператора назад опором бура.
-- Двигун зі змінним крутним моментом регулює оберти залежно від щільності матеріалу, щоб запобігти заклинюванню долота та віддачі від перелому зап'ястя.
+- Мікрорухові механізми, спрямовані назад, запобігають відкиданню оператора назад опором бура.
+- Двигун зі змінним крутним моментом регулює кількість обертів залежно від щільності матеріалу, щоб запобігти заклинюванню долота та віддачі від перелому зап'ястя.
 «Уникаючи необхідності використання важкого транспортного засобу, ви заощадили 4,2 кредити Alterra на амортизації паливних елементів. Будь ласка».</t>
   </si>
   <si>
-    <t>Máy khoan là một thiết bị công nghiệp có khả năng khai thác các mỏ khoáng sản mà các thiết bị sinh tồn tiêu chuẩn không thể tiếp cận được, mà không cần đến bộ đồ lặn Prawn Suit.
+    <t>Máy khoan là một thiết bị công nghiệp có khả năng khai thác khoáng sản mà không cần đến bộ đồ bảo hộ Prawn Suit.
 - Lớp phủ kim cương công nghiệp gia cường cho phép phá vỡ các liên kết phân tử của các mạch khoáng lớn
 - Các động cơ đẩy siêu nhỏ hướng về phía sau ngăn người vận hành bị đẩy lùi do lực cản của mũi khoan
 - Động cơ mô-men xoắn biến đổi điều chỉnh tốc độ quay dựa trên mật độ vật liệu để ngăn ngừa kẹt mũi khoan và hiện tượng giật ngược gây gãy cổ tay
-"Bằng cách bỏ qua nhu cầu sử dụng phương tiện hạng nặng, bạn đã tiết kiệm được cho Alterra 4,2 tín dụng chi phí khấu hao pin nhiên liệu. Không có gì."</t>
+"Bằng cách bỏ qua nhu cầu triển khai phương tiện hạng nặng, bạn đã tiết kiệm cho Alterra 4,2 tín dụng chi phí khấu hao pin nhiên liệu. Không có gì."</t>
   </si>
   <si>
     <t>DrillTool.AutoCollectLabel</t>
@@ -1467,7 +1477,7 @@
     <t>Automatsko prikupljanje</t>
   </si>
   <si>
-    <t>Automatické vyzvednutí</t>
+    <t>Automatický sběr</t>
   </si>
   <si>
     <t>Automatisk afhentning</t>
@@ -1555,7 +1565,7 @@
 Disabled by default.</t>
   </si>
   <si>
-    <t>Indien geaktiveer, sal die ontginde hulpbronne outomaties die speler se inventaris binnegaan, soortgelyk aan die gedrag van 'n Garnaleboorarm.
+    <t>Indien geaktiveer, sal die ontginde hulpbronne outomaties die speler se inventaris binnegaan, soortgelyk aan die gedrag van 'n Garnaalboorarm.
 Standaard gedeaktiveer.</t>
   </si>
   <si>
@@ -1579,8 +1589,8 @@
 Onemogućeno prema zadanim postavkama.</t>
   </si>
   <si>
-    <t>Pokud je tato možnost povolena, vytěžené zdroje se automaticky dostanou do hráčova inventáře, podobně jako se chová rameno pro vrtání krevet.
-Ve výchozím nastavení je tato možnost zakázána.</t>
+    <t>Pokud je tato funkce aktivní, vytěžené suroviny se automaticky uloží do hráčova inventáře, porodně jako funguje Vrtací paže P.R.A.W.N.
+Ve výchozím nastavení tato možnost není aktivní.</t>
   </si>
   <si>
     <t>Hvis aktiveret, vil de udvundne ressourcer automatisk blive tilføjet til spillerens inventar, svarende til en rejeborearms opførsel.
@@ -1666,7 +1676,7 @@
 Predvolene vypnuté.</t>
   </si>
   <si>
-    <t>Če je omogočeno, bodo izkopani viri samodejno vstopili v igralčev inventar, podobno kot se obnaša roka za vrtanje kozic.
+    <t>Če je omogočeno, bodo izkopani viri samodejno dodani v igralčev inventar, podobno kot se obnaša roka za vrtanje kozic.
 Privzeto onemogočeno.</t>
   </si>
   <si>
@@ -2932,1129 +2942,1129 @@
         <v>183</v>
       </c>
       <c r="AF5" s="14" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="AG5" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AH5" s="14" t="s">
         <v>180</v>
       </c>
       <c r="AI5" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AJ5" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AK5" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL5" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM5" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN5" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Z6" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AC6" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AD6" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AF6" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG6" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AH6" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AI6" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AJ6" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AK6" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL6" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM6" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN6" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R7" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S7" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="W7" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="X7" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Y7" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Z7" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA7" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AB7" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AC7" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AD7" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AE7" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AF7" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG7" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AH7" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AI7" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AJ7" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AK7" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL7" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM7" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN7" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Y8" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z8" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA8" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AC8" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AD8" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AE8" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AF8" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AH8" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AI8" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AJ8" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AK8" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL8" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM8" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN8" s="17" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="R9" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="S9" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="U9" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="V9" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="W9" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X9" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Y9" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Z9" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA9" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AB9" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AD9" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AE9" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AF9" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG9" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AH9" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AI9" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AJ9" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AK9" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL9" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM9" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN9" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="W10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="X10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="Y10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="Z10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AA10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AB10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AC10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AD10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AE10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AF10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AH10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AI10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AJ10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AK10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AL10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AM10" s="8" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="AN10" s="17" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R11" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="S11" s="14" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U11" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="V11" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="W11" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="X11" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Y11" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Z11" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA11" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AB11" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AD11" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AE11" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AF11" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG11" s="14" t="s">
-        <v>259</v>
+        <v>354</v>
       </c>
       <c r="AH11" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AI11" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AJ11" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AK11" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL11" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AM11" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN11" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M12" s="21" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N12" s="21" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="P12" s="21" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q12" s="21" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="R12" s="21" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="S12" s="21" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T12" s="21" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U12" s="21" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V12" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W12" s="21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="X12" s="21" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Y12" s="21" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Z12" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AA12" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AB12" s="21" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AC12" s="21" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AD12" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AE12" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AF12" s="21" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG12" s="21" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AH12" s="21" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AI12" s="21" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AJ12" s="21" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AK12" s="21" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AL12" s="21" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AM12" s="21" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN12" s="22" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="23" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E13" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>400</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="K13" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="F13" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>396</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>398</v>
-      </c>
-      <c r="J13" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="K13" s="23" t="s">
-        <v>391</v>
-      </c>
       <c r="L13" s="23" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="N13" s="23" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="O13" s="23" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="P13" s="23" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="R13" s="23" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="T13" s="23" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="U13" s="23" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="V13" s="24" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="W13" s="24" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="X13" s="24" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Y13" s="24" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Z13" s="24" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AA13" s="24" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AB13" s="24" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AC13" s="24" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AD13" s="24" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AE13" s="24" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AF13" s="24" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG13" s="24" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AH13" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AI13" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AJ13" s="24" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AK13" s="24" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AL13" s="24" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AM13" s="24" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN13" s="24" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N14" s="23" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O14" s="23" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P14" s="23" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="Q14" s="23" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="R14" s="23" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="S14" s="23" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="T14" s="23" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="U14" s="23" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="V14" s="24" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="W14" s="24" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="X14" s="24" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="Y14" s="24" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="Z14" s="24" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AA14" s="24" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AB14" s="24" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AC14" s="24" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AD14" s="24" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AE14" s="24" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AF14" s="24" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AG14" s="24" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AH14" s="24" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AI14" s="24" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AJ14" s="24" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AK14" s="24" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AL14" s="24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AM14" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AN14" s="24" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15">

--- a/translate.xlsx
+++ b/translate.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="604">
   <si>
     <t>Keycode</t>
   </si>
@@ -133,7 +133,7 @@
     <t>Vietnamese</t>
   </si>
   <si>
-    <t>README</t>
+    <t>READ ME</t>
   </si>
   <si>
     <t>en</t>
@@ -388,12 +388,12 @@
   </si>
   <si>
     <t>每次开采资源矿藏都会消耗电池电量。
-最多需要开采 320 次才能完全摧毁一个矿藏。
+最多需要开采 320 次才能彻底摧毁一个矿藏。
 只有在开采大型资源矿藏时才会消耗能量。</t>
   </si>
   <si>
     <t>每次開採資源礦藏都會消耗電池電量。
-最多需要開採 320 次才能完全摧毀一個礦藏。
+最多需要開採 320 次才能徹底摧毀一個礦藏。
 只有在開採大型資源礦藏時才會消耗能量。</t>
   </si>
   <si>
@@ -574,9 +574,6 @@
     <t>Hitinterval</t>
   </si>
   <si>
-    <t>Interval raken</t>
-  </si>
-  <si>
     <t>Tabamuse intervall</t>
   </si>
   <si>
@@ -780,7 +777,7 @@
 При использовании значения по умолчанию скорость добычи будет соответствовать скорости буровой руки Prawn Suit.</t>
   </si>
   <si>
-    <t>Интервал поготка на лежишту ресурса. Мање је брже. Користите подразумевану вредност да бисте ускладили брзину рударења са бушаћом руком за праун суит.</t>
+    <t>Интервал поготка на лежишту ресурса. Мање је брже. Користите подразумевану вредност да бисте ускладили брзину рударења бушилице Prawn Suit.</t>
   </si>
   <si>
     <t>Interval ťažby na ložisku surovín. Menšie je rýchlejšie. Použite predvolenú hodnotu, ktorá zodpovedá rýchlosti ťažby vrtného ramena Prawn Suit.</t>
@@ -1190,9 +1187,6 @@
   </si>
   <si>
     <t>Сверло</t>
-  </si>
-  <si>
-    <t>Orodje za vrtanje</t>
   </si>
   <si>
     <t>Matkap Aleti</t>
@@ -1268,7 +1262,7 @@
 - Versterkte industriële diamantcoating maakt het mogelijk om de moleculaire bindingen van grote minerale aders te verbreken.
 - Naar achteren gerichte micro-stuwraketten voorkomen dat de operator door de weerstand van de boor naar achteren wordt geduwd.
 - De motor met variabel koppel past het toerental aan op basis van de materiaaldichtheid om vastlopen van de boor en terugslag die tot polsfracturen kan leiden te voorkomen.
-"Door de noodzaak van zwaar transport te omzeilen, heeft u 4,2 Alterra-credits bespaard op de afschrijving van de brandstofcel. Graag gedaan."</t>
+"Door de noodzaak van zwaar transport te omzeilen, heeft u Alterra 4,2 credits bespaard op de afschrijving van de brandstofcel. Graag gedaan."</t>
   </si>
   <si>
     <t>See puurimisvahend on tööstuslik instrument, mis on võimeline mineraalformatsioone kaevandama ilma krevetiülikonnata.
@@ -1365,8 +1359,8 @@
     <t>Wiertnica to urządzenie przemysłowe, które umożliwia wydobywanie minerałów bez konieczności stosowania kombinezonu Prawn.
 - Wzmocniona przemysłowa powłoka diamentowa umożliwia rozrywanie wiązań molekularnych w dużych żyłach mineralnych.
 - Mikrosilniki skierowane do tyłu zapobiegają odpychaniu operatora do tyłu przez opór wiertarki.
-- Silnik o zmiennym momencie obrotowym dostosowuje prędkość obrotową w oparciu o gęstość materiału, aby zapobiec zakleszczaniu się wiertła i odrzutowi nadgarstka, powodującemu złamanie.
-„Dzięki wyeliminowaniu konieczności użycia ciężkich pojazdów zaoszczędziliście Państwo 4,2 punktu procentowego na amortyzacji ogniw paliwowych w Alterra. Zapraszamy”.</t>
+- Silnik o zmiennym momencie obrotowym dostosowuje obroty na podstawie gęstości materiału, aby zapobiec zakleszczaniu się wiertła i odrzutowi nadgarstka.
+„Dzięki wyeliminowaniu konieczności użycia ciężkich pojazdów zaoszczędziliście Państwo 4,2 punktu kredytowego na amortyzacji ogniw paliwowych w Alterra. Zapraszamy”.</t>
   </si>
   <si>
     <t>A ferramenta de perfuração é um instrumento industrial capaz de extrair formações minerais sem a necessidade de um traje de mergulho.
@@ -1401,7 +1395,7 @@
 - Zosilnený priemyselný diamantový povlak umožňuje rozbíjanie molekulárnych väzieb veľkých minerálnych žíl
 - Mikromotory smerujúce dozadu zabraňujú tomu, aby bol operátor hnaný dozadu odporom vrtáka
 - Motor s premenlivým krútiacim momentom upravuje otáčky na základe hustoty materiálu, aby sa zabránilo zaseknutiu vrtáka a spätnému rázu spôsobenému zlomeninou zápästia
-„Vďaka obídeniu potreby nasadenia ťažkých vozidiel ste ušetrili 4,2 kreditu Alterra na odpisoch palivových článkov. Nemáte začo.“</t>
+„Vďaka obídeniu potreby nasadenia ťažkých vozidiel ste ušetrili 4,2 kreditu Alterra na odpisoch palivových článkov. Nie je zač.“</t>
   </si>
   <si>
     <t>Vrtalno orodje je industrijski instrument, ki lahko izkopava mineralne formacije brez potrebe po obleki Prawn Suit.
@@ -1442,7 +1436,7 @@
     <t>Буровий інструмент — це промисловий інструмент, здатний видобувати мінеральні утворення без використання костюма для креветок.
 - Посилене промислове алмазне покриття дозволяє руйнувати молекулярні зв'язки великих мінеральних жил.
 - Мікрорухові механізми, спрямовані назад, запобігають відкиданню оператора назад опором бура.
-- Двигун зі змінним крутним моментом регулює кількість обертів залежно від щільності матеріалу, щоб запобігти заклинюванню долота та віддачі від перелому зап'ястя.
+- Двигун зі змінним крутним моментом регулює швидкість обертання залежно від щільності матеріалу, щоб запобігти заклинюванню долота та віддачі від перелому зап'ястя.
 «Уникаючи необхідності використання важкого транспортного засобу, ви заощадили 4,2 кредити Alterra на амортизації паливних елементів. Будь ласка».</t>
   </si>
   <si>
@@ -1561,147 +1555,569 @@
     <t>DrillTool.AutoCollectTooltip</t>
   </si>
   <si>
-    <t>If enabled, then the mined resources will automatically enter the player's inventory, similar to the behaviour of a Prawn Drill Arm.
-Disabled by default.</t>
-  </si>
-  <si>
-    <t>Indien geaktiveer, sal die ontginde hulpbronne outomaties die speler se inventaris binnegaan, soortgelyk aan die gedrag van 'n Garnaalboorarm.
-Standaard gedeaktiveer.</t>
-  </si>
-  <si>
-    <t>Ако е активирано, добитите ресурси автоматично ще влязат в инвентара на играча, подобно на поведението на ръката за сондажи за скариди.
-Деактивирано по подразбиране.</t>
-  </si>
-  <si>
-    <t>Si està activat, els recursos extrets entraran automàticament a l'inventari del jugador, de manera similar al comportament d'un Prawn Drill Arm.
-Desactivat per defecte.</t>
-  </si>
-  <si>
-    <t>启用后，开采出的资源将自动进入玩家的物品栏，类似于虾式钻臂的操作。
-默认禁用。</t>
-  </si>
-  <si>
-    <t>啟用後，開採的資源將自動進入玩家的物品欄，類似蝦式鑽臂的操作。
-預設禁用。</t>
-  </si>
-  <si>
-    <t>Ako je omogućeno, iskopani resursi će automatski ući u inventar igrača, slično ponašanju ruke za bušenje kozica.
-Onemogućeno prema zadanim postavkama.</t>
+    <t>If enabled, then the mined resources will automatically enter the player's inventory, similar to the behaviour of a Prawn Drill Arm.</t>
+  </si>
+  <si>
+    <t>Indien geaktiveer, sal die ontginde hulpbronne outomaties die speler se inventaris binnegaan, soortgelyk aan die gedrag van 'n Garnaleboorarm.</t>
+  </si>
+  <si>
+    <t>Ако е активирано, добитите ресурси автоматично ще влязат в инвентара на играча, подобно на поведението на ръката за сондажи за скариди.</t>
+  </si>
+  <si>
+    <t>Si està activat, els recursos extrets entraran automàticament a l'inventari del jugador, de manera similar al comportament d'un braç perforador de gambes.</t>
+  </si>
+  <si>
+    <t>如果启用，则开采的资源将自动进入玩家的物品栏，类似于虾式钻臂的行为。</t>
+  </si>
+  <si>
+    <t>如果啟用，則開採的資源將自動進入玩家的物品欄，類似於蝦式鑽臂的行為。</t>
+  </si>
+  <si>
+    <t>Ako je omogućeno, iskopani resursi će automatski ući u igračev inventar, slično ponašanju ruke za bušenje kozica.</t>
   </si>
   <si>
     <t>Pokud je tato funkce aktivní, vytěžené suroviny se automaticky uloží do hráčova inventáře, porodně jako funguje Vrtací paže P.R.A.W.N.
 Ve výchozím nastavení tato možnost není aktivní.</t>
   </si>
   <si>
-    <t>Hvis aktiveret, vil de udvundne ressourcer automatisk blive tilføjet til spillerens inventar, svarende til en rejeborearms opførsel.
-Deaktiveret som standard.</t>
-  </si>
-  <si>
-    <t>Indien ingeschakeld, komen de gewonnen grondstoffen automatisch in de inventaris van de speler terecht, vergelijkbaar met het gedrag van een Prawn Drill Arm.
-Standaard uitgeschakeld.</t>
-  </si>
-  <si>
-    <t>Kui see on lubatud, siis kaevandatud ressursid lisatakse automaatselt mängija inventari, sarnaselt krevetipuurvarda käitumisele.
-Vaikimisi keelatud.</t>
-  </si>
-  <si>
-    <t>Jos käytössä, louhitut resurssit siirtyvät automaattisesti pelaajan tavaraluetteloon samalla tavalla kuin katkarapuporakone.
-Oletusarvoisesti pois käytöstä.</t>
-  </si>
-  <si>
-    <t>Si cette option est activée, les ressources extraites seront automatiquement ajoutées à l'inventaire du joueur, comme le ferait un bras de forage Prawn.
-Désactivée par défaut.</t>
-  </si>
-  <si>
-    <t>Ist diese Option aktiviert, gelangen die abgebauten Ressourcen automatisch in das Inventar des Spielers, ähnlich wie beim Prawn-Bohrarm. Standardmäßig deaktiviert.</t>
-  </si>
-  <si>
-    <t>Εάν είναι ενεργοποιημένη, τότε οι εξορυγμένοι πόροι θα εισέλθουν αυτόματα στο απόθεμα του παίκτη, παρόμοια με τη συμπεριφορά ενός βραχίονα τρυπανιού γαρίδας.
-Απενεργοποιημένο από προεπιλογή.</t>
-  </si>
-  <si>
-    <t>Ha engedélyezve van, akkor a kibányászott erőforrások automatikusan bekerülnek a játékos felszerelésébe, hasonlóan a garnélarák-fúró kar viselkedéséhez.
-Alapértelmezés szerint letiltva.</t>
-  </si>
-  <si>
-    <t>Má tá sé cumasaithe, cuirfear na hacmhainní mianadóireachta isteach i bhfardal an imreora go huathoibríoch, cosúil le hiompar Lámh Druileála Cloicheán.
-Díchumasaithe de réir réamhshocraithe.</t>
-  </si>
-  <si>
-    <t>Se abilitata, le risorse estratte entreranno automaticamente nell'inventario del giocatore, in modo simile al comportamento di un braccio perforatore Prawn.
-Disabilitata per impostazione predefinita.</t>
-  </si>
-  <si>
-    <t>有効にすると、採掘された資源はプラウンドリルアームと同様に、自動的にプレイヤーのインベントリに格納されます。
-デフォルトでは無効になっています。</t>
-  </si>
-  <si>
-    <t>이 기능을 활성화하면 채굴한 자원이 프론 드릴 암처럼 자동으로 플레이어의 인벤토리에 추가됩니다.
-기본적으로 비활성화되어 있습니다.</t>
-  </si>
-  <si>
-    <t>Ja iespējots, iegūtie resursi automātiski nonāks spēlētāja inventārā, līdzīgi kā garneļu urbšanas roka.
-Pēc noklusējuma atspējots.</t>
-  </si>
-  <si>
-    <t>Jei įjungta, iškasti ištekliai automatiškai pateks į žaidėjo inventorių, panašiai kaip krevečių grąžto rankos veikimas.
-Pagal numatytuosius nustatymus išjungta.</t>
-  </si>
-  <si>
-    <t>Hvis aktivert, vil de utvunnede ressursene automatisk bli lagt inn i spillerens inventar, på samme måte som en rekeborearm oppfører seg.
-Deaktivert som standard.</t>
-  </si>
-  <si>
-    <t>Jeśli ta opcja jest włączona, wydobyte surowce automatycznie trafią do ekwipunku gracza, podobnie jak ramię wiertnicze do krewetek.
-Domyślnie wyłączone.</t>
-  </si>
-  <si>
-    <t>Se ativado, os recursos extraídos entrarão automaticamente no inventário do jogador, de forma semelhante ao comportamento do Braço Perfurador do Prawn.
-Desativado por padrão.</t>
-  </si>
-  <si>
-    <t>Dacă este activată, resursele extrase vor intra automat în inventarul jucătorului, similar comportamentului unui braț de foraj pentru creveți.
-Dezactivată în mod implicit.</t>
-  </si>
-  <si>
-    <t>Если эта функция включена, добытые ресурсы будут автоматически попадать в инвентарь игрока, подобно работе буровой установки Prawn Drill Arm.
-По умолчанию отключено.</t>
-  </si>
-  <si>
-    <t>Ако је омогућено, ископани ресурси ће аутоматски ући у инвентар играча, слично понашању руке за бушење шкампа.
-Подразумевано онемогућено.</t>
-  </si>
-  <si>
-    <t>Ak je povolené, vyťažené zdroje sa automaticky dostanú do hráčovho inventára, podobne ako sa správa rameno na vŕtanie kreviet.
-Predvolene vypnuté.</t>
-  </si>
-  <si>
-    <t>Če je omogočeno, bodo izkopani viri samodejno dodani v igralčev inventar, podobno kot se obnaša roka za vrtanje kozic.
-Privzeto onemogočeno.</t>
-  </si>
-  <si>
-    <t>Si está activada, los recursos extraídos se añadirán automáticamente al inventario del jugador, de forma similar al comportamiento del Brazo Perforador de Gambas.
-Desactivada por defecto.</t>
-  </si>
-  <si>
-    <t>Om aktiverat kommer de utvunna resurserna automatiskt att läggas in i spelarens inventarieförråd, ungefär som en räkborrarm beter sig.
-Inaktiverad som standard.</t>
-  </si>
-  <si>
-    <t>หากเปิดใช้งาน ทรัพยากรที่ขุดได้จะเข้าสู่คลังของผู้เล่นโดยอัตโนมัติ คล้ายกับพฤติกรรมของแขนเจาะกุ้ง
-ปิดใช้งานโดยค่าเริ่มต้น</t>
-  </si>
-  <si>
-    <t>Etkinleştirilirse, çıkarılan kaynaklar, bir Karides Matkap Kolunun davranışına benzer şekilde, otomatik olarak oyuncunun envanterine girer.
-Varsayılan olarak devre dışıdır.</t>
-  </si>
-  <si>
-    <t>Якщо ввімкнено, то видобуті ресурси автоматично потраплятимуть до інвентарю гравця, подібно до поведінки Креветкової бурильної руки.
-За замовчуванням вимкнено.</t>
-  </si>
-  <si>
-    <t>Nếu được kích hoạt, tài nguyên khai thác được sẽ tự động được chuyển vào kho đồ của người chơi, tương tự như hoạt động của Cánh tay khoan tôm.
-Mặc định là tắt.</t>
+    <t>Hvis aktiveret, vil de udvundne ressourcer automatisk blive indført i spillerens inventar, svarende til en rejeborearms opførsel.</t>
+  </si>
+  <si>
+    <t>Indien ingeschakeld, komen de gewonnen grondstoffen automatisch in de inventaris van de speler terecht, vergelijkbaar met het gedrag van een Prawn Drill Arm.</t>
+  </si>
+  <si>
+    <t>Kui see on lubatud, lisatakse kaevandatud ressursid automaatselt mängija inventari, sarnaselt krevetipuurija käe käitumisele.</t>
+  </si>
+  <si>
+    <t>Jos tämä on käytössä, louhitut resurssit siirtyvät automaattisesti pelaajan tavaraluetteloon samalla tavalla kuin katkarapuporavarsi.</t>
+  </si>
+  <si>
+    <t>Si cette option est activée, les ressources extraites seront automatiquement ajoutées à l'inventaire du joueur, comme le ferait un bras de forage Prawn.</t>
+  </si>
+  <si>
+    <t>Ist diese Option aktiviert, gelangen die abgebauten Ressourcen automatisch in das Inventar des Spielers, ähnlich wie beim Prawn-Bohrarm.</t>
+  </si>
+  <si>
+    <t>Εάν είναι ενεργοποιημένο, τότε οι εξορυγμένοι πόροι θα εισέλθουν αυτόματα στο απόθεμα του παίκτη, παρόμοια με τη συμπεριφορά ενός βραχίονα τρυπανιού γαρίδας.</t>
+  </si>
+  <si>
+    <t>Ha engedélyezve van, akkor a kibányászott erőforrások automatikusan bekerülnek a játékos felszerelésébe, hasonlóan egy garnélarák-fúró kar viselkedéséhez.</t>
+  </si>
+  <si>
+    <t>Má tá sé cumasaithe, cuirfear na hacmhainní mianadóireachta isteach i bhfardal an imreora go huathoibríoch, cosúil le hiompar Lámh Druileála Cloicheán.</t>
+  </si>
+  <si>
+    <t>Se abilitata, le risorse estratte entreranno automaticamente nell'inventario del giocatore, in modo simile al comportamento di un braccio perforatore Prawn.</t>
+  </si>
+  <si>
+    <t>有効にすると、採掘された資源は、プラウンドリルアームの動作と同様に、自動的にプレイヤーのインベントリに追加されます。</t>
+  </si>
+  <si>
+    <t>이 기능을 활성화하면 채굴된 자원이 새우 드릴 팔처럼 자동으로 플레이어의 인벤토리에 들어갑니다.</t>
+  </si>
+  <si>
+    <t>Ja šī opcija ir iespējota, iegūtie resursi automātiski nonāks spēlētāja inventārā, līdzīgi kā garneļu urbšanas roka.</t>
+  </si>
+  <si>
+    <t>Jei įjungta, iškasti ištekliai automatiškai pateks į žaidėjo inventorių, panašiai kaip krevečių grąžto ranka.</t>
+  </si>
+  <si>
+    <t>Hvis aktivert, vil de utvunnede ressursene automatisk bli lagt inn i spillerens inventar, på samme måte som en rekeborearm oppfører seg.</t>
+  </si>
+  <si>
+    <t>Jeśli ta opcja jest włączona, wydobyte surowce automatycznie trafią do ekwipunku gracza, podobnie jak ramię wiertnicze do krewetek.</t>
+  </si>
+  <si>
+    <t>Se ativada, a função permite que os recursos extraídos entrem automaticamente no inventário do jogador, de forma semelhante ao funcionamento do Braço Perfurador do Camarão.</t>
+  </si>
+  <si>
+    <t>Dacă este activată, resursele extrase vor intra automat în inventarul jucătorului, similar cu comportamentul unui braț de foraj pentru creveți.</t>
+  </si>
+  <si>
+    <t>Если эта функция включена, добытые ресурсы будут автоматически поступать в инвентарь игрока, подобно работе буровой установки Prawn Drill Arm.</t>
+  </si>
+  <si>
+    <t>Ако је омогућено, ископани ресурси ће аутоматски ући у инвентар играча, слично понашању руке за бушење шкампа.</t>
+  </si>
+  <si>
+    <t>Ak je táto možnosť povolená, vyťažené zdroje sa automaticky dostanú do hráčovho inventára, podobne ako sa správa rameno na vŕtanie kreviet.</t>
+  </si>
+  <si>
+    <t>Če je omogočeno, se bodo izkopani viri samodejno dodali v igralčev inventar, podobno kot se obnaša roka za vrtanje kozic.</t>
+  </si>
+  <si>
+    <t>Si está habilitada, los recursos extraídos entrarán automáticamente en el inventario del jugador, de forma similar al comportamiento de un Brazo Perforador de Gambas.</t>
+  </si>
+  <si>
+    <t>Om aktiverat kommer de utvunna resurserna automatiskt att läggas in i spelarens inventarieförråd, ungefär som en räkborrarm beter sig.</t>
+  </si>
+  <si>
+    <t>หากเปิดใช้งาน ทรัพยากรที่ขุดได้จะเข้าสู่ช่องเก็บของของผู้เล่นโดยอัตโนมัติ คล้ายกับพฤติกรรมของแขนเจาะกุ้ง</t>
+  </si>
+  <si>
+    <t>Etkinleştirilirse, çıkarılan kaynaklar, bir Karides Matkap Kolunun davranışına benzer şekilde, otomatik olarak oyuncunun envanterine girer.</t>
+  </si>
+  <si>
+    <t>Якщо ввімкнено, то видобуті ресурси автоматично потраплятимуть до інвентарю гравця, подібно до поведінки руки для свердла креветок.</t>
+  </si>
+  <si>
+    <t>Nếu được kích hoạt, các tài nguyên khai thác được sẽ tự động được chuyển vào kho đồ của người chơi, tương tự như cách hoạt động của Cánh tay khoan tôm.</t>
+  </si>
+  <si>
+    <t>OreBomb</t>
+  </si>
+  <si>
+    <t>Ore Bomb</t>
+  </si>
+  <si>
+    <t>Ertsbom</t>
+  </si>
+  <si>
+    <t>Рудна бомба</t>
+  </si>
+  <si>
+    <t>Bomba de mineral</t>
+  </si>
+  <si>
+    <t>矿石炸弹</t>
+  </si>
+  <si>
+    <t>礦石炸彈</t>
+  </si>
+  <si>
+    <t>Rudna bomba</t>
+  </si>
+  <si>
+    <t>Rudná bomba</t>
+  </si>
+  <si>
+    <t>Malmbombe</t>
+  </si>
+  <si>
+    <t>Maagipomm</t>
+  </si>
+  <si>
+    <t>Malmipommi</t>
+  </si>
+  <si>
+    <t>Bombe à minerai</t>
+  </si>
+  <si>
+    <t>Erzbombe</t>
+  </si>
+  <si>
+    <t>Βόμβα μεταλλεύματος</t>
+  </si>
+  <si>
+    <t>Ércbomba</t>
+  </si>
+  <si>
+    <t>Buama Méine</t>
+  </si>
+  <si>
+    <t>Bomba di minerale</t>
+  </si>
+  <si>
+    <t>鉱石爆弾</t>
+  </si>
+  <si>
+    <t>광석 폭탄</t>
+  </si>
+  <si>
+    <t>Rūdas bumba</t>
+  </si>
+  <si>
+    <t>Rūdos bomba</t>
+  </si>
+  <si>
+    <t>Bomba rudowa</t>
+  </si>
+  <si>
+    <t>Bomba de Minério</t>
+  </si>
+  <si>
+    <t>Bombă cu minereu</t>
+  </si>
+  <si>
+    <t>Рудная бомба</t>
+  </si>
+  <si>
+    <t>Malmbomb</t>
+  </si>
+  <si>
+    <t>ระเบิดแร่</t>
+  </si>
+  <si>
+    <t>Cevher Bombası</t>
+  </si>
+  <si>
+    <t>Bom quặng</t>
+  </si>
+  <si>
+    <t>Tooltip_OreBomb</t>
+  </si>
+  <si>
+    <t>Drop this by a large resource to explode it.</t>
+  </si>
+  <si>
+    <t>Laat dit by 'n groot hulpbron val om dit te laat ontplof.</t>
+  </si>
+  <si>
+    <t>Пуснете това от голям ресурс, за да го взривите.</t>
+  </si>
+  <si>
+    <t>Deixa caure això al costat d'un recurs gran per fer-lo explotar.</t>
+  </si>
+  <si>
+    <t>把它扔到大型资源附近就能引爆。</t>
+  </si>
+  <si>
+    <t>把它丟到大型資源附近就能引爆。</t>
+  </si>
+  <si>
+    <t>Ispustite ovo za veliki resurs da biste ga eksplodirali.</t>
+  </si>
+  <si>
+    <t>Pro explozi to upusťte o velký zdroj.</t>
+  </si>
+  <si>
+    <t>Smid dette ved siden af ​​en stor ressource for at få det til at eksplodere.</t>
+  </si>
+  <si>
+    <t>Laat dit bij een grote grondstof vallen om het te laten exploderen.</t>
+  </si>
+  <si>
+    <t>Plahvatamiseks kukuta see suure ressursi juures.</t>
+  </si>
+  <si>
+    <t>Pudota tämä suuren resurssin viereen räjäyttääksesi sen.</t>
+  </si>
+  <si>
+    <t>Déposez ceci à proximité d'une ressource importante pour le faire exploser.</t>
+  </si>
+  <si>
+    <t>Lass es neben einer großen Ressource explodieren.</t>
+  </si>
+  <si>
+    <t>Ρίξτε το δίπλα σε έναν μεγάλο πόρο για να το εκραγεί.</t>
+  </si>
+  <si>
+    <t>Egy nagy erőforrás eldobásával felrobbanthatod.</t>
+  </si>
+  <si>
+    <t>Scaoil seo le hacmhainn mhór chun é a phléascadh.</t>
+  </si>
+  <si>
+    <t>Lascia cadere questo oggetto vicino a una grande risorsa per farlo esplodere.</t>
+  </si>
+  <si>
+    <t>これを大きな資源の近くに落とすと爆発します。</t>
+  </si>
+  <si>
+    <t>이것을 큰 자원 근처에 떨어뜨리면 폭발합니다.</t>
+  </si>
+  <si>
+    <t>Nometiet to pie liela resursa, lai to eksplodētu.</t>
+  </si>
+  <si>
+    <t>Numeskite tai dideliu ištekliumi, kad jį susprogdintumėte.</t>
+  </si>
+  <si>
+    <t>Slipp dette av en stor ressurs for å sprenge det.</t>
+  </si>
+  <si>
+    <t>Zrzuć to w pobliże większego obiektu, aby eksplodowało.</t>
+  </si>
+  <si>
+    <t>Solte isso perto de um recurso grande para explodi-lo.</t>
+  </si>
+  <si>
+    <t>Aruncă asta lângă o resursă mare pentru a o exploda.</t>
+  </si>
+  <si>
+    <t>Сбросьте это рядом с крупным ресурсом, чтобы оно взорвалось.</t>
+  </si>
+  <si>
+    <t>Испустите ово поред великог ресурса да бисте га експлодирали.</t>
+  </si>
+  <si>
+    <t>Zhoďte to o veľký zdroj, aby ste to explodovali.</t>
+  </si>
+  <si>
+    <t>Spusti to za velik vir, da ga razstreliš.</t>
+  </si>
+  <si>
+    <t>Suéltalo cerca de un recurso grande para hacerlo explotar.</t>
+  </si>
+  <si>
+    <t>Släpp detta vid en stor resurs för att explodera det.</t>
+  </si>
+  <si>
+    <t>โยนสิ่งนี้ลงใกล้กับทรัพยากรขนาดใหญ่เพื่อทำให้มันระเบิด</t>
+  </si>
+  <si>
+    <t>Bunu büyük bir kaynağın yanına bırakın, patlatın.</t>
+  </si>
+  <si>
+    <t>Киньте це за допомогою великого ресурсу, щоб підірвати його.</t>
+  </si>
+  <si>
+    <t>Thả vật này xuống gần một nguồn tài nguyên lớn để làm nó phát nổ.</t>
+  </si>
+  <si>
+    <t>DrillTool.CreatureDamageLabel</t>
+  </si>
+  <si>
+    <t>Creature Damage</t>
+  </si>
+  <si>
+    <t>Skepselskade</t>
+  </si>
+  <si>
+    <t>Щети от същества</t>
+  </si>
+  <si>
+    <t>Dany de criatura</t>
+  </si>
+  <si>
+    <t>生物伤害</t>
+  </si>
+  <si>
+    <t>生物傷害</t>
+  </si>
+  <si>
+    <t>Šteta stvorenja</t>
+  </si>
+  <si>
+    <t>Poškození tvorů</t>
+  </si>
+  <si>
+    <t>Skade på væsen</t>
+  </si>
+  <si>
+    <t>Schade door wezens</t>
+  </si>
+  <si>
+    <t>Olendi kahjustus</t>
+  </si>
+  <si>
+    <t>Olentojen vauriot</t>
+  </si>
+  <si>
+    <t>Dégâts de créature</t>
+  </si>
+  <si>
+    <t>Kreaturenschaden</t>
+  </si>
+  <si>
+    <t>Ζημιά από πλάσματα</t>
+  </si>
+  <si>
+    <t>Lénykár</t>
+  </si>
+  <si>
+    <t>Damáiste Créatúir</t>
+  </si>
+  <si>
+    <t>Danni da creature</t>
+  </si>
+  <si>
+    <t>クリーチャーダメージ</t>
+  </si>
+  <si>
+    <t>생물 피해</t>
+  </si>
+  <si>
+    <t>Radības bojājumi</t>
+  </si>
+  <si>
+    <t>Padarų žala</t>
+  </si>
+  <si>
+    <t>Skade på skapninger</t>
+  </si>
+  <si>
+    <t>Obrażenia od stworzeń</t>
+  </si>
+  <si>
+    <t>Dano de Criatura</t>
+  </si>
+  <si>
+    <t>Daune creaturilor</t>
+  </si>
+  <si>
+    <t>Урон существам</t>
+  </si>
+  <si>
+    <t>Штета нанесена створењима</t>
+  </si>
+  <si>
+    <t>Poškodenie tvorov</t>
+  </si>
+  <si>
+    <t>Škoda bitja</t>
+  </si>
+  <si>
+    <t>Daño de criatura</t>
+  </si>
+  <si>
+    <t>Varelseskada</t>
+  </si>
+  <si>
+    <t>ความเสียหายของสิ่งมีชีวิต</t>
+  </si>
+  <si>
+    <t>Yaratık Hasarı</t>
+  </si>
+  <si>
+    <t>Шкода істот</t>
+  </si>
+  <si>
+    <t>Sát thương sinh vật</t>
+  </si>
+  <si>
+    <t>DrillTool.CreatureDamageTooltip</t>
+  </si>
+  <si>
+    <t>Damage dealt to creatures.
+This also applies to anything else that can be damaged, like flora or habitat.</t>
+  </si>
+  <si>
+    <t>Skade aan wesens aangerig. Dit geld ook vir enigiets anders wat beskadig kan word, soos flora of habitat.</t>
+  </si>
+  <si>
+    <t>Щети, нанесени на същества.
+Това важи и за всичко друго, което може да бъде повредено, като флора или местообитание.</t>
+  </si>
+  <si>
+    <t>Dany infligit a les criatures.
+Això també s'aplica a qualsevol altra cosa que pugui ser danyada, com la flora o l'hàbitat.</t>
+  </si>
+  <si>
+    <t>对生物造成的伤害。
+这也适用于其他任何可能受到损害的事物，例如植物或栖息地。</t>
+  </si>
+  <si>
+    <t>對生物造成的傷害。
+這也適用於其他任何可能受到損害的事物，例如植物或棲息地。</t>
+  </si>
+  <si>
+    <t>Šteta nanesena stvorenjima.
+To se odnosi i na sve ostalo što može biti oštećeno, poput flore ili staništa.</t>
+  </si>
+  <si>
+    <t>Škoda způsobená tvorům.
+To platí i pro cokoli jiného, ​​co může být poškozeno, jako je flóra nebo biotop.</t>
+  </si>
+  <si>
+    <t>Skade påført dyr.
+Dette gælder også for alt andet, der kan blive beskadiget, såsom flora eller levesteder.</t>
+  </si>
+  <si>
+    <t>Schade toegebracht aan wezens.
+Dit geldt ook voor alles wat beschadigd kan raken, zoals flora of leefgebied.</t>
+  </si>
+  <si>
+    <t>Olenditele tekitatud kahju.
+See kehtib ka kõige muu kohta, mida saab kahjustada, näiteks taimestik või elupaik.</t>
+  </si>
+  <si>
+    <t>Olennoille aiheutettu vahinko.
+Tämä koskee myös kaikkea muuta, mikä voi vaurioitua, kuten kasvistoa tai elinympäristöä.</t>
+  </si>
+  <si>
+    <t>Dégâts infligés aux créatures.
+Ceci s'applique également à tout ce qui peut être endommagé, comme la flore ou l'habitat.</t>
+  </si>
+  <si>
+    <t>Schäden an Lebewesen.
+Dies gilt auch für alles andere, was beschädigt werden kann, wie Pflanzen oder Lebensräume.</t>
+  </si>
+  <si>
+    <t>Ζημιά που προκαλείται σε πλάσματα.
+Αυτό ισχύει και για οτιδήποτε άλλο μπορεί να υποστεί ζημιά, όπως η χλωρίδα ή το βιότοπο.</t>
+  </si>
+  <si>
+    <t>Lényeknek okozott sebzés.
+Ez minden másra is vonatkozik, ami megsérülhet, például a növényekre vagy az élőhelyekre.</t>
+  </si>
+  <si>
+    <t>Damáiste a dhéantar do chréatúir. Baineann sé seo freisin le haon rud eile a d’fhéadfaí a mhilleadh, amhail flóra nó gnáthóg.</t>
+  </si>
+  <si>
+    <t>Danni inflitti alle creature.
+Questo vale anche per qualsiasi altra cosa che possa essere danneggiata, come la flora o l'habitat.</t>
+  </si>
+  <si>
+    <t>生物に与えたダメージ。
+これは、植物や生息地など、ダメージを受ける可能性のある他のあらゆるものにも適用されます。</t>
+  </si>
+  <si>
+    <t>생물에게 가해지는 피해량.
+이는 식물이나 서식지 등 피해를 입을 수 있는 다른 모든 것에도 적용됩니다.</t>
+  </si>
+  <si>
+    <t>Radībām nodarītais bojājums.
+Tas attiecas arī uz visu pārējo, kam var tikt nodarīts kaitējums, piemēram, floru vai dzīvotni.</t>
+  </si>
+  <si>
+    <t>Žala, padaryta gyvūnams.
+Tai taip pat taikoma viskam, kas gali būti pažeista, pavyzdžiui, florai ar buveinei.</t>
+  </si>
+  <si>
+    <t>Skade påført skapninger.
+Dette gjelder også alt annet som kan bli skadet, som flora eller habitat.</t>
+  </si>
+  <si>
+    <t>Obrażenia zadawane stworzeniom. Dotyczy to również wszystkiego innego, co może zostać uszkodzone, np. flory czy siedlisk.</t>
+  </si>
+  <si>
+    <t>Dano causado às criaturas.
+Isso também se aplica a qualquer outra coisa que possa ser danificada, como flora ou habitat.</t>
+  </si>
+  <si>
+    <t>Daune provocate creaturilor.
+Acest lucru se aplică și oricărui alt factor care poate fi deteriorat, cum ar fi flora sau habitatul.</t>
+  </si>
+  <si>
+    <t>Урон, наносимый существам.
+Это также относится ко всему остальному, что может быть повреждено, например, к флоре или среде обитания.</t>
+  </si>
+  <si>
+    <t>Штета нанета створењима.
+Ово се односи и на све остало што може бити оштећено, попут флоре или станишта.</t>
+  </si>
+  <si>
+    <t>Poškodenie spôsobené tvorom.
+Toto platí aj pre čokoľvek iné, čo môže byť poškodené, ako napríklad flóra alebo biotop.</t>
+  </si>
+  <si>
+    <t>Škoda, povzročena bitjem.
+To velja tudi za vse ostalo, kar je mogoče poškodovati, na primer rastlinstvo ali habitat.</t>
+  </si>
+  <si>
+    <t>Daños infligidos a las criaturas.
+Esto también se aplica a cualquier otra cosa que pueda resultar dañada, como la flora o el hábitat.</t>
+  </si>
+  <si>
+    <t>Skador på varelser.
+Detta gäller även allt annat som kan skadas, som flora eller livsmiljö.</t>
+  </si>
+  <si>
+    <t>ความเสียหายที่เกิดขึ้นกับสิ่งมีชีวิต
+นอกจากนี้ยังรวมถึงสิ่งอื่น ๆ ที่อาจได้รับความเสียหาย เช่น พืชหรือที่อยู่อาศัย</t>
+  </si>
+  <si>
+    <t>Canlılara verilen hasar.
+Bu, bitki örtüsü veya yaşam alanı gibi hasar görebilecek diğer her şey için de geçerlidir.</t>
+  </si>
+  <si>
+    <t>Шкода, завдана істотам.
+Це також стосується всього іншого, що може бути пошкоджено, як-от флора чи середовище існування.</t>
+  </si>
+  <si>
+    <t>Thiệt hại gây ra cho sinh vật.
+Điều này cũng áp dụng cho bất cứ thứ gì khác có thể bị hư hại, như thực vật hoặc môi trường sống.</t>
   </si>
 </sst>
 </file>
@@ -2354,8 +2770,9 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="22.38"/>
-    <col customWidth="1" min="2" max="3" width="37.63"/>
-    <col customWidth="1" min="4" max="4" width="124.25"/>
+    <col customWidth="1" min="2" max="2" width="37.63"/>
+    <col customWidth="1" min="3" max="3" width="11.25"/>
+    <col customWidth="1" min="4" max="4" width="11.63"/>
     <col customWidth="1" min="5" max="5" width="19.38"/>
   </cols>
   <sheetData>
@@ -2879,1285 +3296,1681 @@
         <v>164</v>
       </c>
       <c r="K5" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="L5" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="N5" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="O5" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="P5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="P5" s="14" t="s">
+      <c r="Q5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="Q5" s="14" t="s">
+      <c r="R5" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="R5" s="14" t="s">
+      <c r="S5" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="S5" s="14" t="s">
+      <c r="T5" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="T5" s="14" t="s">
+      <c r="U5" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="U5" s="14" t="s">
+      <c r="V5" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="V5" s="14" t="s">
+      <c r="W5" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="W5" s="14" t="s">
+      <c r="X5" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="X5" s="14" t="s">
+      <c r="Y5" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="Y5" s="14" t="s">
+      <c r="Z5" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="Z5" s="14" t="s">
+      <c r="AA5" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB5" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AA5" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB5" s="14" t="s">
+      <c r="AC5" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="AC5" s="15" t="s">
+      <c r="AD5" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="AD5" s="14" t="s">
+      <c r="AE5" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF5" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="AE5" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="AF5" s="14" t="s">
+      <c r="AG5" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="AG5" s="14" t="s">
+      <c r="AH5" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI5" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="AH5" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="AI5" s="15" t="s">
+      <c r="AJ5" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="AJ5" s="14" t="s">
+      <c r="AK5" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="AK5" s="14" t="s">
+      <c r="AL5" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="AL5" s="15" t="s">
+      <c r="AM5" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="AM5" s="14" t="s">
+      <c r="AN5" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="AN5" s="16" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="O6" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="O6" s="15" t="s">
+      <c r="P6" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="Q6" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="R6" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="S6" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="T6" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="T6" s="8" t="s">
+      <c r="U6" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="U6" s="8" t="s">
+      <c r="V6" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="V6" s="8" t="s">
+      <c r="W6" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="X6" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="X6" s="8" t="s">
+      <c r="Y6" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Z6" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="Z6" s="8" t="s">
+      <c r="AA6" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB6" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="AA6" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="AB6" s="8" t="s">
+      <c r="AC6" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="AC6" s="15" t="s">
+      <c r="AD6" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="AD6" s="8" t="s">
+      <c r="AE6" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="AF6" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="AE6" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="AF6" s="8" t="s">
+      <c r="AG6" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="AG6" s="8" t="s">
+      <c r="AH6" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AH6" s="8" t="s">
+      <c r="AI6" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="AI6" s="15" t="s">
+      <c r="AJ6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AJ6" s="8" t="s">
+      <c r="AK6" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="AK6" s="8" t="s">
+      <c r="AL6" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="AL6" s="15" t="s">
+      <c r="AM6" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="AM6" s="8" t="s">
+      <c r="AN6" s="17" t="s">
         <v>228</v>
-      </c>
-      <c r="AN6" s="17" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="F7" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="H7" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="I7" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="J7" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="K7" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="L7" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="M7" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="N7" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="O7" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="O7" s="15" t="s">
+      <c r="P7" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="Q7" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="Q7" s="14" t="s">
+      <c r="R7" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="R7" s="14" t="s">
+      <c r="S7" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="S7" s="14" t="s">
+      <c r="T7" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="T7" s="14" t="s">
+      <c r="U7" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="U7" s="14" t="s">
+      <c r="V7" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="V7" s="14" t="s">
+      <c r="W7" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="X7" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="X7" s="14" t="s">
+      <c r="Y7" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="Y7" s="14" t="s">
+      <c r="Z7" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="Z7" s="14" t="s">
+      <c r="AA7" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="AB7" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="AA7" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="AB7" s="14" t="s">
+      <c r="AC7" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="AC7" s="15" t="s">
+      <c r="AD7" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="AD7" s="14" t="s">
+      <c r="AE7" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AF7" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="AE7" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="AF7" s="14" t="s">
+      <c r="AG7" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="AG7" s="14" t="s">
+      <c r="AH7" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="AH7" s="14" t="s">
+      <c r="AI7" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="AI7" s="15" t="s">
+      <c r="AJ7" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="AJ7" s="14" t="s">
+      <c r="AK7" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="AK7" s="14" t="s">
+      <c r="AL7" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="AL7" s="15" t="s">
+      <c r="AM7" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="AM7" s="14" t="s">
+      <c r="AN7" s="16" t="s">
         <v>266</v>
-      </c>
-      <c r="AN7" s="16" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="N8" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="O8" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="O8" s="15" t="s">
+      <c r="P8" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="Q8" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="Q8" s="8" t="s">
+      <c r="R8" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="S8" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="S8" s="8" t="s">
+      <c r="T8" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="T8" s="8" t="s">
+      <c r="U8" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="U8" s="8" t="s">
+      <c r="V8" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="V8" s="8" t="s">
+      <c r="W8" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="W8" s="8" t="s">
+      <c r="X8" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="X8" s="8" t="s">
+      <c r="Y8" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="Y8" s="8" t="s">
+      <c r="Z8" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="Z8" s="8" t="s">
+      <c r="AA8" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB8" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="AA8" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="AB8" s="8" t="s">
+      <c r="AC8" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="AC8" s="15" t="s">
+      <c r="AD8" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="AD8" s="8" t="s">
+      <c r="AE8" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="AF8" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="AE8" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="AF8" s="8" t="s">
+      <c r="AG8" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="AG8" s="8" t="s">
+      <c r="AH8" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="AH8" s="8" t="s">
+      <c r="AI8" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="AI8" s="15" t="s">
+      <c r="AJ8" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="AJ8" s="8" t="s">
+      <c r="AK8" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="AK8" s="8" t="s">
+      <c r="AL8" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="AL8" s="15" t="s">
+      <c r="AM8" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="AM8" s="8" t="s">
+      <c r="AN8" s="17" t="s">
         <v>304</v>
-      </c>
-      <c r="AN8" s="17" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E9" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="F9" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="G9" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="H9" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="I9" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="J9" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="L9" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="M9" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="N9" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="O9" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="O9" s="14" t="s">
+      <c r="P9" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="Q9" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="Q9" s="14" t="s">
+      <c r="R9" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="S9" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="T9" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="T9" s="14" t="s">
+      <c r="U9" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="U9" s="14" t="s">
+      <c r="V9" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V9" s="14" t="s">
+      <c r="W9" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="W9" s="14" t="s">
+      <c r="X9" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="X9" s="14" t="s">
+      <c r="Y9" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="Y9" s="14" t="s">
+      <c r="Z9" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="Z9" s="14" t="s">
+      <c r="AA9" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="AB9" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="AA9" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="AB9" s="14" t="s">
+      <c r="AC9" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="AC9" s="14" t="s">
+      <c r="AD9" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="AD9" s="14" t="s">
+      <c r="AE9" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="AF9" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="AE9" s="14" t="s">
-        <v>334</v>
-      </c>
-      <c r="AF9" s="14" t="s">
+      <c r="AG9" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="AG9" s="14" t="s">
+      <c r="AH9" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="AH9" s="14" t="s">
+      <c r="AI9" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="AJ9" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="AI9" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="AJ9" s="14" t="s">
+      <c r="AK9" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="AK9" s="14" t="s">
+      <c r="AL9" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="AL9" s="14" t="s">
+      <c r="AM9" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="AM9" s="14" t="s">
+      <c r="AN9" s="16" t="s">
         <v>341</v>
-      </c>
-      <c r="AN9" s="16" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="T10" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="T10" s="8" t="s">
-        <v>345</v>
-      </c>
       <c r="U10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="W10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="X10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Y10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Z10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AA10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AB10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AC10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AD10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AE10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AF10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AH10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AI10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AJ10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AK10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AL10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AM10" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN10" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="E11" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="O11" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="O11" s="14" t="s">
+      <c r="P11" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="R11" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="P11" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q11" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="R11" s="14" t="s">
+      <c r="S11" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="T11" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="V11" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="T11" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="U11" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="V11" s="14" t="s">
+      <c r="W11" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="X11" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="Y11" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z11" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA11" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="AB11" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="AC11" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="W11" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="X11" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="Y11" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="Z11" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="AA11" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="AB11" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="AC11" s="14" t="s">
+      <c r="AD11" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AE11" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AF11" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="AG11" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="AH11" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="AI11" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="AJ11" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK11" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="AL11" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="AD11" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="AE11" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="AF11" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="AG11" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="AH11" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="AI11" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="AJ11" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="AK11" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="AL11" s="14" t="s">
-        <v>355</v>
-      </c>
       <c r="AM11" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="AN11" s="16" t="s">
         <v>266</v>
-      </c>
-      <c r="AN11" s="16" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="F12" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="G12" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="H12" s="21" t="s">
         <v>361</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="I12" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="J12" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="K12" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="L12" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="M12" s="21" t="s">
         <v>366</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="N12" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="M12" s="21" t="s">
+      <c r="O12" s="21" t="s">
         <v>368</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="P12" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="O12" s="21" t="s">
+      <c r="Q12" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="P12" s="21" t="s">
+      <c r="R12" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="Q12" s="21" t="s">
+      <c r="S12" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="R12" s="21" t="s">
+      <c r="T12" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="S12" s="21" t="s">
+      <c r="U12" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="T12" s="21" t="s">
+      <c r="V12" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="U12" s="21" t="s">
+      <c r="W12" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="V12" s="21" t="s">
+      <c r="X12" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="W12" s="21" t="s">
+      <c r="Y12" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="X12" s="21" t="s">
+      <c r="Z12" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="Y12" s="21" t="s">
+      <c r="AA12" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="AB12" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="Z12" s="21" t="s">
+      <c r="AC12" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="AA12" s="21" t="s">
-        <v>381</v>
-      </c>
-      <c r="AB12" s="21" t="s">
+      <c r="AD12" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="AC12" s="21" t="s">
+      <c r="AE12" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="AF12" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="AD12" s="21" t="s">
+      <c r="AG12" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="AE12" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="AF12" s="21" t="s">
+      <c r="AH12" s="21" t="s">
         <v>385</v>
       </c>
-      <c r="AG12" s="21" t="s">
+      <c r="AI12" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="AJ12" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="AH12" s="21" t="s">
+      <c r="AK12" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="AI12" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="AJ12" s="21" t="s">
+      <c r="AL12" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="AK12" s="21" t="s">
+      <c r="AM12" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="AL12" s="21" t="s">
+      <c r="AN12" s="22" t="s">
         <v>390</v>
-      </c>
-      <c r="AM12" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="AN12" s="22" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C13" s="23" t="s">
         <v>393</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="D13" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="E13" s="23" t="s">
         <v>395</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="F13" s="23" t="s">
         <v>396</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="G13" s="23" t="s">
         <v>397</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="H13" s="23" t="s">
         <v>398</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="I13" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="J13" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="K13" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="L13" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="M13" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="K13" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="L13" s="23" t="s">
+      <c r="N13" s="23" t="s">
         <v>403</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="O13" s="23" t="s">
         <v>404</v>
       </c>
-      <c r="N13" s="23" t="s">
+      <c r="P13" s="23" t="s">
         <v>405</v>
       </c>
-      <c r="O13" s="23" t="s">
+      <c r="Q13" s="23" t="s">
         <v>406</v>
       </c>
-      <c r="P13" s="23" t="s">
+      <c r="R13" s="23" t="s">
         <v>407</v>
       </c>
-      <c r="Q13" s="23" t="s">
+      <c r="S13" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="R13" s="23" t="s">
+      <c r="T13" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="S13" s="23" t="s">
+      <c r="U13" s="23" t="s">
         <v>410</v>
       </c>
-      <c r="T13" s="23" t="s">
+      <c r="V13" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="U13" s="23" t="s">
+      <c r="W13" s="24" t="s">
         <v>412</v>
       </c>
-      <c r="V13" s="24" t="s">
+      <c r="X13" s="24" t="s">
         <v>413</v>
       </c>
-      <c r="W13" s="24" t="s">
+      <c r="Y13" s="24" t="s">
         <v>414</v>
       </c>
-      <c r="X13" s="24" t="s">
+      <c r="Z13" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="Y13" s="24" t="s">
+      <c r="AA13" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="AB13" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="Z13" s="24" t="s">
+      <c r="AC13" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="AA13" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB13" s="24" t="s">
+      <c r="AD13" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="AC13" s="24" t="s">
+      <c r="AE13" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="AF13" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="AD13" s="24" t="s">
+      <c r="AG13" s="24" t="s">
         <v>420</v>
       </c>
-      <c r="AE13" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="AF13" s="24" t="s">
+      <c r="AH13" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="AI13" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="AJ13" s="24" t="s">
         <v>421</v>
       </c>
-      <c r="AG13" s="24" t="s">
+      <c r="AK13" s="24" t="s">
         <v>422</v>
       </c>
-      <c r="AH13" s="24" t="s">
-        <v>394</v>
-      </c>
-      <c r="AI13" s="24" t="s">
-        <v>394</v>
-      </c>
-      <c r="AJ13" s="24" t="s">
+      <c r="AL13" s="24" t="s">
         <v>423</v>
       </c>
-      <c r="AK13" s="24" t="s">
+      <c r="AM13" s="24" t="s">
         <v>424</v>
       </c>
-      <c r="AL13" s="24" t="s">
+      <c r="AN13" s="24" t="s">
         <v>425</v>
-      </c>
-      <c r="AM13" s="24" t="s">
-        <v>426</v>
-      </c>
-      <c r="AN13" s="24" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>428</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="D14" s="23" t="s">
         <v>429</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="E14" s="23" t="s">
         <v>430</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="F14" s="23" t="s">
         <v>431</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="G14" s="23" t="s">
         <v>432</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="H14" s="23" t="s">
         <v>433</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="I14" s="23" t="s">
         <v>434</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="J14" s="23" t="s">
         <v>435</v>
       </c>
-      <c r="I14" s="23" t="s">
+      <c r="K14" s="23" t="s">
         <v>436</v>
       </c>
-      <c r="J14" s="23" t="s">
+      <c r="L14" s="23" t="s">
         <v>437</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="M14" s="23" t="s">
         <v>438</v>
       </c>
-      <c r="L14" s="23" t="s">
+      <c r="N14" s="23" t="s">
         <v>439</v>
       </c>
-      <c r="M14" s="23" t="s">
+      <c r="O14" s="23" t="s">
         <v>440</v>
       </c>
-      <c r="N14" s="23" t="s">
+      <c r="P14" s="23" t="s">
         <v>441</v>
       </c>
-      <c r="O14" s="23" t="s">
+      <c r="Q14" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="P14" s="23" t="s">
+      <c r="R14" s="23" t="s">
         <v>443</v>
       </c>
-      <c r="Q14" s="23" t="s">
+      <c r="S14" s="23" t="s">
         <v>444</v>
       </c>
-      <c r="R14" s="23" t="s">
+      <c r="T14" s="23" t="s">
         <v>445</v>
       </c>
-      <c r="S14" s="23" t="s">
+      <c r="U14" s="23" t="s">
         <v>446</v>
       </c>
-      <c r="T14" s="23" t="s">
+      <c r="V14" s="24" t="s">
         <v>447</v>
       </c>
-      <c r="U14" s="23" t="s">
+      <c r="W14" s="24" t="s">
         <v>448</v>
       </c>
-      <c r="V14" s="24" t="s">
+      <c r="X14" s="24" t="s">
         <v>449</v>
       </c>
-      <c r="W14" s="24" t="s">
+      <c r="Y14" s="24" t="s">
         <v>450</v>
       </c>
-      <c r="X14" s="24" t="s">
+      <c r="Z14" s="24" t="s">
         <v>451</v>
       </c>
-      <c r="Y14" s="24" t="s">
+      <c r="AA14" s="24" t="s">
+        <v>451</v>
+      </c>
+      <c r="AB14" s="24" t="s">
         <v>452</v>
       </c>
-      <c r="Z14" s="24" t="s">
+      <c r="AC14" s="24" t="s">
         <v>453</v>
       </c>
-      <c r="AA14" s="24" t="s">
-        <v>453</v>
-      </c>
-      <c r="AB14" s="24" t="s">
+      <c r="AD14" s="24" t="s">
         <v>454</v>
       </c>
-      <c r="AC14" s="24" t="s">
+      <c r="AE14" s="24" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF14" s="24" t="s">
         <v>455</v>
       </c>
-      <c r="AD14" s="24" t="s">
+      <c r="AG14" s="24" t="s">
         <v>456</v>
       </c>
-      <c r="AE14" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="AF14" s="24" t="s">
+      <c r="AH14" s="24" t="s">
         <v>457</v>
       </c>
-      <c r="AG14" s="24" t="s">
+      <c r="AI14" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="AJ14" s="24" t="s">
         <v>458</v>
       </c>
-      <c r="AH14" s="24" t="s">
+      <c r="AK14" s="24" t="s">
         <v>459</v>
       </c>
-      <c r="AI14" s="24" t="s">
-        <v>459</v>
-      </c>
-      <c r="AJ14" s="24" t="s">
+      <c r="AL14" s="24" t="s">
         <v>460</v>
       </c>
-      <c r="AK14" s="24" t="s">
+      <c r="AM14" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="AL14" s="24" t="s">
+      <c r="AN14" s="24" t="s">
         <v>462</v>
-      </c>
-      <c r="AM14" s="24" t="s">
-        <v>463</v>
-      </c>
-      <c r="AN14" s="24" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
+      <c r="A15" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="O15" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q15" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="S15" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="T15" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="U15" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="V15" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="W15" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="X15" s="24" t="s">
+        <v>472</v>
+      </c>
+      <c r="Y15" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="Z15" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="AA15" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="AB15" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="AC15" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="AD15" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="AE15" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="AF15" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="AG15" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="AH15" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="AI15" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="AJ15" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="AK15" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="AL15" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="AM15" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="AN15" s="24" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
+      <c r="A16" s="23" t="s">
+        <v>493</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>495</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>501</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="L16" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="M16" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="N16" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="O16" s="23" t="s">
+        <v>507</v>
+      </c>
+      <c r="P16" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q16" s="23" t="s">
+        <v>509</v>
+      </c>
+      <c r="R16" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="S16" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="T16" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="U16" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="V16" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="W16" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="X16" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="Y16" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="Z16" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="AA16" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="AB16" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="AC16" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="AD16" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="AE16" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="AF16" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="AG16" s="24" t="s">
+        <v>523</v>
+      </c>
+      <c r="AH16" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="AI16" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="AJ16" s="24" t="s">
+        <v>525</v>
+      </c>
+      <c r="AK16" s="24" t="s">
+        <v>526</v>
+      </c>
+      <c r="AL16" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="AM16" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="AN16" s="24" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
+      <c r="A17" s="23" t="s">
+        <v>530</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>531</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>532</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>535</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>536</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>537</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>538</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="L17" s="23" t="s">
+        <v>541</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>542</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>543</v>
+      </c>
+      <c r="O17" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="P17" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="Q17" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="R17" s="23" t="s">
+        <v>547</v>
+      </c>
+      <c r="S17" s="23" t="s">
+        <v>548</v>
+      </c>
+      <c r="T17" s="23" t="s">
+        <v>549</v>
+      </c>
+      <c r="U17" s="23" t="s">
+        <v>550</v>
+      </c>
+      <c r="V17" s="24" t="s">
+        <v>551</v>
+      </c>
+      <c r="W17" s="24" t="s">
+        <v>552</v>
+      </c>
+      <c r="X17" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="Y17" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="Z17" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="AA17" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="AB17" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC17" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="AD17" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="AE17" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="AF17" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="AG17" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="AH17" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="AI17" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="AJ17" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="AK17" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="AL17" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="AM17" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="AN17" s="24" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="25"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
+      <c r="A18" s="23" t="s">
+        <v>567</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>568</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>569</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>570</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>571</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>572</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>573</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>574</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>575</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>577</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>578</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>579</v>
+      </c>
+      <c r="N18" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="O18" s="23" t="s">
+        <v>581</v>
+      </c>
+      <c r="P18" s="23" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q18" s="23" t="s">
+        <v>583</v>
+      </c>
+      <c r="R18" s="23" t="s">
+        <v>584</v>
+      </c>
+      <c r="S18" s="23" t="s">
+        <v>585</v>
+      </c>
+      <c r="T18" s="23" t="s">
+        <v>586</v>
+      </c>
+      <c r="U18" s="23" t="s">
+        <v>587</v>
+      </c>
+      <c r="V18" s="24" t="s">
+        <v>588</v>
+      </c>
+      <c r="W18" s="24" t="s">
+        <v>589</v>
+      </c>
+      <c r="X18" s="24" t="s">
+        <v>590</v>
+      </c>
+      <c r="Y18" s="24" t="s">
+        <v>591</v>
+      </c>
+      <c r="Z18" s="24" t="s">
+        <v>592</v>
+      </c>
+      <c r="AA18" s="24" t="s">
+        <v>592</v>
+      </c>
+      <c r="AB18" s="24" t="s">
+        <v>593</v>
+      </c>
+      <c r="AC18" s="24" t="s">
+        <v>594</v>
+      </c>
+      <c r="AD18" s="24" t="s">
+        <v>595</v>
+      </c>
+      <c r="AE18" s="24" t="s">
+        <v>595</v>
+      </c>
+      <c r="AF18" s="24" t="s">
+        <v>596</v>
+      </c>
+      <c r="AG18" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="AH18" s="24" t="s">
+        <v>598</v>
+      </c>
+      <c r="AI18" s="24" t="s">
+        <v>598</v>
+      </c>
+      <c r="AJ18" s="24" t="s">
+        <v>599</v>
+      </c>
+      <c r="AK18" s="24" t="s">
+        <v>600</v>
+      </c>
+      <c r="AL18" s="24" t="s">
+        <v>601</v>
+      </c>
+      <c r="AM18" s="24" t="s">
+        <v>602</v>
+      </c>
+      <c r="AN18" s="24" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="25"/>

--- a/translate.xlsx
+++ b/translate.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="603">
   <si>
     <t>Keycode</t>
   </si>
@@ -367,181 +367,148 @@
     <t>DrillTool.EnergyCostTooltip</t>
   </si>
   <si>
-    <t>Battery drain per resource deposit hit.
-It takes up to 320 hits to fully destroy a deposit.
-Energy is only drained when mining a large resource deposit.</t>
-  </si>
-  <si>
-    <t>Battery dreineer per hulpbronafsetting-treffer.
-Dit neem tot 320 treffers om 'n afsetting volledig te vernietig.
-Energie word slegs gedreineer wanneer 'n groot hulpbronafsetting gemyn word.</t>
-  </si>
-  <si>
-    <t>Разход на батерия за всеки \"удар\" по находище на ресурси.
-За пълно разрушаване на находището може да са необходими до 320 удара.
-Енергия се консумира само при добив на големи находища ресурси.</t>
-  </si>
-  <si>
-    <t>Esgotament de bateria per cada cop que es colpeja un dipòsit de recursos.
-Es necessiten fins a 320 cops per destruir completament un dipòsit.
-L'energia només es consumeix quan s'explota un dipòsit de recursos gran.</t>
-  </si>
-  <si>
-    <t>每次开采资源矿藏都会消耗电池电量。
-最多需要开采 320 次才能彻底摧毁一个矿藏。
-只有在开采大型资源矿藏时才会消耗能量。</t>
-  </si>
-  <si>
-    <t>每次開採資源礦藏都會消耗電池電量。
-最多需要開採 320 次才能徹底摧毀一個礦藏。
-只有在開採大型資源礦藏時才會消耗能量。</t>
-  </si>
-  <si>
-    <t>Pražnjenje baterije po udarcu u ležište resursa.
-Potrebno je do 320 udaraca da se ležište potpuno uništi. Energija se troši samo prilikom rudarenja velikog ležišta resursa.</t>
-  </si>
-  <si>
-    <t>Spotřeba energie na 1 úder do ložiska. K úplnému zničení ložiska je třeba až 320 úderů. Při výchozí hodnotě vystačí baterie na 2 ložiska.
-Energie se spotřebovává jen při těžbě velkých ložisek.</t>
-  </si>
-  <si>
-    <t>Batteriforbrug pr. hit på en ressourcedepot.
-Det tager op til 320 hits at ødelægge en depot fuldstændigt.
-Energi drænes kun ved udvinding af en stor ressourcedepot.</t>
-  </si>
-  <si>
-    <t>Batterijverbruik per geraakte grondstofafzetting.
-Het duurt tot 320 treffers om een ​​afzetting volledig te vernietigen.
-Energie wordt alleen verbruikt bij het delven van een grote grondstofafzetting.</t>
-  </si>
-  <si>
-    <t>Aku tühjenemine iga ressursimaardla tabamuse kohta.
-Maardla täielikuks hävitamiseks kulub kuni 320 tabamust.
-Energiat kulub ainult suure ressursimaardla kaevandamisel.</t>
-  </si>
-  <si>
-    <t>Akun tyhjennys osumaa kohden resurssiesiintymää kohden.
-Esiintymän täydellinen tuhoaminen vaatii jopa 320 osumaa.
-Energiaa kuluu vain suuren resurssiesiintymän louhimista varten.</t>
-  </si>
-  <si>
-    <t>Consommation de batterie à chaque exploitation d'un gisement.
-Il faut jusqu'à 320 exploitations pour détruire complètement un gisement.
-L'énergie n'est consommée que lors de l'exploitation d'un gisement important.</t>
-  </si>
-  <si>
-    <t>Batterieverbrauch pro \"Treffer\" an einer Rohstoffader.
-Bis zu 320 Treffer sind erforderlich, um eine Ader vollständig zu zerstören.
-Energie wird nur beim Abbauen großer Rohstoffvorkommen verbraucht.</t>
-  </si>
-  <si>
-    <t>Εξάντληση μπαταρίας ανά χτύπημα κατάθεσης πόρων.
-Χρειάζονται έως και 320 χτυπήματα για να καταστραφεί πλήρως ένα κοίτασμα.
-Η ενέργεια εξαντλείται μόνο κατά την εξόρυξη ενός μεγάλου κοιτάσματος πόρων.</t>
-  </si>
-  <si>
-    <t>Erőforrás-lelőhely találatánként akkumulátormerülés.
-Egy lelőhely teljes megsemmisítéséhez akár 320 találat is szükséges.
-Energia csak nagy erőforrás-lelőhely kibányászásakor merül el.</t>
-  </si>
-  <si>
-    <t>Ídítear an ceallraí in aghaidh gach buille taisce acmhainní.
-Tógann sé suas le 320 buille chun taisce a scriosadh go hiomlán.
-Ní dhéantar fuinneamh a ídiú ach amháin nuair a bhíonn taisce acmhainní mór á mianadóireacht.</t>
-  </si>
-  <si>
-    <t>Consumo di batteria per ogni colpo a un giacimento di risorse.
-Occorrono fino a 320 colpi per distruggere completamente un giacimento.
-L'energia viene consumata solo quando si estrae un grande giacimento di risorse.</t>
-  </si>
-  <si>
-    <t>資源鉱床を採掘するたびにバッテリーが消耗します。
-鉱床を完全に破壊するには最大320回の採掘が必要です。
-エネルギーは、大規模な資源鉱床を採掘する場合にのみ消費されます。</t>
-  </si>
-  <si>
-    <t>자원 매장지 채굴 시 배터리 소모량이 발생합니다.
-매장지를 완전히 파괴하려면 최대 320번의 채굴이 필요합니다.
-에너지는 대형 자원 매장지를 채굴할 때만 소모됩니다.</t>
-  </si>
-  <si>
-    <t>Akumulatora izlādēšanās uz katru resursu atradnes trāpījumu.
-Lai pilnībā iznīcinātu atradni, nepieciešami līdz 320 trāpījumiem.
-Enerģija tiek patērēta tikai tad, ja tiek iegūta liela resursu atradne.</t>
-  </si>
-  <si>
-    <t>Baterijos išeikvojimas kiekvienam išteklių telkinio pataikymui.
-Norint visiškai sunaikinti telkinį, reikia iki 320 pataikymų.
-Energija eikvojama tik iškasant didelį išteklių telkinį.</t>
-  </si>
-  <si>
-    <t>Batteriforbruk per treff på ressursforekomst.
-Det tar opptil 320 treff å ødelegge en forekomst fullstendig.
-Energi tappes bare når man utvinner en stor ressursforekomst.</t>
-  </si>
-  <si>
-    <t>Zużycie baterii przy każdym trafieniu w złoże zasobów.
-Całkowite zniszczenie złoża wymaga do 320 trafień.
-Energia jest wyczerpywana tylko podczas wydobywania dużego złoża zasobów.</t>
-  </si>
-  <si>
-    <t>Consumo de bateria por ataque a um depósito de recursos.
-São necessários até 320 ataques para destruir completamente um depósito.
-A energia só é consumida ao minerar um depósito de recursos grande.</t>
-  </si>
-  <si>
-    <t>Consumul bateriei se face pentru fiecare lovitură a unui depozit de resurse.
-Sunt necesare până la 320 de lovituri pentru a distruge complet un depozit.
-Energia se consumă doar la extragerea unui depozit mare de resurse.</t>
-  </si>
-  <si>
-    <t>Расход батареи за один «удар» по залежи ресурса.
-На полное разрушение залежи может потребоваться до 320 ударов.
-Энергия расходуется только при добыче крупных залежей ресурсов.</t>
-  </si>
-  <si>
-    <t>Пражњење батерије по поготку у лежиште ресурса.
-Потребно је до 320 поготка да се лежиште потпуно уништи. Енергија се троши само приликом ископавања великог лежишта ресурса.</t>
-  </si>
-  <si>
-    <t>Vybíjanie batérie na jeden zásah do ložiska surovín.
-Na úplné zničenie ložiska je potrebných až 320 zásahov. Energia sa vybíja iba pri ťažbe veľkého ložiska surovín.</t>
-  </si>
-  <si>
-    <t>Izpraznitev baterije na zadetek nahajališča surovin. Za popolno uničenje nahajališča je potrebnih do 320 zadetkov. Energija se izprazni le pri rudarjenju velikega nahajališča surovin.</t>
-  </si>
-  <si>
-    <t>Consumo de batería por cada yacimiento de recursos.
-Se necesitan hasta 320 impactos para destruir completamente un yacimiento.
-La energía solo se consume al extraer un yacimiento de recursos grande.</t>
-  </si>
-  <si>
-    <t>Consumo de batería por cada «golpe» en un depósito de recursos.
-Se requieren hasta 320 golpes para destruir completamente un depósito.
-La energía solo se consume al minar depósitos grandes de recursos.</t>
-  </si>
-  <si>
-    <t>Batteriet förbrukas per träff med en resursfyndighet.
-Det tar upp till 320 träffar att helt förstöra en fyndighet.
-Energi förbrukas endast vid utvinning av en stor resursfyndighet.</t>
-  </si>
-  <si>
-    <t>อัตราการใช้พลังงานแบตเตอรี่ต่อการทำลายแหล่งทรัพยากรแต่ละครั้ง
-ต้องทำลายแหล่งทรัพยากรมากถึง 320 ครั้งจึงจะทำลายแหล่งทรัพยากรได้หมด
-พลังงานจะถูกใช้ก็ต่อเมื่อทำการขุดแหล่งทรัพยากรขนาดใหญ่เท่านั้น</t>
-  </si>
-  <si>
-    <t>Her kaynak yatağı \"vuruşu\" başına pil tüketimi.
-Bir yatağı tamamen yok etmek için en fazla 320 vuruş gerekir.
-Enerji yalnızca büyük kaynak yatakları kazılırken tüketilir.</t>
-  </si>
-  <si>
-    <t>Розрядка батареї за один удар по родовищу ресурсу. Для повного знищення родовища потрібно до 320 ударів. Енергія витрачається лише під час видобутку великого родовища ресурсів.</t>
-  </si>
-  <si>
-    <t>Mức hao pin mỗi khi khai thác mỏ tài nguyên.
-Cần tới 320 lần khai thác để phá hủy hoàn toàn một mỏ tài nguyên.
-Năng lượng chỉ bị hao khi khai thác mỏ tài nguyên lớn.</t>
+    <t>Battery drain per hit, whether hitting a resource or creature.
+It takes up to 320 hits to fully destroy a deposit.</t>
+  </si>
+  <si>
+    <t>Battery dreineer per treffer, of dit nou 'n hulpbron of skepsel tref.
+Dit neem tot 320 treffers om 'n neerslag volledig te vernietig.</t>
+  </si>
+  <si>
+    <t>Изтощаване на батерията на удар, независимо дали удряте ресурс или същество.
+Необходими са до 320 удара, за да се унищожи напълно депозит.</t>
+  </si>
+  <si>
+    <t>Esgotament de bateria per impacte, tant si colpeges un recurs com una criatura.
+Es necessiten fins a 320 impactes per destruir completament un dipòsit.</t>
+  </si>
+  <si>
+    <t>每次攻击都会消耗电池电量，无论攻击目标是资源还是生物。
+最多需要 320 次攻击才能彻底摧毁一个矿藏。</t>
+  </si>
+  <si>
+    <t>每次攻擊都會消耗電池電量，無論攻擊目標是資源還是生物。
+最多需要 320 次攻擊才能徹底摧毀一個礦藏。</t>
+  </si>
+  <si>
+    <t>Pražnjenje baterije po udarcu, bez obzira na to je li riječ o pogotku resursa ili stvorenja.
+Potrebno je do 320 udaraca da se polog potpuno uništi.</t>
+  </si>
+  <si>
+    <t>Vybíjení baterie na jeden zásah, ať už se jedná o zásah zdroje nebo tvora.
+K úplnému zničení ložiska je potřeba až 320 zásahů.</t>
+  </si>
+  <si>
+    <t>Batteriforbrug pr. træf, uanset om det rammer en ressource eller et væsen.
+Det tager op til 320 træf at ødelægge en aflejring fuldstændigt.</t>
+  </si>
+  <si>
+    <t>Batterijverbruik per slag, ongeacht of je een grondstof of een wezen raakt.
+Het kost tot 320 slagen om een ​​afzetting volledig te vernietigen.</t>
+  </si>
+  <si>
+    <t>Aku tühjenemine löögi kohta, olenemata sellest, kas tabab ressurssi või olendit.
+Laoseisu täielikuks hävitamiseks kulub kuni 320 tabamust.</t>
+  </si>
+  <si>
+    <t>Akun tyhjennys osumaa kohden, osuupa se sitten resurssiin tai olentoon.
+Talletuksen täydellinen tuhoaminen vaatii jopa 320 osumaa.</t>
+  </si>
+  <si>
+    <t>Chaque coup porté consomme de la batterie, qu'il s'agisse d'une ressource ou d'une créature.
+Il faut jusqu'à 320 coups pour détruire complètement un gisement.</t>
+  </si>
+  <si>
+    <t>Der Akkuverbrauch pro Treffer, egal ob auf eine Ressource oder ein Lebewesen, variiert.
+Es sind bis zu 320 Treffer nötig, um ein Vorkommen vollständig zu zerstören.</t>
+  </si>
+  <si>
+    <t>Εξάντληση μπαταρίας ανά χτύπημα, είτε χτυπάει πόρο είτε πλάσμα.
+Χρειάζονται έως και 320 χτυπήματα για να καταστραφεί πλήρως μια κατάθεση.</t>
+  </si>
+  <si>
+    <t>Találatonként akkumulátor merül, akár erőforrást, akár lényt találsz el.
+Akár 320 találat is elegendő egy lelőhely teljes megsemmisítéséhez.</t>
+  </si>
+  <si>
+    <t>Ídíonn an ceallraí gach buille, bíodh sé ag bualadh acmhainne nó créatúir.
+Tógann sé suas le 320 buille chun taisce a scriosadh go hiomlán.</t>
+  </si>
+  <si>
+    <t>Consumo della batteria per ogni colpo, sia che si colpisca una risorsa o una creatura.
+Sono necessari fino a 320 colpi per distruggere completamente un giacimento.</t>
+  </si>
+  <si>
+    <t>資源であろうと生物であろうと、攻撃するたびにバッテリーを消費します。
+鉱床を完全に破壊するには、最大320回の攻撃が必要です。</t>
+  </si>
+  <si>
+    <t>자원이나 생물을 공격할 때마다 배터리가 소모됩니다.
+광물 매장지를 완전히 파괴하려면 최대 320번의 공격이 필요합니다.</t>
+  </si>
+  <si>
+    <t>Akumulatora izlāde ar katru trāpījumu, neatkarīgi no tā, vai trāpa resursam vai radījumam.
+Lai pilnībā iznīcinātu noguldījumu, nepieciešami līdz 320 trāpījumiem.</t>
+  </si>
+  <si>
+    <t>Baterijos išeikvojimas po kiekvieno smūgio, nesvarbu, ar pataikoma į išteklių, ar į būtybę.
+Norint visiškai sunaikinti užstatą, reikia iki 320 smūgių.</t>
+  </si>
+  <si>
+    <t>Batteriforbruk per treff, enten det treffer en ressurs eller en skapning.
+Det tar opptil 320 treff å ødelegge en innskudd fullstendig.</t>
+  </si>
+  <si>
+    <t>Zużycie baterii przy każdym trafieniu, niezależnie od tego, czy trafisz w zasób, czy stworzenie.
+Całkowite zniszczenie złoża wymaga do 320 trafień.</t>
+  </si>
+  <si>
+    <t>Consumo de bateria por golpe, seja atingindo um recurso ou uma criatura.
+São necessários até 320 golpes para destruir completamente um depósito.</t>
+  </si>
+  <si>
+    <t>Bateria se consumă per lovitură, indiferent dacă lovești o resursă sau o creatură.
+Este nevoie de până la 320 de lovituri pentru a distruge complet un depozit.</t>
+  </si>
+  <si>
+    <t>Расход батареи за каждый удар, будь то попадание по ресурсу или существу.
+Для полного уничтожения месторождения требуется до 320 ударов.</t>
+  </si>
+  <si>
+    <t>Пражњење батерије по ударцу, без обзира да ли се ради о ресурсу или створењу.
+Потребно је до 320 удараца да се депозит потпуно уништи.</t>
+  </si>
+  <si>
+    <t>Vybíjanie batérie na jeden zásah, či už ide o zásah do zdroja alebo tvora.
+Na úplné zničenie ložiska je potrebných až 320 zásahov.</t>
+  </si>
+  <si>
+    <t>Izpraznitev baterije na zadetek, ne glede na to, ali zadenete vir ali bitje.
+Za popolno uničenje nahajališča je potrebnih do 320 zadetkov.</t>
+  </si>
+  <si>
+    <t>Consumo de batería por impacto, ya sea contra un recurso o una criatura.
+Se necesitan hasta 320 impactos para destruir completamente un depósito.</t>
+  </si>
+  <si>
+    <t>Batteriet förbrukas per träff, oavsett om det träffar en resurs eller varelse.
+Det krävs upp till 320 träffar för att helt förstöra en fyndighet.</t>
+  </si>
+  <si>
+    <t>อัตราการใช้พลังงานแบตเตอรี่ต่อการโจมตีแต่ละครั้ง ไม่ว่าจะโจมตีทรัพยากรหรือสิ่งมีชีวิต
+ต้องโจมตีมากถึง 320 ครั้งจึงจะทำลายแหล่งทรัพยากรได้ทั้งหมด</t>
+  </si>
+  <si>
+    <t>İster kaynağa ister yaratığa vurun, her vuruşta pil tüketimi artar.
+Bir kaynağı tamamen yok etmek 320 vuruşa kadar sürebilir.</t>
+  </si>
+  <si>
+    <t>Розрядка батареї за удар, незалежно від того, чи вражає він ресурс чи істоту.
+Для повного знищення родовища потрібно до 320 ударів.</t>
+  </si>
+  <si>
+    <t>Mức hao pin mỗi lần tấn công, cho dù tấn công tài nguyên hay sinh vật.
+Cần tới 320 lần tấn công để phá hủy hoàn toàn một mỏ quặng.</t>
   </si>
   <si>
     <t>DrillTool.HitIntervalLabel</t>
@@ -1576,8 +1543,7 @@
     <t>Ako je omogućeno, iskopani resursi će automatski ući u igračev inventar, slično ponašanju ruke za bušenje kozica.</t>
   </si>
   <si>
-    <t>Pokud je tato funkce aktivní, vytěžené suroviny se automaticky uloží do hráčova inventáře, porodně jako funguje Vrtací paže P.R.A.W.N.
-Ve výchozím nastavení tato možnost není aktivní.</t>
+    <t>Pokud je tato možnost povolena, vytěžené zdroje se automaticky dostanou do hráčova inventáře, podobně jako se chová rameno s krevetovým vrtákem.</t>
   </si>
   <si>
     <t>Hvis aktiveret, vil de udvundne ressourcer automatisk blive indført i spillerens inventar, svarende til en rejeborearms opførsel.</t>
@@ -1979,145 +1945,112 @@
     <t>DrillTool.CreatureDamageTooltip</t>
   </si>
   <si>
-    <t>Damage dealt to creatures.
-This also applies to anything else that can be damaged, like flora or habitat.</t>
-  </si>
-  <si>
-    <t>Skade aan wesens aangerig. Dit geld ook vir enigiets anders wat beskadig kan word, soos flora of habitat.</t>
-  </si>
-  <si>
-    <t>Щети, нанесени на същества.
-Това важи и за всичко друго, което може да бъде повредено, като флора или местообитание.</t>
-  </si>
-  <si>
-    <t>Dany infligit a les criatures.
-Això també s'aplica a qualsevol altra cosa que pugui ser danyada, com la flora o l'hàbitat.</t>
-  </si>
-  <si>
-    <t>对生物造成的伤害。
-这也适用于其他任何可能受到损害的事物，例如植物或栖息地。</t>
-  </si>
-  <si>
-    <t>對生物造成的傷害。
-這也適用於其他任何可能受到損害的事物，例如植物或棲息地。</t>
-  </si>
-  <si>
-    <t>Šteta nanesena stvorenjima.
-To se odnosi i na sve ostalo što može biti oštećeno, poput flore ili staništa.</t>
-  </si>
-  <si>
-    <t>Škoda způsobená tvorům.
-To platí i pro cokoli jiného, ​​co může být poškozeno, jako je flóra nebo biotop.</t>
-  </si>
-  <si>
-    <t>Skade påført dyr.
-Dette gælder også for alt andet, der kan blive beskadiget, såsom flora eller levesteder.</t>
-  </si>
-  <si>
-    <t>Schade toegebracht aan wezens.
-Dit geldt ook voor alles wat beschadigd kan raken, zoals flora of leefgebied.</t>
-  </si>
-  <si>
-    <t>Olenditele tekitatud kahju.
-See kehtib ka kõige muu kohta, mida saab kahjustada, näiteks taimestik või elupaik.</t>
-  </si>
-  <si>
-    <t>Olennoille aiheutettu vahinko.
-Tämä koskee myös kaikkea muuta, mikä voi vaurioitua, kuten kasvistoa tai elinympäristöä.</t>
-  </si>
-  <si>
-    <t>Dégâts infligés aux créatures.
-Ceci s'applique également à tout ce qui peut être endommagé, comme la flore ou l'habitat.</t>
-  </si>
-  <si>
-    <t>Schäden an Lebewesen.
-Dies gilt auch für alles andere, was beschädigt werden kann, wie Pflanzen oder Lebensräume.</t>
-  </si>
-  <si>
-    <t>Ζημιά που προκαλείται σε πλάσματα.
-Αυτό ισχύει και για οτιδήποτε άλλο μπορεί να υποστεί ζημιά, όπως η χλωρίδα ή το βιότοπο.</t>
-  </si>
-  <si>
-    <t>Lényeknek okozott sebzés.
-Ez minden másra is vonatkozik, ami megsérülhet, például a növényekre vagy az élőhelyekre.</t>
-  </si>
-  <si>
-    <t>Damáiste a dhéantar do chréatúir. Baineann sé seo freisin le haon rud eile a d’fhéadfaí a mhilleadh, amhail flóra nó gnáthóg.</t>
-  </si>
-  <si>
-    <t>Danni inflitti alle creature.
-Questo vale anche per qualsiasi altra cosa che possa essere danneggiata, come la flora o l'habitat.</t>
-  </si>
-  <si>
-    <t>生物に与えたダメージ。
-これは、植物や生息地など、ダメージを受ける可能性のある他のあらゆるものにも適用されます。</t>
-  </si>
-  <si>
-    <t>생물에게 가해지는 피해량.
-이는 식물이나 서식지 등 피해를 입을 수 있는 다른 모든 것에도 적용됩니다.</t>
-  </si>
-  <si>
-    <t>Radībām nodarītais bojājums.
-Tas attiecas arī uz visu pārējo, kam var tikt nodarīts kaitējums, piemēram, floru vai dzīvotni.</t>
-  </si>
-  <si>
-    <t>Žala, padaryta gyvūnams.
-Tai taip pat taikoma viskam, kas gali būti pažeista, pavyzdžiui, florai ar buveinei.</t>
-  </si>
-  <si>
-    <t>Skade påført skapninger.
-Dette gjelder også alt annet som kan bli skadet, som flora eller habitat.</t>
-  </si>
-  <si>
-    <t>Obrażenia zadawane stworzeniom. Dotyczy to również wszystkiego innego, co może zostać uszkodzone, np. flory czy siedlisk.</t>
-  </si>
-  <si>
-    <t>Dano causado às criaturas.
-Isso também se aplica a qualquer outra coisa que possa ser danificada, como flora ou habitat.</t>
-  </si>
-  <si>
-    <t>Daune provocate creaturilor.
-Acest lucru se aplică și oricărui alt factor care poate fi deteriorat, cum ar fi flora sau habitatul.</t>
-  </si>
-  <si>
-    <t>Урон, наносимый существам.
-Это также относится ко всему остальному, что может быть повреждено, например, к флоре или среде обитания.</t>
-  </si>
-  <si>
-    <t>Штета нанета створењима.
-Ово се односи и на све остало што може бити оштећено, попут флоре или станишта.</t>
-  </si>
-  <si>
-    <t>Poškodenie spôsobené tvorom.
-Toto platí aj pre čokoľvek iné, čo môže byť poškodené, ako napríklad flóra alebo biotop.</t>
-  </si>
-  <si>
-    <t>Škoda, povzročena bitjem.
-To velja tudi za vse ostalo, kar je mogoče poškodovati, na primer rastlinstvo ali habitat.</t>
-  </si>
-  <si>
-    <t>Daños infligidos a las criaturas.
-Esto también se aplica a cualquier otra cosa que pueda resultar dañada, como la flora o el hábitat.</t>
-  </si>
-  <si>
-    <t>Skador på varelser.
-Detta gäller även allt annat som kan skadas, som flora eller livsmiljö.</t>
-  </si>
-  <si>
-    <t>ความเสียหายที่เกิดขึ้นกับสิ่งมีชีวิต
-นอกจากนี้ยังรวมถึงสิ่งอื่น ๆ ที่อาจได้รับความเสียหาย เช่น พืชหรือที่อยู่อาศัย</t>
-  </si>
-  <si>
-    <t>Canlılara verilen hasar.
-Bu, bitki örtüsü veya yaşam alanı gibi hasar görebilecek diğer her şey için de geçerlidir.</t>
-  </si>
-  <si>
-    <t>Шкода, завдана істотам.
-Це також стосується всього іншого, що може бути пошкоджено, як-от флора чи середовище існування.</t>
-  </si>
-  <si>
-    <t>Thiệt hại gây ra cho sinh vật.
-Điều này cũng áp dụng cho bất cứ thứ gì khác có thể bị hư hại, như thực vật hoặc môi trường sống.</t>
+    <t>Damage dealt to creatures, flora, and habitat.</t>
+  </si>
+  <si>
+    <t>Skade aangerig aan wesens, flora en habitat.</t>
+  </si>
+  <si>
+    <t>Щети, нанесени на същества, флора и местообитания.</t>
+  </si>
+  <si>
+    <t>Danys causats a criatures, flora i hàbitat.</t>
+  </si>
+  <si>
+    <t>对生物、植物和栖息地造成的损害。</t>
+  </si>
+  <si>
+    <t>對生物、植物和棲息地造成的損害。</t>
+  </si>
+  <si>
+    <t>Šteta nanesena stvorenjima, flori i staništu.</t>
+  </si>
+  <si>
+    <t>Škoda způsobená tvorům, flóře a prostředí.</t>
+  </si>
+  <si>
+    <t>Skader påført dyr, flora og levesteder.</t>
+  </si>
+  <si>
+    <t>Schade toegebracht aan dieren, planten en hun leefomgeving.</t>
+  </si>
+  <si>
+    <t>Kahju tekitatud olenditele, taimestikule ja elupaikadele.</t>
+  </si>
+  <si>
+    <t>Olennoille, kasveille ja elinympäristöille aiheutettu vahinko.</t>
+  </si>
+  <si>
+    <t>Dommages causés aux créatures, à la flore et à leur habitat.</t>
+  </si>
+  <si>
+    <t>Schäden an Tieren, Pflanzen und Lebensräumen.</t>
+  </si>
+  <si>
+    <t>Ζημιές που προκλήθηκαν σε πλάσματα, χλωρίδα και βιότοπο.</t>
+  </si>
+  <si>
+    <t>Élőlényeknek, növényeknek és élőhelyeknek okozott sebzés.</t>
+  </si>
+  <si>
+    <t>Damáiste a rinneadh do chréatúir, flóra agus gnáthóg.</t>
+  </si>
+  <si>
+    <t>Danni arrecati a creature, flora e habitat.</t>
+  </si>
+  <si>
+    <t>生物、植物、生息地に与えられた損害。</t>
+  </si>
+  <si>
+    <t>생물, 식물 및 서식지에 가해진 피해.</t>
+  </si>
+  <si>
+    <t>Bojājumi nodarīti radībām, florai un dzīvotnei.</t>
+  </si>
+  <si>
+    <t>Žala, padaryta gyviams, florai ir buveinei.</t>
+  </si>
+  <si>
+    <t>Skader påført dyr, flora og habitat.</t>
+  </si>
+  <si>
+    <t>Szkody wyrządzone istotom, florze i siedliskom.</t>
+  </si>
+  <si>
+    <t>Danos causados ​​a criaturas, flora e habitat.</t>
+  </si>
+  <si>
+    <t>Daune provocate creaturilor, florei și habitatului.</t>
+  </si>
+  <si>
+    <t>Ущерб, нанесенный животным, флоре и среде обитания.</t>
+  </si>
+  <si>
+    <t>Штета нанета створењима, флори и станишту.</t>
+  </si>
+  <si>
+    <t>Škoda spôsobená tvorom, flóre a biotopom.</t>
+  </si>
+  <si>
+    <t>Škoda, povzročena bitjem, rastlinstvu in habitatu.</t>
+  </si>
+  <si>
+    <t>Daños causados ​​a criaturas, flora y hábitat.</t>
+  </si>
+  <si>
+    <t>Skador på varelser, flora och livsmiljöer.</t>
+  </si>
+  <si>
+    <t>ความเสียหายที่เกิดขึ้นกับสิ่งมีชีวิต พืช และแหล่งที่อยู่อาศัย</t>
+  </si>
+  <si>
+    <t>Canlılara, bitki örtüsüne ve yaşam alanlarına verilen zarar.</t>
+  </si>
+  <si>
+    <t>Шкода, завдана істотам, флорі та середовищу існування.</t>
+  </si>
+  <si>
+    <t>Thiệt hại gây ra cho sinh vật, thực vật và môi trường sống.</t>
   </si>
 </sst>
 </file>
@@ -3246,1730 +3179,1730 @@
         <v>148</v>
       </c>
       <c r="AI4" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="AJ4" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="AJ4" s="8" t="s">
+      <c r="AK4" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="AK4" s="8" t="s">
+      <c r="AL4" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="AL4" s="15" t="s">
+      <c r="AM4" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="AM4" s="8" t="s">
+      <c r="AN4" s="17" t="s">
         <v>153</v>
-      </c>
-      <c r="AN4" s="17" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="H5" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="I5" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="K5" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="L5" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="N5" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="O5" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="P5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="P5" s="14" t="s">
+      <c r="Q5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="Q5" s="14" t="s">
+      <c r="R5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="R5" s="14" t="s">
+      <c r="S5" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="S5" s="14" t="s">
+      <c r="T5" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="T5" s="14" t="s">
+      <c r="U5" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="U5" s="14" t="s">
+      <c r="V5" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="V5" s="14" t="s">
+      <c r="W5" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="W5" s="14" t="s">
+      <c r="X5" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="X5" s="14" t="s">
+      <c r="Y5" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="Y5" s="14" t="s">
+      <c r="Z5" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="Z5" s="14" t="s">
+      <c r="AA5" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB5" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="AA5" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB5" s="14" t="s">
+      <c r="AC5" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="AC5" s="15" t="s">
+      <c r="AD5" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="AD5" s="14" t="s">
+      <c r="AE5" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="AF5" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="AE5" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF5" s="14" t="s">
+      <c r="AG5" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="AG5" s="14" t="s">
+      <c r="AH5" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="AI5" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="AH5" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI5" s="15" t="s">
+      <c r="AJ5" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="AJ5" s="14" t="s">
+      <c r="AK5" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="AK5" s="14" t="s">
+      <c r="AL5" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="AL5" s="15" t="s">
+      <c r="AM5" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="AM5" s="14" t="s">
+      <c r="AN5" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="AN5" s="16" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="O6" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="O6" s="15" t="s">
+      <c r="P6" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="Q6" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="R6" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="S6" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="T6" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="T6" s="8" t="s">
+      <c r="U6" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="U6" s="8" t="s">
+      <c r="V6" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="V6" s="8" t="s">
+      <c r="W6" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="X6" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="X6" s="8" t="s">
+      <c r="Y6" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Z6" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="Z6" s="8" t="s">
+      <c r="AA6" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB6" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="AA6" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB6" s="8" t="s">
+      <c r="AC6" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="AC6" s="15" t="s">
+      <c r="AD6" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="AD6" s="8" t="s">
+      <c r="AE6" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="AF6" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="AE6" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="AF6" s="8" t="s">
+      <c r="AG6" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="AG6" s="8" t="s">
+      <c r="AH6" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="AH6" s="8" t="s">
+      <c r="AI6" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="AI6" s="15" t="s">
+      <c r="AJ6" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="AJ6" s="8" t="s">
+      <c r="AK6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AK6" s="8" t="s">
+      <c r="AL6" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="AL6" s="15" t="s">
+      <c r="AM6" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="AM6" s="8" t="s">
+      <c r="AN6" s="17" t="s">
         <v>227</v>
-      </c>
-      <c r="AN6" s="17" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="F7" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="H7" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="I7" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="J7" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="K7" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="L7" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="M7" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="N7" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="O7" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="O7" s="15" t="s">
+      <c r="P7" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="Q7" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="Q7" s="14" t="s">
+      <c r="R7" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="R7" s="14" t="s">
+      <c r="S7" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="S7" s="14" t="s">
+      <c r="T7" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="T7" s="14" t="s">
+      <c r="U7" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="U7" s="14" t="s">
+      <c r="V7" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="V7" s="14" t="s">
+      <c r="W7" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="X7" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="X7" s="14" t="s">
+      <c r="Y7" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="Y7" s="14" t="s">
+      <c r="Z7" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="Z7" s="14" t="s">
+      <c r="AA7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB7" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="AA7" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="AB7" s="14" t="s">
+      <c r="AC7" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="AC7" s="15" t="s">
+      <c r="AD7" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="AD7" s="14" t="s">
+      <c r="AE7" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AF7" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="AE7" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="AF7" s="14" t="s">
+      <c r="AG7" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="AG7" s="14" t="s">
+      <c r="AH7" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="AH7" s="14" t="s">
+      <c r="AI7" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="AI7" s="15" t="s">
+      <c r="AJ7" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="AJ7" s="14" t="s">
+      <c r="AK7" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="AK7" s="14" t="s">
+      <c r="AL7" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="AL7" s="15" t="s">
+      <c r="AM7" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="AM7" s="14" t="s">
+      <c r="AN7" s="16" t="s">
         <v>265</v>
-      </c>
-      <c r="AN7" s="16" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="N8" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="O8" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="O8" s="15" t="s">
+      <c r="P8" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="Q8" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="Q8" s="8" t="s">
+      <c r="R8" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="S8" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="S8" s="8" t="s">
+      <c r="T8" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="T8" s="8" t="s">
+      <c r="U8" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="U8" s="8" t="s">
+      <c r="V8" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="V8" s="8" t="s">
+      <c r="W8" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="W8" s="8" t="s">
+      <c r="X8" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="X8" s="8" t="s">
+      <c r="Y8" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="Y8" s="8" t="s">
+      <c r="Z8" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="Z8" s="8" t="s">
+      <c r="AA8" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="AB8" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="AA8" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB8" s="8" t="s">
+      <c r="AC8" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="AC8" s="15" t="s">
+      <c r="AD8" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="AD8" s="8" t="s">
+      <c r="AE8" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="AF8" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="AE8" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="AF8" s="8" t="s">
+      <c r="AG8" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="AG8" s="8" t="s">
+      <c r="AH8" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="AH8" s="8" t="s">
+      <c r="AI8" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="AI8" s="15" t="s">
+      <c r="AJ8" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="AJ8" s="8" t="s">
+      <c r="AK8" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="AK8" s="8" t="s">
+      <c r="AL8" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="AL8" s="15" t="s">
+      <c r="AM8" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="AM8" s="8" t="s">
+      <c r="AN8" s="17" t="s">
         <v>303</v>
-      </c>
-      <c r="AN8" s="17" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E9" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="F9" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="G9" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="H9" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="I9" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="J9" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="L9" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="M9" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="N9" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="O9" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="O9" s="14" t="s">
+      <c r="P9" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="Q9" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="Q9" s="14" t="s">
+      <c r="R9" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="S9" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="T9" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="T9" s="14" t="s">
+      <c r="U9" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="U9" s="14" t="s">
+      <c r="V9" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="V9" s="14" t="s">
+      <c r="W9" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="W9" s="14" t="s">
+      <c r="X9" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="X9" s="14" t="s">
+      <c r="Y9" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="Y9" s="14" t="s">
+      <c r="Z9" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="Z9" s="14" t="s">
+      <c r="AA9" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="AB9" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="AA9" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="AB9" s="14" t="s">
+      <c r="AC9" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="AC9" s="14" t="s">
+      <c r="AD9" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="AD9" s="14" t="s">
+      <c r="AE9" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="AF9" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="AE9" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="AF9" s="14" t="s">
+      <c r="AG9" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="AG9" s="14" t="s">
+      <c r="AH9" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="AH9" s="14" t="s">
+      <c r="AI9" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="AJ9" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="AI9" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="AJ9" s="14" t="s">
+      <c r="AK9" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="AK9" s="14" t="s">
+      <c r="AL9" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="AL9" s="14" t="s">
+      <c r="AM9" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="AM9" s="14" t="s">
+      <c r="AN9" s="16" t="s">
         <v>340</v>
-      </c>
-      <c r="AN9" s="16" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="T10" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="T10" s="8" t="s">
-        <v>344</v>
-      </c>
       <c r="U10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="W10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="X10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Z10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AB10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AC10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AD10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AE10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AF10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AH10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AI10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AJ10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AK10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AL10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AM10" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="E11" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="O11" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="O11" s="14" t="s">
+      <c r="P11" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="R11" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="P11" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q11" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="R11" s="14" t="s">
+      <c r="S11" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="T11" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="V11" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="T11" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="U11" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="V11" s="14" t="s">
+      <c r="W11" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="X11" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y11" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z11" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA11" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB11" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="AC11" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="W11" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="X11" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y11" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="Z11" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="AA11" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="AB11" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="AC11" s="14" t="s">
+      <c r="AD11" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AE11" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AF11" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AG11" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="AH11" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="AI11" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="AJ11" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="AK11" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="AL11" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="AD11" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="AE11" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="AF11" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="AG11" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="AH11" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="AI11" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="AJ11" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="AK11" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="AL11" s="14" t="s">
-        <v>353</v>
-      </c>
       <c r="AM11" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="AN11" s="16" t="s">
         <v>265</v>
-      </c>
-      <c r="AN11" s="16" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>354</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="C12" s="20" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="D12" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="F12" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="G12" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="H12" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="I12" s="21" t="s">
         <v>361</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="J12" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="K12" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="L12" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="M12" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="M12" s="21" t="s">
+      <c r="N12" s="21" t="s">
         <v>366</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="O12" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="O12" s="21" t="s">
+      <c r="P12" s="21" t="s">
         <v>368</v>
       </c>
-      <c r="P12" s="21" t="s">
+      <c r="Q12" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="Q12" s="21" t="s">
+      <c r="R12" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="R12" s="21" t="s">
+      <c r="S12" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="S12" s="21" t="s">
+      <c r="T12" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="T12" s="21" t="s">
+      <c r="U12" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="U12" s="21" t="s">
+      <c r="V12" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="V12" s="21" t="s">
+      <c r="W12" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="W12" s="21" t="s">
+      <c r="X12" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="X12" s="21" t="s">
+      <c r="Y12" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="Y12" s="21" t="s">
+      <c r="Z12" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="Z12" s="21" t="s">
+      <c r="AA12" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="AB12" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="AA12" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="AB12" s="21" t="s">
+      <c r="AC12" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="AC12" s="21" t="s">
+      <c r="AD12" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="AD12" s="21" t="s">
+      <c r="AE12" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="AF12" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="AE12" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="AF12" s="21" t="s">
+      <c r="AG12" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="AG12" s="21" t="s">
+      <c r="AH12" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="AH12" s="21" t="s">
+      <c r="AI12" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="AJ12" s="21" t="s">
         <v>385</v>
       </c>
-      <c r="AI12" s="21" t="s">
-        <v>385</v>
-      </c>
-      <c r="AJ12" s="21" t="s">
+      <c r="AK12" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="AK12" s="21" t="s">
+      <c r="AL12" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="AL12" s="21" t="s">
+      <c r="AM12" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="AM12" s="21" t="s">
+      <c r="AN12" s="22" t="s">
         <v>389</v>
-      </c>
-      <c r="AN12" s="22" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>391</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="C13" s="23" t="s">
         <v>392</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="D13" s="23" t="s">
         <v>393</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="E13" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="F13" s="23" t="s">
         <v>395</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="G13" s="23" t="s">
         <v>396</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="H13" s="23" t="s">
         <v>397</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="I13" s="23" t="s">
         <v>398</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="J13" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="K13" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="L13" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="K13" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="L13" s="23" t="s">
+      <c r="M13" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="N13" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="N13" s="23" t="s">
+      <c r="O13" s="23" t="s">
         <v>403</v>
       </c>
-      <c r="O13" s="23" t="s">
+      <c r="P13" s="23" t="s">
         <v>404</v>
       </c>
-      <c r="P13" s="23" t="s">
+      <c r="Q13" s="23" t="s">
         <v>405</v>
       </c>
-      <c r="Q13" s="23" t="s">
+      <c r="R13" s="23" t="s">
         <v>406</v>
       </c>
-      <c r="R13" s="23" t="s">
+      <c r="S13" s="23" t="s">
         <v>407</v>
       </c>
-      <c r="S13" s="23" t="s">
+      <c r="T13" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="T13" s="23" t="s">
+      <c r="U13" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="U13" s="23" t="s">
+      <c r="V13" s="24" t="s">
         <v>410</v>
       </c>
-      <c r="V13" s="24" t="s">
+      <c r="W13" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="W13" s="24" t="s">
+      <c r="X13" s="24" t="s">
         <v>412</v>
       </c>
-      <c r="X13" s="24" t="s">
+      <c r="Y13" s="24" t="s">
         <v>413</v>
       </c>
-      <c r="Y13" s="24" t="s">
+      <c r="Z13" s="24" t="s">
         <v>414</v>
       </c>
-      <c r="Z13" s="24" t="s">
+      <c r="AA13" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB13" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="AA13" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB13" s="24" t="s">
+      <c r="AC13" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="AC13" s="24" t="s">
+      <c r="AD13" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="AD13" s="24" t="s">
+      <c r="AE13" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="AF13" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="AE13" s="24" t="s">
-        <v>418</v>
-      </c>
-      <c r="AF13" s="24" t="s">
+      <c r="AG13" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="AG13" s="24" t="s">
+      <c r="AH13" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="AI13" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="AJ13" s="24" t="s">
         <v>420</v>
       </c>
-      <c r="AH13" s="24" t="s">
-        <v>392</v>
-      </c>
-      <c r="AI13" s="24" t="s">
-        <v>392</v>
-      </c>
-      <c r="AJ13" s="24" t="s">
+      <c r="AK13" s="24" t="s">
         <v>421</v>
       </c>
-      <c r="AK13" s="24" t="s">
+      <c r="AL13" s="24" t="s">
         <v>422</v>
       </c>
-      <c r="AL13" s="24" t="s">
+      <c r="AM13" s="24" t="s">
         <v>423</v>
       </c>
-      <c r="AM13" s="24" t="s">
+      <c r="AN13" s="24" t="s">
         <v>424</v>
-      </c>
-      <c r="AN13" s="24" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>426</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="C14" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="D14" s="23" t="s">
         <v>428</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="E14" s="23" t="s">
         <v>429</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="F14" s="23" t="s">
         <v>430</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="G14" s="23" t="s">
         <v>431</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="H14" s="23" t="s">
         <v>432</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="I14" s="23" t="s">
         <v>433</v>
       </c>
-      <c r="I14" s="23" t="s">
+      <c r="J14" s="23" t="s">
         <v>434</v>
       </c>
-      <c r="J14" s="23" t="s">
+      <c r="K14" s="23" t="s">
         <v>435</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="L14" s="23" t="s">
         <v>436</v>
       </c>
-      <c r="L14" s="23" t="s">
+      <c r="M14" s="23" t="s">
         <v>437</v>
       </c>
-      <c r="M14" s="23" t="s">
+      <c r="N14" s="23" t="s">
         <v>438</v>
       </c>
-      <c r="N14" s="23" t="s">
+      <c r="O14" s="23" t="s">
         <v>439</v>
       </c>
-      <c r="O14" s="23" t="s">
+      <c r="P14" s="23" t="s">
         <v>440</v>
       </c>
-      <c r="P14" s="23" t="s">
+      <c r="Q14" s="23" t="s">
         <v>441</v>
       </c>
-      <c r="Q14" s="23" t="s">
+      <c r="R14" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="R14" s="23" t="s">
+      <c r="S14" s="23" t="s">
         <v>443</v>
       </c>
-      <c r="S14" s="23" t="s">
+      <c r="T14" s="23" t="s">
         <v>444</v>
       </c>
-      <c r="T14" s="23" t="s">
+      <c r="U14" s="23" t="s">
         <v>445</v>
       </c>
-      <c r="U14" s="23" t="s">
+      <c r="V14" s="24" t="s">
         <v>446</v>
       </c>
-      <c r="V14" s="24" t="s">
+      <c r="W14" s="24" t="s">
         <v>447</v>
       </c>
-      <c r="W14" s="24" t="s">
+      <c r="X14" s="24" t="s">
         <v>448</v>
       </c>
-      <c r="X14" s="24" t="s">
+      <c r="Y14" s="24" t="s">
         <v>449</v>
       </c>
-      <c r="Y14" s="24" t="s">
+      <c r="Z14" s="24" t="s">
         <v>450</v>
       </c>
-      <c r="Z14" s="24" t="s">
+      <c r="AA14" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="AB14" s="24" t="s">
         <v>451</v>
       </c>
-      <c r="AA14" s="24" t="s">
-        <v>451</v>
-      </c>
-      <c r="AB14" s="24" t="s">
+      <c r="AC14" s="24" t="s">
         <v>452</v>
       </c>
-      <c r="AC14" s="24" t="s">
+      <c r="AD14" s="24" t="s">
         <v>453</v>
       </c>
-      <c r="AD14" s="24" t="s">
+      <c r="AE14" s="24" t="s">
+        <v>453</v>
+      </c>
+      <c r="AF14" s="24" t="s">
         <v>454</v>
       </c>
-      <c r="AE14" s="24" t="s">
-        <v>454</v>
-      </c>
-      <c r="AF14" s="24" t="s">
+      <c r="AG14" s="24" t="s">
         <v>455</v>
       </c>
-      <c r="AG14" s="24" t="s">
+      <c r="AH14" s="24" t="s">
         <v>456</v>
       </c>
-      <c r="AH14" s="24" t="s">
+      <c r="AI14" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="AJ14" s="24" t="s">
         <v>457</v>
       </c>
-      <c r="AI14" s="24" t="s">
-        <v>457</v>
-      </c>
-      <c r="AJ14" s="24" t="s">
+      <c r="AK14" s="24" t="s">
         <v>458</v>
       </c>
-      <c r="AK14" s="24" t="s">
+      <c r="AL14" s="24" t="s">
         <v>459</v>
       </c>
-      <c r="AL14" s="24" t="s">
+      <c r="AM14" s="24" t="s">
         <v>460</v>
       </c>
-      <c r="AM14" s="24" t="s">
+      <c r="AN14" s="24" t="s">
         <v>461</v>
-      </c>
-      <c r="AN14" s="24" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="B15" s="23" t="s">
         <v>463</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="C15" s="23" t="s">
         <v>464</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="D15" s="23" t="s">
         <v>465</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="E15" s="23" t="s">
         <v>466</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="F15" s="23" t="s">
         <v>467</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="G15" s="23" t="s">
         <v>468</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="H15" s="23" t="s">
         <v>469</v>
       </c>
-      <c r="H15" s="23" t="s">
+      <c r="I15" s="23" t="s">
         <v>470</v>
       </c>
-      <c r="I15" s="23" t="s">
+      <c r="J15" s="23" t="s">
         <v>471</v>
       </c>
-      <c r="J15" s="23" t="s">
+      <c r="K15" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="L15" s="23" t="s">
         <v>472</v>
       </c>
-      <c r="K15" s="23" t="s">
+      <c r="M15" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="O15" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q15" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="S15" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="T15" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="U15" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="V15" s="24" t="s">
+        <v>482</v>
+      </c>
+      <c r="W15" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="X15" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="Y15" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z15" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="AA15" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="AB15" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="AC15" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="AD15" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="L15" s="23" t="s">
-        <v>473</v>
-      </c>
-      <c r="M15" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="N15" s="23" t="s">
-        <v>475</v>
-      </c>
-      <c r="O15" s="23" t="s">
-        <v>476</v>
-      </c>
-      <c r="P15" s="23" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q15" s="23" t="s">
-        <v>478</v>
-      </c>
-      <c r="R15" s="23" t="s">
-        <v>479</v>
-      </c>
-      <c r="S15" s="23" t="s">
-        <v>480</v>
-      </c>
-      <c r="T15" s="23" t="s">
-        <v>481</v>
-      </c>
-      <c r="U15" s="23" t="s">
-        <v>482</v>
-      </c>
-      <c r="V15" s="24" t="s">
-        <v>483</v>
-      </c>
-      <c r="W15" s="24" t="s">
-        <v>484</v>
-      </c>
-      <c r="X15" s="24" t="s">
-        <v>472</v>
-      </c>
-      <c r="Y15" s="24" t="s">
-        <v>485</v>
-      </c>
-      <c r="Z15" s="24" t="s">
-        <v>486</v>
-      </c>
-      <c r="AA15" s="24" t="s">
-        <v>486</v>
-      </c>
-      <c r="AB15" s="24" t="s">
-        <v>487</v>
-      </c>
-      <c r="AC15" s="24" t="s">
+      <c r="AE15" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="AF15" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="AG15" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="AH15" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="AI15" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="AJ15" s="24" t="s">
         <v>488</v>
       </c>
-      <c r="AD15" s="24" t="s">
-        <v>466</v>
-      </c>
-      <c r="AE15" s="24" t="s">
-        <v>466</v>
-      </c>
-      <c r="AF15" s="24" t="s">
-        <v>471</v>
-      </c>
-      <c r="AG15" s="24" t="s">
-        <v>470</v>
-      </c>
-      <c r="AH15" s="24" t="s">
-        <v>467</v>
-      </c>
-      <c r="AI15" s="24" t="s">
-        <v>467</v>
-      </c>
-      <c r="AJ15" s="24" t="s">
+      <c r="AK15" s="24" t="s">
         <v>489</v>
       </c>
-      <c r="AK15" s="24" t="s">
+      <c r="AL15" s="24" t="s">
         <v>490</v>
       </c>
-      <c r="AL15" s="24" t="s">
+      <c r="AM15" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="AN15" s="24" t="s">
         <v>491</v>
-      </c>
-      <c r="AM15" s="24" t="s">
-        <v>466</v>
-      </c>
-      <c r="AN15" s="24" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="s">
+        <v>492</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>493</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="C16" s="23" t="s">
         <v>494</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="23" t="s">
         <v>495</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="E16" s="23" t="s">
         <v>496</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="F16" s="23" t="s">
         <v>497</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="G16" s="23" t="s">
         <v>498</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="H16" s="23" t="s">
         <v>499</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="I16" s="23" t="s">
         <v>500</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="J16" s="23" t="s">
         <v>501</v>
       </c>
-      <c r="J16" s="23" t="s">
+      <c r="K16" s="23" t="s">
         <v>502</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="L16" s="23" t="s">
         <v>503</v>
       </c>
-      <c r="L16" s="23" t="s">
+      <c r="M16" s="23" t="s">
         <v>504</v>
       </c>
-      <c r="M16" s="23" t="s">
+      <c r="N16" s="23" t="s">
         <v>505</v>
       </c>
-      <c r="N16" s="23" t="s">
+      <c r="O16" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="O16" s="23" t="s">
+      <c r="P16" s="23" t="s">
         <v>507</v>
       </c>
-      <c r="P16" s="23" t="s">
+      <c r="Q16" s="23" t="s">
         <v>508</v>
       </c>
-      <c r="Q16" s="23" t="s">
+      <c r="R16" s="23" t="s">
         <v>509</v>
       </c>
-      <c r="R16" s="23" t="s">
+      <c r="S16" s="23" t="s">
         <v>510</v>
       </c>
-      <c r="S16" s="23" t="s">
+      <c r="T16" s="23" t="s">
         <v>511</v>
       </c>
-      <c r="T16" s="23" t="s">
+      <c r="U16" s="23" t="s">
         <v>512</v>
       </c>
-      <c r="U16" s="23" t="s">
+      <c r="V16" s="24" t="s">
         <v>513</v>
       </c>
-      <c r="V16" s="24" t="s">
+      <c r="W16" s="24" t="s">
         <v>514</v>
       </c>
-      <c r="W16" s="24" t="s">
+      <c r="X16" s="24" t="s">
         <v>515</v>
       </c>
-      <c r="X16" s="24" t="s">
+      <c r="Y16" s="24" t="s">
         <v>516</v>
       </c>
-      <c r="Y16" s="24" t="s">
+      <c r="Z16" s="24" t="s">
         <v>517</v>
       </c>
-      <c r="Z16" s="24" t="s">
+      <c r="AA16" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="AB16" s="24" t="s">
         <v>518</v>
       </c>
-      <c r="AA16" s="24" t="s">
-        <v>518</v>
-      </c>
-      <c r="AB16" s="24" t="s">
+      <c r="AC16" s="24" t="s">
         <v>519</v>
       </c>
-      <c r="AC16" s="24" t="s">
+      <c r="AD16" s="24" t="s">
         <v>520</v>
       </c>
-      <c r="AD16" s="24" t="s">
+      <c r="AE16" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="AF16" s="24" t="s">
         <v>521</v>
       </c>
-      <c r="AE16" s="24" t="s">
-        <v>521</v>
-      </c>
-      <c r="AF16" s="24" t="s">
+      <c r="AG16" s="24" t="s">
         <v>522</v>
       </c>
-      <c r="AG16" s="24" t="s">
+      <c r="AH16" s="24" t="s">
         <v>523</v>
       </c>
-      <c r="AH16" s="24" t="s">
+      <c r="AI16" s="24" t="s">
+        <v>523</v>
+      </c>
+      <c r="AJ16" s="24" t="s">
         <v>524</v>
       </c>
-      <c r="AI16" s="24" t="s">
-        <v>524</v>
-      </c>
-      <c r="AJ16" s="24" t="s">
+      <c r="AK16" s="24" t="s">
         <v>525</v>
       </c>
-      <c r="AK16" s="24" t="s">
+      <c r="AL16" s="24" t="s">
         <v>526</v>
       </c>
-      <c r="AL16" s="24" t="s">
+      <c r="AM16" s="24" t="s">
         <v>527</v>
       </c>
-      <c r="AM16" s="24" t="s">
+      <c r="AN16" s="24" t="s">
         <v>528</v>
-      </c>
-      <c r="AN16" s="24" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>530</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="C17" s="23" t="s">
         <v>531</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="D17" s="23" t="s">
         <v>532</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="E17" s="23" t="s">
         <v>533</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="F17" s="23" t="s">
         <v>534</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="G17" s="23" t="s">
         <v>535</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="H17" s="23" t="s">
         <v>536</v>
       </c>
-      <c r="H17" s="23" t="s">
+      <c r="I17" s="23" t="s">
         <v>537</v>
       </c>
-      <c r="I17" s="23" t="s">
+      <c r="J17" s="23" t="s">
         <v>538</v>
       </c>
-      <c r="J17" s="23" t="s">
+      <c r="K17" s="23" t="s">
         <v>539</v>
       </c>
-      <c r="K17" s="23" t="s">
+      <c r="L17" s="23" t="s">
         <v>540</v>
       </c>
-      <c r="L17" s="23" t="s">
+      <c r="M17" s="23" t="s">
         <v>541</v>
       </c>
-      <c r="M17" s="23" t="s">
+      <c r="N17" s="23" t="s">
         <v>542</v>
       </c>
-      <c r="N17" s="23" t="s">
+      <c r="O17" s="23" t="s">
         <v>543</v>
       </c>
-      <c r="O17" s="23" t="s">
+      <c r="P17" s="23" t="s">
         <v>544</v>
       </c>
-      <c r="P17" s="23" t="s">
+      <c r="Q17" s="23" t="s">
         <v>545</v>
       </c>
-      <c r="Q17" s="23" t="s">
+      <c r="R17" s="23" t="s">
         <v>546</v>
       </c>
-      <c r="R17" s="23" t="s">
+      <c r="S17" s="23" t="s">
         <v>547</v>
       </c>
-      <c r="S17" s="23" t="s">
+      <c r="T17" s="23" t="s">
         <v>548</v>
       </c>
-      <c r="T17" s="23" t="s">
+      <c r="U17" s="23" t="s">
         <v>549</v>
       </c>
-      <c r="U17" s="23" t="s">
+      <c r="V17" s="24" t="s">
         <v>550</v>
       </c>
-      <c r="V17" s="24" t="s">
+      <c r="W17" s="24" t="s">
         <v>551</v>
       </c>
-      <c r="W17" s="24" t="s">
+      <c r="X17" s="24" t="s">
         <v>552</v>
       </c>
-      <c r="X17" s="24" t="s">
+      <c r="Y17" s="24" t="s">
         <v>553</v>
       </c>
-      <c r="Y17" s="24" t="s">
+      <c r="Z17" s="24" t="s">
         <v>554</v>
       </c>
-      <c r="Z17" s="24" t="s">
+      <c r="AA17" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="AB17" s="24" t="s">
         <v>555</v>
       </c>
-      <c r="AA17" s="24" t="s">
-        <v>555</v>
-      </c>
-      <c r="AB17" s="24" t="s">
+      <c r="AC17" s="24" t="s">
         <v>556</v>
       </c>
-      <c r="AC17" s="24" t="s">
+      <c r="AD17" s="24" t="s">
         <v>557</v>
       </c>
-      <c r="AD17" s="24" t="s">
+      <c r="AE17" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="AF17" s="24" t="s">
         <v>558</v>
       </c>
-      <c r="AE17" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="AF17" s="24" t="s">
+      <c r="AG17" s="24" t="s">
         <v>559</v>
       </c>
-      <c r="AG17" s="24" t="s">
+      <c r="AH17" s="24" t="s">
         <v>560</v>
       </c>
-      <c r="AH17" s="24" t="s">
+      <c r="AI17" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="AJ17" s="24" t="s">
         <v>561</v>
       </c>
-      <c r="AI17" s="24" t="s">
-        <v>561</v>
-      </c>
-      <c r="AJ17" s="24" t="s">
+      <c r="AK17" s="24" t="s">
         <v>562</v>
       </c>
-      <c r="AK17" s="24" t="s">
+      <c r="AL17" s="24" t="s">
         <v>563</v>
       </c>
-      <c r="AL17" s="24" t="s">
+      <c r="AM17" s="24" t="s">
         <v>564</v>
       </c>
-      <c r="AM17" s="24" t="s">
+      <c r="AN17" s="24" t="s">
         <v>565</v>
-      </c>
-      <c r="AN17" s="24" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="s">
+        <v>566</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>567</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="C18" s="23" t="s">
         <v>568</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="D18" s="23" t="s">
         <v>569</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="E18" s="23" t="s">
         <v>570</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="F18" s="23" t="s">
         <v>571</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="G18" s="23" t="s">
         <v>572</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="H18" s="23" t="s">
         <v>573</v>
       </c>
-      <c r="H18" s="23" t="s">
+      <c r="I18" s="23" t="s">
         <v>574</v>
       </c>
-      <c r="I18" s="23" t="s">
+      <c r="J18" s="23" t="s">
         <v>575</v>
       </c>
-      <c r="J18" s="23" t="s">
+      <c r="K18" s="23" t="s">
         <v>576</v>
       </c>
-      <c r="K18" s="23" t="s">
+      <c r="L18" s="23" t="s">
         <v>577</v>
       </c>
-      <c r="L18" s="23" t="s">
+      <c r="M18" s="23" t="s">
         <v>578</v>
       </c>
-      <c r="M18" s="23" t="s">
+      <c r="N18" s="23" t="s">
         <v>579</v>
       </c>
-      <c r="N18" s="23" t="s">
+      <c r="O18" s="23" t="s">
         <v>580</v>
       </c>
-      <c r="O18" s="23" t="s">
+      <c r="P18" s="23" t="s">
         <v>581</v>
       </c>
-      <c r="P18" s="23" t="s">
+      <c r="Q18" s="23" t="s">
         <v>582</v>
       </c>
-      <c r="Q18" s="23" t="s">
+      <c r="R18" s="23" t="s">
         <v>583</v>
       </c>
-      <c r="R18" s="23" t="s">
+      <c r="S18" s="23" t="s">
         <v>584</v>
       </c>
-      <c r="S18" s="23" t="s">
+      <c r="T18" s="23" t="s">
         <v>585</v>
       </c>
-      <c r="T18" s="23" t="s">
+      <c r="U18" s="23" t="s">
         <v>586</v>
       </c>
-      <c r="U18" s="23" t="s">
+      <c r="V18" s="24" t="s">
         <v>587</v>
       </c>
-      <c r="V18" s="24" t="s">
+      <c r="W18" s="24" t="s">
         <v>588</v>
       </c>
-      <c r="W18" s="24" t="s">
+      <c r="X18" s="24" t="s">
         <v>589</v>
       </c>
-      <c r="X18" s="24" t="s">
+      <c r="Y18" s="24" t="s">
         <v>590</v>
       </c>
-      <c r="Y18" s="24" t="s">
+      <c r="Z18" s="24" t="s">
         <v>591</v>
       </c>
-      <c r="Z18" s="24" t="s">
+      <c r="AA18" s="24" t="s">
+        <v>591</v>
+      </c>
+      <c r="AB18" s="24" t="s">
         <v>592</v>
       </c>
-      <c r="AA18" s="24" t="s">
-        <v>592</v>
-      </c>
-      <c r="AB18" s="24" t="s">
+      <c r="AC18" s="24" t="s">
         <v>593</v>
       </c>
-      <c r="AC18" s="24" t="s">
+      <c r="AD18" s="24" t="s">
         <v>594</v>
       </c>
-      <c r="AD18" s="24" t="s">
+      <c r="AE18" s="24" t="s">
+        <v>594</v>
+      </c>
+      <c r="AF18" s="24" t="s">
         <v>595</v>
       </c>
-      <c r="AE18" s="24" t="s">
-        <v>595</v>
-      </c>
-      <c r="AF18" s="24" t="s">
+      <c r="AG18" s="24" t="s">
         <v>596</v>
       </c>
-      <c r="AG18" s="24" t="s">
+      <c r="AH18" s="24" t="s">
         <v>597</v>
       </c>
-      <c r="AH18" s="24" t="s">
+      <c r="AI18" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="AJ18" s="24" t="s">
         <v>598</v>
       </c>
-      <c r="AI18" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="AJ18" s="24" t="s">
+      <c r="AK18" s="24" t="s">
         <v>599</v>
       </c>
-      <c r="AK18" s="24" t="s">
+      <c r="AL18" s="24" t="s">
         <v>600</v>
       </c>
-      <c r="AL18" s="24" t="s">
+      <c r="AM18" s="24" t="s">
         <v>601</v>
       </c>
-      <c r="AM18" s="24" t="s">
+      <c r="AN18" s="24" t="s">
         <v>602</v>
-      </c>
-      <c r="AN18" s="24" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="19">
